--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-13 13:15  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -784,58 +784,58 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01175</t>
+          <t>CM-25-02970</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Finca Piedra Infinita Gravascal</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>37</v>
+        <v>512</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>6.45%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>19'457.69</t>
+          <t>49'677.65</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.6485</v>
+        <v>0.3869</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.231</v>
+        <v>0.5897</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4815</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -844,58 +844,58 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02970</t>
+          <t>CM-26-01175</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita Gravascal</t>
+          <t>Côte Rôtie La Mouline</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>512</v>
+        <v>37</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>10.81%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>49'677.65</t>
+          <t>16'491.15</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3869</v>
+        <v>0.6485</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.5897</v>
+        <v>0.1958</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.468</v>
+        <v>0.4674</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -1444,58 +1444,58 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>14'190.88</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.3257</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.1685</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2585</v>
+        <v>0.2628</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1224</v>
+        <v>0.1278</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.4309</v>
+        <v>0.4545</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2458</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1564,58 +1564,58 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3155</v>
+        <v>0.1224</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0683</v>
+        <v>0.4309</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.2166</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1634,48 +1634,48 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>4</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>12'510.88</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.2609</v>
+        <v>0.3155</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1485</v>
+        <v>0.0683</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2159</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 06 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 07 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-13 13:15  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
@@ -2266,17 +2266,17 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>19'457.69</t>
+          <t>16'491.15</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
         <v>0.6485</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.231</v>
+        <v>0.1958</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.4815</v>
+        <v>0.4674</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -2341,11 +2341,11 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2355,26 +2355,26 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0</v>
@@ -2401,11 +2401,11 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -2415,26 +2415,26 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
@@ -2521,11 +2521,11 @@
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -2550,11 +2550,11 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
@@ -2581,11 +2581,11 @@
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -2595,26 +2595,26 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -2737,14 +2737,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 14 Mar 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 15 Mar 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-13 13:15  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>19'457.69</t>
+          <t>16'491.15</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
         <v>0.6485</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.231</v>
+        <v>0.1958</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4815</v>
+        <v>0.4674</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -3006,58 +3006,58 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>14'190.88</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.3257</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.4545</v>
+        <v>0.1685</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2585</v>
+        <v>0.2628</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -3076,108 +3076,108 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1224</v>
+        <v>0.1278</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4309</v>
+        <v>0.4545</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2458</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>12'510.88</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2609</v>
+        <v>0.1224</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1485</v>
+        <v>0.4309</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2159</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -3422,11 +3422,11 @@
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3436,26 +3436,26 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>0</v>
@@ -3482,11 +3482,11 @@
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -3496,26 +3496,26 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
@@ -3542,11 +3542,11 @@
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3556,17 +3556,17 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>0</v>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
@@ -3662,11 +3662,11 @@
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>0</v>
@@ -3722,11 +3722,11 @@
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -3736,26 +3736,26 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
@@ -3782,11 +3782,11 @@
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3796,26 +3796,26 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
@@ -3842,7 +3842,7 @@
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-13 13:15  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4207,58 +4207,58 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01175</t>
+          <t>CM-25-02970</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Finca Piedra Infinita Gravascal</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>37</v>
+        <v>512</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>6.45%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>19'457.69</t>
+          <t>49'677.65</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.6485</v>
+        <v>0.3869</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.231</v>
+        <v>0.5897</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4815</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -4267,58 +4267,58 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02970</t>
+          <t>CM-26-01175</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita Gravascal</t>
+          <t>Côte Rôtie La Mouline</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>512</v>
+        <v>37</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>10.81%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>49'677.65</t>
+          <t>16'491.15</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3869</v>
+        <v>0.6485</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.5897</v>
+        <v>0.1958</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.468</v>
+        <v>0.4674</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -4867,58 +4867,58 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>14'190.88</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.3257</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.1685</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2585</v>
+        <v>0.2628</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -4937,48 +4937,48 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1224</v>
+        <v>0.1278</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.4309</v>
+        <v>0.4545</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2458</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4987,58 +4987,58 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3155</v>
+        <v>0.1224</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0683</v>
+        <v>0.4309</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.2166</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -5057,48 +5057,48 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>4</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>12'510.88</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.2609</v>
+        <v>0.3155</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1485</v>
+        <v>0.0683</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2159</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -6677,26 +6677,26 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="I48" s="4" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -6737,26 +6737,26 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0</v>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -6797,26 +6797,26 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>20</v>
+        <v>643</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>0</v>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -6857,26 +6857,26 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>643</v>
+        <v>42</v>
       </c>
       <c r="I51" s="6" t="n">
         <v>0</v>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02438</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée Conti</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -6932,11 +6932,11 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>410</v>
+        <v>252</v>
       </c>
       <c r="I52" s="4" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -6977,12 +6977,12 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>252</v>
+        <v>126</v>
       </c>
       <c r="I53" s="6" t="n">
         <v>0</v>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -7037,26 +7037,26 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="I54" s="4" t="n">
         <v>0</v>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -7097,12 +7097,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -7112,11 +7112,11 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>28</v>
+        <v>362</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>0</v>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -7157,26 +7157,26 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="I56" s="4" t="n">
         <v>0</v>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -7217,26 +7217,26 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="I57" s="6" t="n">
         <v>0</v>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -7277,26 +7277,26 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -7337,26 +7337,26 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>63</v>
+        <v>543</v>
       </c>
       <c r="I59" s="6" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -7397,26 +7397,26 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>0</v>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -7457,26 +7457,26 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I61" s="6" t="n">
         <v>0</v>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -7532,11 +7532,11 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>191</v>
+        <v>28</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>0</v>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -7577,26 +7577,26 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>543</v>
+        <v>26</v>
       </c>
       <c r="I63" s="6" t="n">
         <v>0</v>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -7637,26 +7637,26 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="I64" s="4" t="n">
         <v>0</v>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -7697,26 +7697,26 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="I65" s="6" t="n">
         <v>0</v>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -7757,26 +7757,26 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>11</v>
+        <v>191</v>
       </c>
       <c r="I66" s="4" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-25-02438</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -7817,12 +7817,12 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Romanée Conti</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -7832,11 +7832,11 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>362</v>
+        <v>410</v>
       </c>
       <c r="I67" s="6" t="n">
         <v>0</v>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-15 10:52  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -705,14 +705,14 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>5'806.44</t>
+          <t>5'818.62</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.0689</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="N5" s="6" t="n">
         <v>0.6276</v>
@@ -885,17 +885,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>16'491.15</t>
+          <t>15'275.79</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
         <v>0.6485</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1958</v>
+        <v>0.1813</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4674</v>
+        <v>0.4616</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>14'190.88</t>
+          <t>13'335.52</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
         <v>0.3257</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1685</v>
+        <v>0.1583</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2628</v>
+        <v>0.2587</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 07 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 08 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-15 10:52  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2266,17 +2266,17 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>16'491.15</t>
+          <t>15'275.79</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
         <v>0.6485</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.1958</v>
+        <v>0.1813</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.4674</v>
+        <v>0.4616</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -2341,11 +2341,11 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2355,26 +2355,26 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0</v>
@@ -2401,11 +2401,11 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -2415,26 +2415,26 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
@@ -2521,11 +2521,11 @@
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -2550,11 +2550,11 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
@@ -2581,11 +2581,11 @@
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -2595,26 +2595,26 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -2737,14 +2737,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 15 Mar 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 16 Mar 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-15 10:52  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2867,14 +2867,14 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>5'806.44</t>
+          <t>5'818.62</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.0689</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>0.6276</v>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>16'491.15</t>
+          <t>15'275.79</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
         <v>0.6485</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.1958</v>
+        <v>0.1813</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4674</v>
+        <v>0.4616</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -3047,17 +3047,17 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>14'190.88</t>
+          <t>13'335.52</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
         <v>0.3257</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1685</v>
+        <v>0.1583</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2628</v>
+        <v>0.2587</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -3422,11 +3422,11 @@
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3436,26 +3436,26 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>0</v>
@@ -3482,11 +3482,11 @@
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -3496,26 +3496,26 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
@@ -3542,11 +3542,11 @@
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3556,17 +3556,17 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>0</v>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
@@ -3662,11 +3662,11 @@
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>0</v>
@@ -3722,11 +3722,11 @@
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -3736,26 +3736,26 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
@@ -3782,11 +3782,11 @@
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3796,26 +3796,26 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
@@ -3842,7 +3842,7 @@
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-15 10:52  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>5'806.44</t>
+          <t>5'818.62</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.0689</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="N5" s="6" t="n">
         <v>0.6276</v>
@@ -4308,17 +4308,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>16'491.15</t>
+          <t>15'275.79</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
         <v>0.6485</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1958</v>
+        <v>0.1813</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4674</v>
+        <v>0.4616</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -4908,17 +4908,17 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>14'190.88</t>
+          <t>13'335.52</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
         <v>0.3257</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1685</v>
+        <v>0.1583</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2628</v>
+        <v>0.2587</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -6677,26 +6677,26 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="I48" s="4" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -6737,26 +6737,26 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0</v>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -6797,26 +6797,26 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>643</v>
+        <v>20</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>0</v>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -6857,26 +6857,26 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>42</v>
+        <v>643</v>
       </c>
       <c r="I51" s="6" t="n">
         <v>0</v>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-25-02438</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Romanée Conti</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -6932,11 +6932,11 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>252</v>
+        <v>410</v>
       </c>
       <c r="I52" s="4" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -6977,12 +6977,12 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>126</v>
+        <v>252</v>
       </c>
       <c r="I53" s="6" t="n">
         <v>0</v>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -7037,26 +7037,26 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="I54" s="4" t="n">
         <v>0</v>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -7097,12 +7097,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -7112,11 +7112,11 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>362</v>
+        <v>28</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>0</v>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -7157,26 +7157,26 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="I56" s="4" t="n">
         <v>0</v>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -7217,26 +7217,26 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="I57" s="6" t="n">
         <v>0</v>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -7277,26 +7277,26 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -7337,26 +7337,26 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>543</v>
+        <v>63</v>
       </c>
       <c r="I59" s="6" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -7397,26 +7397,26 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>0</v>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -7457,26 +7457,26 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I61" s="6" t="n">
         <v>0</v>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -7532,11 +7532,11 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>28</v>
+        <v>191</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>0</v>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -7577,26 +7577,26 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>26</v>
+        <v>543</v>
       </c>
       <c r="I63" s="6" t="n">
         <v>0</v>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -7637,26 +7637,26 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I64" s="4" t="n">
         <v>0</v>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -7697,26 +7697,26 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="I65" s="6" t="n">
         <v>0</v>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -7757,26 +7757,26 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>191</v>
+        <v>11</v>
       </c>
       <c r="I66" s="4" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02438</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -7817,12 +7817,12 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée Conti</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -7832,11 +7832,11 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>410</v>
+        <v>362</v>
       </c>
       <c r="I67" s="6" t="n">
         <v>0</v>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-15 10:52  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-16 11:53  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>49'677.65</t>
+          <t>48'518.45</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
         <v>0.3869</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.5897</v>
+        <v>0.576</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.468</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 08 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 09 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-15 10:52  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-16 11:53  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2281,11 +2281,11 @@
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -2295,17 +2295,17 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -2314,38 +2314,38 @@
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>24'547.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.0462</v>
+        <v>0</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.2914</v>
+        <v>0</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.1443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>45</v>
+        <v>191</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0</v>
@@ -2399,308 +2399,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01167</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Pétrus</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Château Pétrus</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>104</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01158</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>DRC Corton Charlemagne</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01156</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>DRC Corton Charlemagne</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01155</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Chevalier Montrachet</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Leflaive</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01170</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>DRC Romanée St. Vivant</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>191</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:N11"/>
+  <autoFilter ref="A3:N6"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2715,7 +2415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2737,14 +2437,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 16 Mar 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 17 Mar 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-15 10:52  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-16 11:53  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2942,21 +2642,21 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00871</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2966,107 +2666,107 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>29'483.52</t>
+          <t>13'335.52</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.3155</v>
+        <v>0.3257</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.35</v>
+        <v>0.1583</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3293</v>
+        <v>0.2587</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>13'335.52</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3257</v>
+        <v>0.1278</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1583</v>
+        <v>0.4545</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2587</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -3076,57 +2776,57 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.1224</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.4309</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2585</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -3136,67 +2836,67 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>24'547.24</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1224</v>
+        <v>0.0462</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.4309</v>
+        <v>0.2914</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2458</v>
+        <v>0.1443</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -3206,67 +2906,67 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>130</v>
+        <v>317</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>24'547.24</t>
+          <t>14'921.04</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.0948</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2914</v>
+        <v>0.1771</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1443</v>
+        <v>0.1277</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-26-00963</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -3275,38 +2975,38 @@
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>317</v>
+        <v>74</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>14'921.04</t>
+          <t>12'848.80</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0948</v>
+        <v>0.081</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1771</v>
+        <v>0.1525</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1277</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -3316,17 +3016,17 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -3335,38 +3035,38 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>74</v>
+        <v>487</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>12'848.80</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.081</v>
+        <v>0.0372</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1525</v>
+        <v>0.1716</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1096</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -3376,57 +3076,57 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>487</v>
+        <v>63</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0372</v>
+        <v>0</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1716</v>
+        <v>0</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3436,26 +3136,26 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>0</v>
@@ -3482,11 +3182,11 @@
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -3496,26 +3196,26 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
@@ -3542,7 +3242,7 @@
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
@@ -3602,11 +3302,11 @@
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -3621,7 +3321,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -3631,11 +3331,11 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
@@ -3662,11 +3362,11 @@
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -3676,26 +3376,26 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>0</v>
@@ -3722,11 +3422,11 @@
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -3736,26 +3436,26 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>63</v>
+        <v>191</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
@@ -3780,128 +3480,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-00874</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Château Léoville Las Cases</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01170</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>DRC Romanée St. Vivant</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>191</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:N21"/>
+  <autoFilter ref="A3:N19"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3945,7 +3525,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-15 10:52  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-16 11:53  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4248,17 +3828,17 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>49'677.65</t>
+          <t>48'518.45</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
         <v>0.3869</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.5897</v>
+        <v>0.576</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.468</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -6667,7 +6247,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -6677,26 +6257,26 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="I48" s="4" t="n">
         <v>0</v>
@@ -6727,7 +6307,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -6737,26 +6317,26 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0</v>
@@ -6787,7 +6367,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -6797,26 +6377,26 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>20</v>
+        <v>643</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>0</v>
@@ -6847,7 +6427,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -6857,26 +6437,26 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>643</v>
+        <v>42</v>
       </c>
       <c r="I51" s="6" t="n">
         <v>0</v>
@@ -6907,7 +6487,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02438</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -6917,12 +6497,12 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée Conti</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -6932,11 +6512,11 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>410</v>
+        <v>252</v>
       </c>
       <c r="I52" s="4" t="n">
         <v>0</v>
@@ -6967,7 +6547,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -6977,12 +6557,12 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -6996,7 +6576,7 @@
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>252</v>
+        <v>126</v>
       </c>
       <c r="I53" s="6" t="n">
         <v>0</v>
@@ -7027,7 +6607,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -7037,26 +6617,26 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="I54" s="4" t="n">
         <v>0</v>
@@ -7087,7 +6667,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -7097,12 +6677,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -7112,11 +6692,11 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>28</v>
+        <v>362</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>0</v>
@@ -7147,7 +6727,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -7157,26 +6737,26 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="I56" s="4" t="n">
         <v>0</v>
@@ -7207,7 +6787,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -7217,26 +6797,26 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="I57" s="6" t="n">
         <v>0</v>
@@ -7267,7 +6847,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -7277,26 +6857,26 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>0</v>
@@ -7327,7 +6907,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -7337,26 +6917,26 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>63</v>
+        <v>543</v>
       </c>
       <c r="I59" s="6" t="n">
         <v>0</v>
@@ -7387,7 +6967,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -7397,26 +6977,26 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>0</v>
@@ -7447,7 +7027,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -7457,26 +7037,26 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I61" s="6" t="n">
         <v>0</v>
@@ -7507,7 +7087,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -7517,12 +7097,12 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -7532,11 +7112,11 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>191</v>
+        <v>28</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>0</v>
@@ -7567,7 +7147,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -7577,26 +7157,26 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>543</v>
+        <v>26</v>
       </c>
       <c r="I63" s="6" t="n">
         <v>0</v>
@@ -7627,7 +7207,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -7637,26 +7217,26 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="I64" s="4" t="n">
         <v>0</v>
@@ -7687,7 +7267,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -7697,26 +7277,26 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="I65" s="6" t="n">
         <v>0</v>
@@ -7747,7 +7327,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -7757,26 +7337,26 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>11</v>
+        <v>191</v>
       </c>
       <c r="I66" s="4" t="n">
         <v>0</v>
@@ -7807,7 +7387,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-25-02438</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -7817,12 +7397,12 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Romanée Conti</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -7832,11 +7412,11 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>362</v>
+        <v>410</v>
       </c>
       <c r="I67" s="6" t="n">
         <v>0</v>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-16 11:53  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-20 08:41  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -784,58 +784,58 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02970</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita Gravascal</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>512</v>
+        <v>26</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>11.54%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>48'518.45</t>
+          <t>15'557.61</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3869</v>
+        <v>0.6923</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.576</v>
+        <v>0.1847</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4625</v>
+        <v>0.4893</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -844,58 +844,58 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01175</t>
+          <t>CM-25-02970</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Finca Piedra Infinita Gravascal</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>37</v>
+        <v>512</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>6.45%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>15'275.79</t>
+          <t>48'518.45</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.6485</v>
+        <v>0.3869</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1813</v>
+        <v>0.576</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4616</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -904,58 +904,58 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02472</t>
+          <t>CM-26-01175</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Clos de Vougeot</t>
+          <t>Côte Rôtie La Mouline</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leroy</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>10.81%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>84'240.00</t>
+          <t>15'275.79</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0516</v>
+        <v>0.6485</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>1</v>
+        <v>0.1813</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.431</v>
+        <v>0.4616</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -964,7 +964,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00771</t>
+          <t>CM-25-02472</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -974,48 +974,48 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Clos de Vougeot</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Domaine Leroy</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>10'123.30</t>
+          <t>84'240.00</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.5453</v>
+        <v>0.0516</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1202</v>
+        <v>1</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3753</v>
+        <v>0.431</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00293</t>
+          <t>CM-26-00771</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1034,48 +1034,48 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Latour (Ex-Château)</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>51'964.65</t>
+          <t>10'123.30</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1938</v>
+        <v>0.5453</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.6169</v>
+        <v>0.1202</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.363</v>
+        <v>0.3753</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00724</t>
+          <t>CM-26-00293</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1094,48 +1094,48 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Cheval Blanc</t>
+          <t>Latour (Ex-Château)</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Cheval Blanc</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>53'840.62</t>
+          <t>51'964.65</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1698</v>
+        <v>0.1938</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6391</v>
+        <v>0.6169</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3575</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00871</t>
+          <t>CM-26-00724</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1154,48 +1154,48 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Cheval Blanc</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Château Cheval Blanc</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>29'483.52</t>
+          <t>53'840.62</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.1698</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.35</v>
+        <v>0.6391</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3293</v>
+        <v>0.3575</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1204,58 +1204,58 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02625</t>
+          <t>CM-26-00871</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Rumbo al Norte</t>
+          <t>Chambertin Très Vieilles Vignes</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Bodega Comando G</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>170</v>
+        <v>38</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>37'837.84</t>
+          <t>29'483.52</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2472</v>
+        <v>0.3155</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4492</v>
+        <v>0.35</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.328</v>
+        <v>0.3293</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-25-02625</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1274,48 +1274,48 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Rumbo al Norte</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Bodega Comando G</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>3'508.63</t>
+          <t>37'837.84</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.4895</v>
+        <v>0.2472</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0417</v>
+        <v>0.4492</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.3104</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1324,58 +1324,58 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>3'508.63</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4895</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1902</v>
+        <v>0.0417</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3057</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1384,58 +1384,58 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>20'953.57</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.2771</v>
+        <v>0.3827</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.2487</v>
+        <v>0.1902</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2657</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1444,58 +1444,58 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>92</v>
+        <v>195</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>13'335.52</t>
+          <t>20'974.64</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3257</v>
+        <v>0.2771</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1583</v>
+        <v>0.249</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2587</v>
+        <v>0.2659</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1504,58 +1504,58 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>47</v>
+        <v>181</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>25'538.66</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.2322</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.4545</v>
+        <v>0.3032</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2585</v>
+        <v>0.2606</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1564,58 +1564,58 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>13'335.52</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1224</v>
+        <v>0.3257</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.4309</v>
+        <v>0.1583</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.2458</v>
+        <v>0.2587</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1624,58 +1624,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.1278</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0683</v>
+        <v>0.4545</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2166</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1694,48 +1694,48 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.2609</v>
+        <v>0.1224</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.1399</v>
+        <v>0.4309</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2125</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1744,58 +1744,58 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2501</v>
+        <v>0.3155</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1529</v>
+        <v>0.0683</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2112</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00553</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1824,38 +1824,38 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>37'269.73</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.036</v>
+        <v>0.2609</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4424</v>
+        <v>0.1399</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1986</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1864,58 +1864,58 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03240</t>
+          <t>CM-26-00774</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>La Grande Rue</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Domaine Francois Lamarche</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>245</v>
+        <v>24</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>12'603.94</t>
+          <t>12'881.25</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.2202</v>
+        <v>0.2501</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1496</v>
+        <v>0.1529</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.192</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00844</t>
+          <t>CM-26-00553</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1934,48 +1934,48 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>10'599.18</t>
+          <t>37'269.73</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.222</v>
+        <v>0.036</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1258</v>
+        <v>0.4424</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1835</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1984,58 +1984,58 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02431</t>
+          <t>CM-25-03240</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Château Larcis Ducasse</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>156</v>
+        <v>245</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>11'961.88</t>
+          <t>12'603.94</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1926</v>
+        <v>0.2202</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.142</v>
+        <v>0.1496</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1724</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00730</t>
+          <t>CM-26-00844</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2054,48 +2054,48 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>La Violette</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château La Violette</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>17'433.26</t>
+          <t>10'599.18</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1266</v>
+        <v>0.222</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.2069</v>
+        <v>0.1258</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1587</v>
+        <v>0.1835</v>
       </c>
     </row>
   </sheetData>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 09 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 13 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-16 11:53  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-20 08:41  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01175</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -2235,168 +2235,168 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>11.54%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>15'275.79</t>
+          <t>15'557.61</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.6485</v>
+        <v>0.6923</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.1813</v>
+        <v>0.1847</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.4616</v>
+        <v>0.4893</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01219</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>104</v>
+        <v>221</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>16'298.11</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0</v>
+        <v>0.1626</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0</v>
+        <v>0.1935</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3'090.00</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0</v>
+        <v>0.0336</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0</v>
+        <v>0.0367</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0</v>
+        <v>0.0348</v>
       </c>
     </row>
   </sheetData>
@@ -2415,7 +2415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2437,14 +2437,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 17 Mar 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 21 Mar 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-16 11:53  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-20 08:41  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2582,11 +2582,11 @@
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01175</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -2596,108 +2596,108 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>11.54%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>15'275.79</t>
+          <t>15'557.61</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.6485</v>
+        <v>0.6923</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.1813</v>
+        <v>0.1847</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4616</v>
+        <v>0.4893</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-01175</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>Côte Rôtie La Mouline</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>10.81%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>13'335.52</t>
+          <t>15'275.79</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.3257</v>
+        <v>0.6485</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1583</v>
+        <v>0.1813</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2587</v>
+        <v>0.4616</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2706,58 +2706,58 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>47</v>
+        <v>181</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>25'538.66</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.2322</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.4545</v>
+        <v>0.3032</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2585</v>
+        <v>0.2606</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2766,67 +2766,67 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>13'335.52</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1224</v>
+        <v>0.3257</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4309</v>
+        <v>0.1583</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2458</v>
+        <v>0.2587</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -2836,57 +2836,57 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>24'547.24</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0462</v>
+        <v>0.1224</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2914</v>
+        <v>0.4309</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.1443</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-26-01219</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>317</v>
+        <v>221</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>14'921.04</t>
+          <t>16'298.11</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0948</v>
+        <v>0.1626</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1771</v>
+        <v>0.1935</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1277</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -2956,57 +2956,57 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>12'848.80</t>
+          <t>24'547.24</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.081</v>
+        <v>0.0462</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1525</v>
+        <v>0.2914</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1096</v>
+        <v>0.1443</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-26-00963</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -3016,17 +3016,17 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -3035,98 +3035,98 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>487</v>
+        <v>74</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>12'848.80</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.081</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1716</v>
+        <v>0.1525</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.091</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>63</v>
+        <v>317</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>12'519.72</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0</v>
+        <v>0.0756</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0</v>
+        <v>0.1486</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3136,113 +3136,113 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>52</v>
+        <v>487</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0</v>
+        <v>0.1716</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>28</v>
+        <v>179</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3'090.00</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0</v>
+        <v>0.0336</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0</v>
+        <v>0.0367</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0</v>
+        <v>0.0348</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
@@ -3302,11 +3302,11 @@
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -3316,26 +3316,26 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
@@ -3362,11 +3362,11 @@
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -3376,26 +3376,26 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>0</v>
@@ -3422,66 +3422,246 @@
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
+          <t>CM-26-01156</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>DRC Corton Charlemagne</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01159</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>DRC Corton Charlemagne</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01167</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Pétrus</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Château Pétrus</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
           <t>CM-26-01170</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>🟣</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="H19" s="6" t="n">
-        <v>191</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="H22" s="4" t="n">
+        <v>313</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="6" t="n">
+      <c r="L22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N19"/>
+  <autoFilter ref="A3:N22"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3496,7 +3676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3525,7 +3705,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-16 11:53  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-20 08:41  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -3787,58 +3967,58 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02970</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita Gravascal</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>512</v>
+        <v>26</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>11.54%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>48'518.45</t>
+          <t>15'557.61</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3869</v>
+        <v>0.6923</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.576</v>
+        <v>0.1847</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4625</v>
+        <v>0.4893</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -3847,58 +4027,58 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01175</t>
+          <t>CM-25-02970</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Finca Piedra Infinita Gravascal</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>37</v>
+        <v>512</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>6.45%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>15'275.79</t>
+          <t>48'518.45</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.6485</v>
+        <v>0.3869</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1813</v>
+        <v>0.576</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4616</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -3907,58 +4087,58 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02472</t>
+          <t>CM-26-01175</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Clos de Vougeot</t>
+          <t>Côte Rôtie La Mouline</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leroy</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>10.81%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>84'240.00</t>
+          <t>15'275.79</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0516</v>
+        <v>0.6485</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>1</v>
+        <v>0.1813</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.431</v>
+        <v>0.4616</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -3967,7 +4147,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00771</t>
+          <t>CM-25-02472</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -3977,48 +4157,48 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Clos de Vougeot</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Domaine Leroy</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>10'123.30</t>
+          <t>84'240.00</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.5453</v>
+        <v>0.0516</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1202</v>
+        <v>1</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3753</v>
+        <v>0.431</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -4027,7 +4207,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00293</t>
+          <t>CM-26-00771</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -4037,48 +4217,48 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Latour (Ex-Château)</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>51'964.65</t>
+          <t>10'123.30</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1938</v>
+        <v>0.5453</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.6169</v>
+        <v>0.1202</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.363</v>
+        <v>0.3753</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -4087,7 +4267,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00724</t>
+          <t>CM-26-00293</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -4097,48 +4277,48 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Cheval Blanc</t>
+          <t>Latour (Ex-Château)</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Cheval Blanc</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>53'840.62</t>
+          <t>51'964.65</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1698</v>
+        <v>0.1938</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6391</v>
+        <v>0.6169</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3575</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -4147,7 +4327,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00871</t>
+          <t>CM-26-00724</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -4157,48 +4337,48 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Cheval Blanc</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Château Cheval Blanc</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>29'483.52</t>
+          <t>53'840.62</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.1698</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.35</v>
+        <v>0.6391</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3293</v>
+        <v>0.3575</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -4207,58 +4387,58 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02625</t>
+          <t>CM-26-00871</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Rumbo al Norte</t>
+          <t>Chambertin Très Vieilles Vignes</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Bodega Comando G</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>170</v>
+        <v>38</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>37'837.84</t>
+          <t>29'483.52</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2472</v>
+        <v>0.3155</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4492</v>
+        <v>0.35</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.328</v>
+        <v>0.3293</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -4267,7 +4447,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-25-02625</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -4277,48 +4457,48 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Rumbo al Norte</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Bodega Comando G</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>3'508.63</t>
+          <t>37'837.84</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.4895</v>
+        <v>0.2472</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0417</v>
+        <v>0.4492</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.3104</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -4327,58 +4507,58 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>3'508.63</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4895</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1902</v>
+        <v>0.0417</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3057</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -4387,58 +4567,58 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>20'953.57</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.2771</v>
+        <v>0.3827</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.2487</v>
+        <v>0.1902</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2657</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -4447,58 +4627,58 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>92</v>
+        <v>195</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>13'335.52</t>
+          <t>20'974.64</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3257</v>
+        <v>0.2771</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1583</v>
+        <v>0.249</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2587</v>
+        <v>0.2659</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -4507,58 +4687,58 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>47</v>
+        <v>181</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>25'538.66</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.2322</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.4545</v>
+        <v>0.3032</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2585</v>
+        <v>0.2606</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4567,58 +4747,58 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>13'335.52</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1224</v>
+        <v>0.3257</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.4309</v>
+        <v>0.1583</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.2458</v>
+        <v>0.2587</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4627,58 +4807,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.1278</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0683</v>
+        <v>0.4545</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2166</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4687,7 +4867,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -4697,48 +4877,48 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.2609</v>
+        <v>0.1224</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.1399</v>
+        <v>0.4309</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2125</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4747,58 +4927,58 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2501</v>
+        <v>0.3155</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1529</v>
+        <v>0.0683</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2112</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4807,7 +4987,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00553</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -4817,7 +4997,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -4827,38 +5007,38 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>37'269.73</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.036</v>
+        <v>0.2609</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4424</v>
+        <v>0.1399</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1986</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4867,58 +5047,58 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03240</t>
+          <t>CM-26-00774</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>La Grande Rue</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Domaine Francois Lamarche</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>245</v>
+        <v>24</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>12'603.94</t>
+          <t>12'881.25</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.2202</v>
+        <v>0.2501</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1496</v>
+        <v>0.1529</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.192</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -4927,7 +5107,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00844</t>
+          <t>CM-26-00553</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -4937,48 +5117,48 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>10'599.18</t>
+          <t>37'269.73</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.222</v>
+        <v>0.036</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1258</v>
+        <v>0.4424</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1835</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -4987,58 +5167,58 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02431</t>
+          <t>CM-25-03240</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Château Larcis Ducasse</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>156</v>
+        <v>245</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>11'961.88</t>
+          <t>12'603.94</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1926</v>
+        <v>0.2202</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.142</v>
+        <v>0.1496</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1724</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5047,7 +5227,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00730</t>
+          <t>CM-26-00844</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -5057,48 +5237,48 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>La Violette</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château La Violette</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>17'433.26</t>
+          <t>10'599.18</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1266</v>
+        <v>0.222</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.2069</v>
+        <v>0.1258</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1587</v>
+        <v>0.1835</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5107,58 +5287,58 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02972</t>
+          <t>CM-26-01219</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>73</v>
+        <v>221</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>1'257.15</t>
+          <t>16'298.11</t>
         </is>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.2466</v>
+        <v>0.1626</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.0149</v>
+        <v>0.1935</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1539</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5167,58 +5347,58 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02689</t>
+          <t>CM-25-02431</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges la Perrière</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Domaine Gouges Henri</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="I30" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>3'300.53</t>
+          <t>11'961.88</t>
         </is>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.222</v>
+        <v>0.1926</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.0392</v>
+        <v>0.142</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1489</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -5227,7 +5407,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-26-00730</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -5237,48 +5417,48 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>La Violette</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château La Violette</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>24'547.24</t>
+          <t>17'433.26</t>
         </is>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.0462</v>
+        <v>0.1266</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.2914</v>
+        <v>0.2069</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.1443</v>
+        <v>0.1587</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -5287,58 +5467,58 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00594</t>
+          <t>CM-25-02972</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mordorée</t>
+          <t>Finca Piedra Infinita</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Maison M. Chapoutier</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>12'780.81</t>
+          <t>1'257.15</t>
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1362</v>
+        <v>0.2466</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.1517</v>
+        <v>0.0149</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1424</v>
+        <v>0.1539</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -5347,58 +5527,58 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02637</t>
+          <t>CM-25-02689</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Hommage à Jacques Perrin</t>
+          <t>Nuits Saint Georges la Perrière</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Château de Beaucastel</t>
+          <t>Domaine Gouges Henri</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>1'587.81</t>
+          <t>3'300.53</t>
         </is>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.2142</v>
+        <v>0.222</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.0188</v>
+        <v>0.0392</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.136</v>
+        <v>0.1489</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -5407,17 +5587,17 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -5427,38 +5607,38 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>317</v>
+        <v>130</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>14'921.04</t>
+          <t>24'547.24</t>
         </is>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.0948</v>
+        <v>0.0462</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1771</v>
+        <v>0.2914</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1277</v>
+        <v>0.1443</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -5467,7 +5647,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02474</t>
+          <t>CM-26-00594</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -5477,48 +5657,48 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Mazoyères-Chambertin</t>
+          <t>Côte Rôtie La Mordorée</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Arnaud Mortet</t>
+          <t>Maison M. Chapoutier</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>150</v>
+        <v>88</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>9'311.67</t>
+          <t>12'780.81</t>
         </is>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.12</v>
+        <v>0.1362</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1105</v>
+        <v>0.1517</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1162</v>
+        <v>0.1424</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -5527,58 +5707,58 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-25-02637</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Hommage à Jacques Perrin</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château de Beaucastel</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="I36" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>12'848.80</t>
+          <t>1'587.81</t>
         </is>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.081</v>
+        <v>0.2142</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.1525</v>
+        <v>0.0188</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.1096</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -5587,58 +5767,58 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00779</t>
+          <t>CM-25-02474</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Mazoyères-Chambertin</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Arnaud Mortet</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>10'707.33</t>
+          <t>9'311.67</t>
         </is>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.0936</v>
+        <v>0.12</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1271</v>
+        <v>0.1105</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.107</v>
+        <v>0.1162</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -5647,58 +5827,58 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02628</t>
+          <t>CM-26-00963</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Grillet Blanc</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Château Grillet</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>6'957.56</t>
+          <t>12'848.80</t>
         </is>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.1218</v>
+        <v>0.081</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.1525</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.1061</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -5707,7 +5887,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00772</t>
+          <t>CM-26-00779</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -5717,48 +5897,48 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>198</v>
+        <v>64</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>10'109.38</t>
+          <t>10'707.33</t>
         </is>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.0912</v>
+        <v>0.0936</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.12</v>
+        <v>0.1271</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1027</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -5767,58 +5947,58 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-25-02628</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Grillet Blanc</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Château Grillet</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>487</v>
+        <v>197</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>6'957.56</t>
         </is>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.1218</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.1716</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.091</v>
+        <v>0.1061</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -5827,58 +6007,58 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00658</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Assortment de Grands Crus (12 bottles)</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Domaine Ponsot</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>68</v>
+        <v>317</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>7'018.00</t>
+          <t>12'519.72</t>
         </is>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.0756</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.0833</v>
+        <v>0.1486</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.0862</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -5887,58 +6067,58 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03004</t>
+          <t>CM-26-00772</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>476</v>
+        <v>198</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>10'547.81</t>
+          <t>10'109.38</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.0504</v>
+        <v>0.0912</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.1252</v>
+        <v>0.12</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.0803</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -5947,7 +6127,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02535</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -5957,48 +6137,48 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Meursault Clos des Bouchers</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Domaine Jean Marc Roulot</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>268</v>
+        <v>487</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>10'885.80</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.045</v>
+        <v>0.0372</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.1292</v>
+        <v>0.1716</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -6007,58 +6187,58 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00483</t>
+          <t>CM-26-00658</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Pie Franco</t>
+          <t>Assortment de Grands Crus (12 bottles)</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Bodegas Casa Castillo</t>
+          <t>Domaine Ponsot</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="I44" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>690.03</t>
+          <t>7'018.00</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.1134</v>
+        <v>0.0882</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0833</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.0713</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -6067,58 +6247,58 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02609</t>
+          <t>CM-25-03004</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Clos de la Roche</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Domaine Georges Lignier</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>233</v>
+        <v>476</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>5'003.90</t>
+          <t>10'547.81</t>
         </is>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.0774</v>
+        <v>0.0504</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.0594</v>
+        <v>0.1252</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.0702</v>
+        <v>0.0803</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -6127,58 +6307,58 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00851</t>
+          <t>CM-25-02535</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Meursault Clos des Bouchers</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Jean Marc Roulot</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>4'218.04</t>
+          <t>10'885.80</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.0222</v>
+        <v>0.045</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.0501</v>
+        <v>0.1292</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.0334</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -6187,7 +6367,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02656</t>
+          <t>CM-26-00483</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -6197,48 +6377,48 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
+          <t>Pie Franco</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Weingut Markus Molitor</t>
+          <t>Bodegas Casa Castillo</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>324</v>
+        <v>53</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>1'865.44</t>
+          <t>690.03</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.1134</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.0221</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.0312</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -6247,58 +6427,58 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-25-02609</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Clos de la Roche</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Domaine Georges Lignier</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>11</v>
+        <v>233</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5'003.90</t>
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0</v>
+        <v>0.0774</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0</v>
+        <v>0.0594</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -6307,58 +6487,58 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3'090.00</t>
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0</v>
+        <v>0.0336</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0</v>
+        <v>0.0367</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0</v>
+        <v>0.0348</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -6367,58 +6547,58 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-26-00851</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>643</v>
+        <v>271</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4'218.04</t>
         </is>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0</v>
+        <v>0.0222</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0</v>
+        <v>0.0501</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0</v>
+        <v>0.0334</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -6427,58 +6607,58 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-25-02656</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Weingut Markus Molitor</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>42</v>
+        <v>324</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1'865.44</t>
         </is>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0</v>
+        <v>0.0221</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -6547,7 +6727,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -6557,12 +6737,12 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -6572,11 +6752,11 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>126</v>
+        <v>362</v>
       </c>
       <c r="I53" s="6" t="n">
         <v>0</v>
@@ -6667,7 +6847,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -6677,12 +6857,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -6692,11 +6872,11 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>362</v>
+        <v>126</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>0</v>
@@ -6727,7 +6907,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -6737,26 +6917,26 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="I56" s="4" t="n">
         <v>0</v>
@@ -6787,7 +6967,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -6797,26 +6977,26 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I57" s="6" t="n">
         <v>0</v>
@@ -6847,7 +7027,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -6857,26 +7037,26 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>92</v>
+        <v>643</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>0</v>
@@ -6907,7 +7087,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -6917,26 +7097,26 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>543</v>
+        <v>11</v>
       </c>
       <c r="I59" s="6" t="n">
         <v>0</v>
@@ -6967,7 +7147,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -6977,26 +7157,26 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>0</v>
@@ -7027,7 +7207,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -7037,17 +7217,17 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
@@ -7056,7 +7236,7 @@
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="I61" s="6" t="n">
         <v>0</v>
@@ -7087,7 +7267,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -7097,26 +7277,26 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>0</v>
@@ -7147,7 +7327,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -7157,26 +7337,26 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>26</v>
+        <v>543</v>
       </c>
       <c r="I63" s="6" t="n">
         <v>0</v>
@@ -7207,7 +7387,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -7217,26 +7397,26 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I64" s="4" t="n">
         <v>0</v>
@@ -7267,7 +7447,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -7277,26 +7457,26 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="I65" s="6" t="n">
         <v>0</v>
@@ -7327,7 +7507,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -7337,26 +7517,26 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>191</v>
+        <v>103</v>
       </c>
       <c r="I66" s="4" t="n">
         <v>0</v>
@@ -7387,62 +7567,302 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
+          <t>CM-26-01156</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>DRC Corton Charlemagne</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01159</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>DRC Corton Charlemagne</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01167</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Pétrus</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Château Pétrus</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="I69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01170</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>DRC Romanée St. Vivant</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>313</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
           <t>CM-25-02438</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>🟣</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>DRC Romanée Conti</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="G71" s="6" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="H67" s="6" t="n">
+      <c r="H71" s="6" t="n">
         <v>410</v>
       </c>
-      <c r="I67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="6" t="inlineStr">
+      <c r="I71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K67" s="6" t="inlineStr">
+      <c r="K71" s="6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" s="6" t="n">
+      <c r="L71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="6" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N67"/>
+  <autoFilter ref="A3:N71"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-20 08:41  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-22 08:47  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -705,17 +705,17 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>5'818.62</t>
+          <t>5'831.78</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0692</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6276</v>
+        <v>0.6277</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -784,58 +784,58 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-25-02970</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Finca Piedra Infinita Gravascal</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>26</v>
+        <v>512</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>11.54%</t>
+          <t>6.45%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>15'557.61</t>
+          <t>48'551.95</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.6923</v>
+        <v>0.3869</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1847</v>
+        <v>0.5764</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4893</v>
+        <v>0.4627</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -844,58 +844,58 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02970</t>
+          <t>CM-26-01175</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita Gravascal</t>
+          <t>Côte Rôtie La Mouline</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>512</v>
+        <v>37</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>10.81%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>48'518.45</t>
+          <t>15'275.79</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3869</v>
+        <v>0.6485</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.576</v>
+        <v>0.1813</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4625</v>
+        <v>0.4616</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -904,58 +904,58 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01175</t>
+          <t>CM-25-02472</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Clos de Vougeot</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine Leroy</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>15'275.79</t>
+          <t>84'240.00</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.6485</v>
+        <v>0.0516</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1813</v>
+        <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4616</v>
+        <v>0.431</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -964,7 +964,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02472</t>
+          <t>CM-26-00771</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -974,48 +974,48 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Clos de Vougeot</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leroy</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>84'240.00</t>
+          <t>10'123.30</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0516</v>
+        <v>0.5453</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1</v>
+        <v>0.1202</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.431</v>
+        <v>0.3753</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00771</t>
+          <t>CM-26-00293</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1034,48 +1034,48 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Latour (Ex-Château)</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>10'123.30</t>
+          <t>51'964.65</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.5453</v>
+        <v>0.1938</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1202</v>
+        <v>0.6169</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.3753</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00293</t>
+          <t>CM-26-00724</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1094,48 +1094,48 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Latour (Ex-Château)</t>
+          <t>Cheval Blanc</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château Cheval Blanc</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>51'964.65</t>
+          <t>53'840.62</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1938</v>
+        <v>0.1698</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6169</v>
+        <v>0.6391</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.363</v>
+        <v>0.3575</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1144,58 +1144,58 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00724</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Cheval Blanc</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Cheval Blanc</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>106</v>
+        <v>181</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>4.97%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>53'840.62</t>
+          <t>32'321.12</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1698</v>
+        <v>0.2981</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.6391</v>
+        <v>0.3837</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3575</v>
+        <v>0.3323</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1334,48 +1334,48 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>3'508.63</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.4895</v>
+        <v>0.4613</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.1263</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3104</v>
+        <v>0.3273</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1384,58 +1384,58 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>3'508.63</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.3827</v>
+        <v>0.4895</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1902</v>
+        <v>0.0417</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3057</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1444,58 +1444,58 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>20'974.64</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2771</v>
+        <v>0.3827</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.249</v>
+        <v>0.1902</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2659</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>25'538.66</t>
+          <t>20'974.64</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.2322</v>
+        <v>0.2771</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.3032</v>
+        <v>0.249</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2606</v>
+        <v>0.2659</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 13 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 15 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-20 08:41  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-22 08:47  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
@@ -2257,26 +2257,26 @@
         <v>26</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>11.54%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>15'557.61</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.6923</v>
+        <v>0.4613</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.1847</v>
+        <v>0.1263</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.4893</v>
+        <v>0.3273</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -2326,22 +2326,22 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>16'298.11</t>
+          <t>16'099.11</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
         <v>0.1626</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.1935</v>
+        <v>0.1911</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -2377,30 +2377,330 @@
         <v>179</v>
       </c>
       <c r="I6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2.79%</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>13'289.90</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.1674</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0.1636</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01249</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Pape Clément Blanc</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Château Pape Clément</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>2.08%</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>5'760.55</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>0.1022</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01262</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>🩷</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Auxey-Duresses Les Hautés</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Pierre Vincent</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>0.56%</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>3'090.00</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0.0336</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0.0367</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0.0348</v>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2.08%</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>458.10</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0.077</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01265</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Meursault Crotots</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Pierre Vincent</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01266</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Puligny Montrachet</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Pierre Vincent</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01268</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>🩷</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Pierre Vincent</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N6"/>
+  <autoFilter ref="A3:N11"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2415,7 +2715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2437,14 +2737,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 21 Mar 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 23 Mar 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-20 08:41  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-22 08:47  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2567,86 +2867,86 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>5'818.62</t>
+          <t>5'831.78</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0692</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.6276</v>
+        <v>0.6277</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01175</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>🟨</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Côte Rôtie La Mouline</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Guigal</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="I5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01241</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Cabernet Sauvignon</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Eisele Vineyard</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>11.54%</t>
+          <t>10.81%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>15'557.61</t>
+          <t>15'275.79</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.6923</v>
+        <v>0.6485</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.1847</v>
+        <v>0.1813</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4893</v>
+        <v>0.4616</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01175</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2656,7 +2956,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2675,38 +2975,38 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>37</v>
+        <v>181</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>4.97%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>15'275.79</t>
+          <t>32'321.12</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.6485</v>
+        <v>0.2981</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1813</v>
+        <v>0.3837</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.4616</v>
+        <v>0.3323</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -2716,48 +3016,48 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>181</v>
+        <v>26</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>25'538.66</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2322</v>
+        <v>0.4613</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3032</v>
+        <v>0.1263</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2606</v>
+        <v>0.3273</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2927,86 +3227,86 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>16'298.11</t>
+          <t>16'099.11</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
         <v>0.1626</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1935</v>
+        <v>0.1911</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>24'547.24</t>
+          <t>13'289.90</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0462</v>
+        <v>0.1674</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2914</v>
+        <v>0.1578</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1443</v>
+        <v>0.1636</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -3016,117 +3316,117 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>12'848.80</t>
+          <t>24'547.24</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.081</v>
+        <v>0.0462</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1525</v>
+        <v>0.2914</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1096</v>
+        <v>0.1443</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>12'519.72</t>
+          <t>22'583.46</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0756</v>
+        <v>0.0192</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1486</v>
+        <v>0.2681</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1048</v>
+        <v>0.1188</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-26-00963</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3136,17 +3436,17 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -3155,38 +3455,38 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>487</v>
+        <v>74</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>12'848.80</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.081</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1716</v>
+        <v>0.1525</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.091</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -3196,57 +3496,57 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>179</v>
+        <v>317</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>3'090.00</t>
+          <t>12'552.76</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0336</v>
+        <v>0.0756</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0367</v>
+        <v>0.149</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0348</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3256,57 +3556,57 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0</v>
+        <v>0.1248</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0</v>
+        <v>0.0684</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -3316,117 +3616,117 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>63</v>
+        <v>487</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0</v>
+        <v>0.1716</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>458.10</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0</v>
+        <v>0.1248</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0</v>
+        <v>0.0054</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -3436,26 +3736,26 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
@@ -3486,7 +3786,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3496,26 +3796,26 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
@@ -3546,7 +3846,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -3556,26 +3856,26 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
@@ -3606,7 +3906,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -3616,12 +3916,12 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -3631,37 +3931,337 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01158</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>DRC Corton Charlemagne</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01159</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>DRC Corton Charlemagne</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="H22" s="4" t="n">
-        <v>313</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="H24" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="4" t="n">
+      <c r="L24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01265</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Meursault Crotots</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Pierre Vincent</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01266</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Puligny Montrachet</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Pierre Vincent</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01268</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>🩷</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Pierre Vincent</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="6" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N22"/>
+  <autoFilter ref="A3:N27"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3676,7 +4276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3705,7 +4305,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-20 08:41  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-22 08:47  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -3888,17 +4488,17 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>5'818.62</t>
+          <t>5'831.78</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0692</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6276</v>
+        <v>0.6277</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -3967,58 +4567,58 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-25-02970</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Finca Piedra Infinita Gravascal</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>26</v>
+        <v>512</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>11.54%</t>
+          <t>6.45%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>15'557.61</t>
+          <t>48'551.95</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.6923</v>
+        <v>0.3869</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1847</v>
+        <v>0.5764</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4893</v>
+        <v>0.4627</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -4027,58 +4627,58 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02970</t>
+          <t>CM-26-01175</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita Gravascal</t>
+          <t>Côte Rôtie La Mouline</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>512</v>
+        <v>37</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>10.81%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>48'518.45</t>
+          <t>15'275.79</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3869</v>
+        <v>0.6485</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.576</v>
+        <v>0.1813</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4625</v>
+        <v>0.4616</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -4087,58 +4687,58 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01175</t>
+          <t>CM-25-02472</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Clos de Vougeot</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine Leroy</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>15'275.79</t>
+          <t>84'240.00</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.6485</v>
+        <v>0.0516</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1813</v>
+        <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4616</v>
+        <v>0.431</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -4147,7 +4747,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02472</t>
+          <t>CM-26-00771</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -4157,48 +4757,48 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Clos de Vougeot</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leroy</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>84'240.00</t>
+          <t>10'123.30</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0516</v>
+        <v>0.5453</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1</v>
+        <v>0.1202</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.431</v>
+        <v>0.3753</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -4207,7 +4807,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00771</t>
+          <t>CM-26-00293</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -4217,48 +4817,48 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Latour (Ex-Château)</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>10'123.30</t>
+          <t>51'964.65</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.5453</v>
+        <v>0.1938</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1202</v>
+        <v>0.6169</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.3753</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -4267,7 +4867,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00293</t>
+          <t>CM-26-00724</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -4277,48 +4877,48 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Latour (Ex-Château)</t>
+          <t>Cheval Blanc</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château Cheval Blanc</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>51'964.65</t>
+          <t>53'840.62</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1938</v>
+        <v>0.1698</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6169</v>
+        <v>0.6391</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.363</v>
+        <v>0.3575</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -4327,58 +4927,58 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00724</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Cheval Blanc</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Cheval Blanc</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>106</v>
+        <v>181</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>4.97%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>53'840.62</t>
+          <t>32'321.12</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1698</v>
+        <v>0.2981</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.6391</v>
+        <v>0.3837</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3575</v>
+        <v>0.3323</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -4507,7 +5107,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4517,48 +5117,48 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>3'508.63</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.4895</v>
+        <v>0.4613</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.1263</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3104</v>
+        <v>0.3273</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -4567,58 +5167,58 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>3'508.63</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.3827</v>
+        <v>0.4895</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1902</v>
+        <v>0.0417</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3057</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -4627,58 +5227,58 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>20'974.64</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2771</v>
+        <v>0.3827</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.249</v>
+        <v>0.1902</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2659</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -4687,7 +5287,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -4697,48 +5297,48 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>25'538.66</t>
+          <t>20'974.64</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.2322</v>
+        <v>0.2771</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.3032</v>
+        <v>0.249</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2606</v>
+        <v>0.2659</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -5328,17 +5928,17 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>16'298.11</t>
+          <t>16'099.11</t>
         </is>
       </c>
       <c r="L29" s="6" t="n">
         <v>0.1626</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1935</v>
+        <v>0.1911</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5407,58 +6007,58 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00730</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>La Violette</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Château La Violette</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>17'433.26</t>
+          <t>13'289.90</t>
         </is>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.1266</v>
+        <v>0.1674</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.2069</v>
+        <v>0.1578</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.1587</v>
+        <v>0.1636</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -5467,58 +6067,58 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02972</t>
+          <t>CM-26-00730</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita</t>
+          <t>La Violette</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Château La Violette</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>1'257.15</t>
+          <t>17'433.26</t>
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2466</v>
+        <v>0.1266</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.0149</v>
+        <v>0.2069</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1539</v>
+        <v>0.1587</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -5527,7 +6127,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02689</t>
+          <t>CM-25-02972</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -5537,7 +6137,7 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges la Perrière</t>
+          <t>Finca Piedra Infinita</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -5547,38 +6147,38 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Domaine Gouges Henri</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>3'300.53</t>
+          <t>1'257.15</t>
         </is>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.222</v>
+        <v>0.2466</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.0392</v>
+        <v>0.0149</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1489</v>
+        <v>0.1539</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -5587,58 +6187,58 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-25-02689</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Nuits Saint Georges la Perrière</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Gouges Henri</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>24'547.24</t>
+          <t>3'300.53</t>
         </is>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.222</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.2914</v>
+        <v>0.0392</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1443</v>
+        <v>0.1489</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -5647,58 +6247,58 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00594</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mordorée</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Maison M. Chapoutier</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>12'780.81</t>
+          <t>24'547.24</t>
         </is>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.1362</v>
+        <v>0.0462</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1517</v>
+        <v>0.2914</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1424</v>
+        <v>0.1443</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -5707,7 +6307,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02637</t>
+          <t>CM-26-00594</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -5717,48 +6317,48 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Hommage à Jacques Perrin</t>
+          <t>Côte Rôtie La Mordorée</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Château de Beaucastel</t>
+          <t>Maison M. Chapoutier</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>1'587.81</t>
+          <t>12'780.81</t>
         </is>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.1362</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.0188</v>
+        <v>0.1517</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.136</v>
+        <v>0.1424</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -5767,7 +6367,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02474</t>
+          <t>CM-25-02637</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -5777,48 +6377,48 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Mazoyères-Chambertin</t>
+          <t>Hommage à Jacques Perrin</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Arnaud Mortet</t>
+          <t>Château de Beaucastel</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>150</v>
+        <v>28</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>9'311.67</t>
+          <t>1'587.81</t>
         </is>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.12</v>
+        <v>0.2142</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1105</v>
+        <v>0.0188</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.1162</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -5827,7 +6427,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -5837,48 +6437,48 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>74</v>
+        <v>313</v>
       </c>
       <c r="I38" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>12'848.80</t>
+          <t>22'583.46</t>
         </is>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.081</v>
+        <v>0.0192</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.1525</v>
+        <v>0.2681</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.1096</v>
+        <v>0.1188</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -5887,58 +6487,58 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00779</t>
+          <t>CM-25-02474</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Mazoyères-Chambertin</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Arnaud Mortet</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>10'707.33</t>
+          <t>9'311.67</t>
         </is>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.0936</v>
+        <v>0.12</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1271</v>
+        <v>0.1105</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.107</v>
+        <v>0.1162</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -5947,58 +6547,58 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02628</t>
+          <t>CM-26-00963</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Grillet Blanc</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Château Grillet</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>6'957.56</t>
+          <t>12'848.80</t>
         </is>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.1218</v>
+        <v>0.081</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.1525</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.1061</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -6007,58 +6607,58 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-26-00779</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>317</v>
+        <v>64</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>12'519.72</t>
+          <t>10'707.33</t>
         </is>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.0756</v>
+        <v>0.0936</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1486</v>
+        <v>0.1271</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1048</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -6067,58 +6667,58 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00772</t>
+          <t>CM-25-02628</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Grillet Blanc</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Château Grillet</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>10'109.38</t>
+          <t>6'957.56</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.0912</v>
+        <v>0.1218</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.12</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.1027</v>
+        <v>0.1061</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -6127,27 +6727,27 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -6156,29 +6756,29 @@
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>487</v>
+        <v>317</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>12'552.76</t>
         </is>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0756</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.1716</v>
+        <v>0.149</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.091</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -6187,7 +6787,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00658</t>
+          <t>CM-26-00772</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -6197,48 +6797,48 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Assortment de Grands Crus (12 bottles)</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Domaine Ponsot</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>68</v>
+        <v>198</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>7'018.00</t>
+          <t>10'109.38</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.0882</v>
+        <v>0.0912</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.12</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.0862</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -6247,58 +6847,58 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03004</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>476</v>
+        <v>96</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>10'547.81</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.0504</v>
+        <v>0.1248</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.1252</v>
+        <v>0.0684</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.0803</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -6307,7 +6907,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02535</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -6317,48 +6917,48 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Meursault Clos des Bouchers</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Domaine Jean Marc Roulot</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>268</v>
+        <v>487</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>10'885.80</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.045</v>
+        <v>0.0372</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.1292</v>
+        <v>0.1716</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -6367,58 +6967,58 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00483</t>
+          <t>CM-26-00658</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Pie Franco</t>
+          <t>Assortment de Grands Crus (12 bottles)</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Bodegas Casa Castillo</t>
+          <t>Domaine Ponsot</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>690.03</t>
+          <t>7'018.00</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.1134</v>
+        <v>0.0882</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0833</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.0713</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -6427,58 +7027,58 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02609</t>
+          <t>CM-25-03004</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Clos de la Roche</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Lignier</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>233</v>
+        <v>476</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>5'003.90</t>
+          <t>10'547.81</t>
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.0774</v>
+        <v>0.0504</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.0594</v>
+        <v>0.1252</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.0702</v>
+        <v>0.0803</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -6487,58 +7087,58 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-25-02535</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Meursault Clos des Bouchers</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine Jean Marc Roulot</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>179</v>
+        <v>268</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>3'090.00</t>
+          <t>10'885.80</t>
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.0336</v>
+        <v>0.045</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.0367</v>
+        <v>0.1292</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.0348</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -6547,58 +7147,58 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00851</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>271</v>
+        <v>48</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>4'218.04</t>
+          <t>458.10</t>
         </is>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.0222</v>
+        <v>0.1248</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.0501</v>
+        <v>0.0054</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.0334</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -6607,7 +7207,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02656</t>
+          <t>CM-26-00483</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -6617,48 +7217,48 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
+          <t>Pie Franco</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Weingut Markus Molitor</t>
+          <t>Bodegas Casa Castillo</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>324</v>
+        <v>53</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>1'865.44</t>
+          <t>690.03</t>
         </is>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.1134</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.0221</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.0312</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -6667,58 +7267,58 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-25-02609</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Clos de la Roche</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Georges Lignier</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5'003.90</t>
         </is>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0</v>
+        <v>0.0774</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0</v>
+        <v>0.0594</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -6727,58 +7327,58 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-26-00851</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>362</v>
+        <v>271</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4'218.04</t>
         </is>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0</v>
+        <v>0.0222</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0</v>
+        <v>0.0501</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0</v>
+        <v>0.0334</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -6787,58 +7387,58 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-25-02656</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Weingut Markus Molitor</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>129</v>
+        <v>324</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1'865.44</t>
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0</v>
+        <v>0.0221</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -6907,7 +7507,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -6917,26 +7517,26 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="I56" s="4" t="n">
         <v>0</v>
@@ -6967,7 +7567,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -6982,7 +7582,7 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -6992,11 +7592,11 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>42</v>
+        <v>362</v>
       </c>
       <c r="I57" s="6" t="n">
         <v>0</v>
@@ -7027,7 +7627,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -7037,26 +7637,26 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>643</v>
+        <v>129</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>0</v>
@@ -7087,7 +7687,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -7097,26 +7697,26 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>11</v>
+        <v>643</v>
       </c>
       <c r="I59" s="6" t="n">
         <v>0</v>
@@ -7147,7 +7747,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -7157,26 +7757,26 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>0</v>
@@ -7207,7 +7807,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -7217,12 +7817,12 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -7232,11 +7832,11 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="I61" s="6" t="n">
         <v>0</v>
@@ -7267,7 +7867,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -7277,26 +7877,26 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>0</v>
@@ -7327,7 +7927,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -7337,26 +7937,26 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>543</v>
+        <v>92</v>
       </c>
       <c r="I63" s="6" t="n">
         <v>0</v>
@@ -7387,7 +7987,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -7397,26 +7997,26 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="I64" s="4" t="n">
         <v>0</v>
@@ -7447,7 +8047,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -7457,26 +8057,26 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="I65" s="6" t="n">
         <v>0</v>
@@ -7507,7 +8107,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -7517,26 +8117,26 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>103</v>
+        <v>543</v>
       </c>
       <c r="I66" s="4" t="n">
         <v>0</v>
@@ -7567,7 +8167,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -7577,26 +8177,26 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="I67" s="6" t="n">
         <v>0</v>
@@ -7627,7 +8227,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -7637,26 +8237,26 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="I68" s="4" t="n">
         <v>0</v>
@@ -7687,7 +8287,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -7697,26 +8297,26 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I69" s="6" t="n">
         <v>0</v>
@@ -7747,7 +8347,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -7757,12 +8357,12 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -7772,11 +8372,11 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>313</v>
+        <v>28</v>
       </c>
       <c r="I70" s="4" t="n">
         <v>0</v>
@@ -7807,62 +8407,362 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
+          <t>CM-26-01158</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>DRC Corton Charlemagne</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="I71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01159</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>DRC Corton Charlemagne</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01265</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Meursault Crotots</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Pierre Vincent</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01266</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Puligny Montrachet</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Pierre Vincent</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01268</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>🩷</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Pierre Vincent</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="I75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
           <t>CM-25-02438</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>🟣</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>DRC Romanée Conti</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
-      <c r="G71" s="6" t="inlineStr">
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="H71" s="6" t="n">
+      <c r="H76" s="4" t="n">
         <v>410</v>
       </c>
-      <c r="I71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="6" t="inlineStr">
+      <c r="I76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K71" s="6" t="inlineStr">
+      <c r="K76" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" s="6" t="n">
+      <c r="L76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N71"/>
+  <autoFilter ref="A3:N76"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-22 08:47  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-27 09:11  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -1144,58 +1144,58 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-00871</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Chambertin Très Vieilles Vignes</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>4.97%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>32'321.12</t>
+          <t>29'483.52</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2981</v>
+        <v>0.3155</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.3837</v>
+        <v>0.35</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3323</v>
+        <v>0.3293</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1204,58 +1204,58 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00871</t>
+          <t>CM-25-02625</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Rumbo al Norte</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Bodega Comando G</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>38</v>
+        <v>170</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>29'483.52</t>
+          <t>37'837.84</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3155</v>
+        <v>0.2472</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.35</v>
+        <v>0.4492</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3293</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02625</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1274,48 +1274,48 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Rumbo al Norte</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Bodega Comando G</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>37'837.84</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.2472</v>
+        <v>0.4613</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.4492</v>
+        <v>0.1263</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.328</v>
+        <v>0.3273</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1334,48 +1334,48 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>10'637.89</t>
+          <t>3'508.63</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.4613</v>
+        <v>0.4895</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1263</v>
+        <v>0.0417</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3273</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1384,58 +1384,58 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>3'508.63</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.4895</v>
+        <v>0.3827</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0417</v>
+        <v>0.1902</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3104</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1444,58 +1444,58 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>47</v>
+        <v>181</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>4.42%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>28'181.48</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.2651</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1902</v>
+        <v>0.3345</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3057</v>
+        <v>0.2929</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1744,58 +1744,58 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>4.44%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>12'711.50</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.2663</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0683</v>
+        <v>0.1509</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2166</v>
+        <v>0.2201</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1804,58 +1804,58 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2609</v>
+        <v>0.3155</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1399</v>
+        <v>0.0683</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2125</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1864,58 +1864,58 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.2501</v>
+        <v>0.2609</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1529</v>
+        <v>0.1399</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2112</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1924,58 +1924,58 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00553</t>
+          <t>CM-26-00774</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
+          <t>La Grande Rue</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Francois Lamarche</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>167</v>
+        <v>24</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>37'269.73</t>
+          <t>12'881.25</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.036</v>
+        <v>0.2501</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.4424</v>
+        <v>0.1529</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1986</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1984,17 +1984,17 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03240</t>
+          <t>CM-26-00553</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -2004,38 +2004,38 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>245</v>
+        <v>167</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>12'603.94</t>
+          <t>37'269.73</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.2202</v>
+        <v>0.036</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1496</v>
+        <v>0.4424</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.192</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2044,58 +2044,58 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00844</t>
+          <t>CM-25-03240</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Château Larcis Ducasse</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>27</v>
+        <v>245</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>10'599.18</t>
+          <t>12'603.94</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.222</v>
+        <v>0.2202</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1258</v>
+        <v>0.1496</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1835</v>
+        <v>0.192</v>
       </c>
     </row>
   </sheetData>
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 15 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 20 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-22 08:47  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-27 09:11  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -2235,117 +2235,117 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>4.44%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>10'637.89</t>
+          <t>12'711.50</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.4613</v>
+        <v>0.2663</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.1263</v>
+        <v>0.1509</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.3273</v>
+        <v>0.2201</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01219</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>221</v>
+        <v>96</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>16'099.11</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.1626</v>
+        <v>0.1248</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.1911</v>
+        <v>0.0684</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.174</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-26-01320</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2355,127 +2355,127 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>13'289.90</t>
+          <t>4'696.54</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1674</v>
+        <v>0.132</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1578</v>
+        <v>0.0558</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1636</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>96</v>
+        <v>235</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>2'744.40</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1248</v>
+        <v>0.1278</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.0684</v>
+        <v>0.0326</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1022</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2494,34 +2494,34 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>48</v>
+        <v>257</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>458.10</t>
+          <t>3'382.19</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1248</v>
+        <v>0.0468</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0054</v>
+        <v>0.0401</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.077</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
@@ -2554,53 +2554,53 @@
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>46</v>
+        <v>323</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3'334.13</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0</v>
+        <v>0.0396</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0</v>
+        <v>0.0382</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -2614,67 +2614,67 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>48</v>
+        <v>280</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>576.17</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-01288</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>36</v>
+        <v>240</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
@@ -2699,8 +2699,128 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01310</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Georges Roumier</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01323</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>🟨</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Chambertin Clos de Bèze</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Bruno Clair</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:N11"/>
+  <autoFilter ref="A3:N13"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2737,14 +2857,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 23 Mar 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 28 Mar 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-22 08:47  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-27 09:11  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2942,11 +3062,11 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2956,57 +3076,57 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>181</v>
+        <v>26</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>4.97%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>32'321.12</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2981</v>
+        <v>0.4613</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.3837</v>
+        <v>0.1263</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3323</v>
+        <v>0.3273</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -3016,48 +3136,48 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>4.42%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>10'637.89</t>
+          <t>28'181.48</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.4613</v>
+        <v>0.2651</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1263</v>
+        <v>0.3345</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3273</v>
+        <v>0.2929</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -3122,67 +3242,67 @@
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>4.44%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>12'711.50</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1224</v>
+        <v>0.2663</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.4309</v>
+        <v>0.1509</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2458</v>
+        <v>0.2201</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
@@ -3242,7 +3362,7 @@
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -3287,22 +3407,22 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>13'289.90</t>
+          <t>13'038.03</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
         <v>0.1674</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1578</v>
+        <v>0.1548</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1636</v>
+        <v>0.1624</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
@@ -3362,7 +3482,7 @@
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
@@ -3422,11 +3542,11 @@
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3436,57 +3556,57 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>12'848.80</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.081</v>
+        <v>0.1248</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1525</v>
+        <v>0.0684</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1096</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-26-01320</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -3496,192 +3616,192 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>317</v>
+        <v>91</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>12'552.76</t>
+          <t>4'696.54</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0756</v>
+        <v>0.132</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.149</v>
+        <v>0.0558</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.105</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>96</v>
+        <v>235</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>2'744.40</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1248</v>
+        <v>0.1278</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0684</v>
+        <v>0.0326</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1022</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>487</v>
+        <v>257</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>3'382.19</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0468</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1716</v>
+        <v>0.0401</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.091</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01265</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -3695,98 +3815,98 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>48</v>
+        <v>323</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>458.10</t>
+          <t>3'334.13</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1248</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0054</v>
+        <v>0.0396</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.077</v>
+        <v>0.0382</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>104</v>
+        <v>280</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>576.17</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3796,26 +3916,26 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
@@ -3842,7 +3962,7 @@
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
@@ -3902,7 +4022,7 @@
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
@@ -3962,7 +4082,7 @@
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
@@ -4022,7 +4142,7 @@
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
@@ -4082,40 +4202,40 @@
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-26-01288</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>46</v>
+        <v>240</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
@@ -4142,40 +4262,40 @@
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-26-01310</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Georges Roumier</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>48</v>
+        <v>360</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>0</v>
@@ -4202,40 +4322,40 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
@@ -4276,7 +4396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4305,7 +4425,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-22 08:47  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-04-27 09:11  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4927,58 +5047,58 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-00871</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Chambertin Très Vieilles Vignes</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>4.97%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>32'321.12</t>
+          <t>29'483.52</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2981</v>
+        <v>0.3155</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.3837</v>
+        <v>0.35</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3323</v>
+        <v>0.3293</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -4987,58 +5107,58 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00871</t>
+          <t>CM-25-02625</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Rumbo al Norte</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Bodega Comando G</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>38</v>
+        <v>170</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>29'483.52</t>
+          <t>37'837.84</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3155</v>
+        <v>0.2472</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.35</v>
+        <v>0.4492</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3293</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -5047,7 +5167,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02625</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -5057,48 +5177,48 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Rumbo al Norte</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Bodega Comando G</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>37'837.84</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.2472</v>
+        <v>0.4613</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.4492</v>
+        <v>0.1263</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.328</v>
+        <v>0.3273</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -5107,7 +5227,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -5117,48 +5237,48 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>10'637.89</t>
+          <t>3'508.63</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.4613</v>
+        <v>0.4895</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1263</v>
+        <v>0.0417</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3273</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -5167,58 +5287,58 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>3'508.63</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.4895</v>
+        <v>0.3827</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0417</v>
+        <v>0.1902</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3104</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -5227,58 +5347,58 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>47</v>
+        <v>181</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>4.42%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>28'181.48</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.2651</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1902</v>
+        <v>0.3345</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3057</v>
+        <v>0.2929</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -5527,58 +5647,58 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>4.44%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>12'711.50</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.2663</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0683</v>
+        <v>0.1509</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2166</v>
+        <v>0.2201</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -5587,58 +5707,58 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2609</v>
+        <v>0.3155</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1399</v>
+        <v>0.0683</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2125</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -5647,58 +5767,58 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.2501</v>
+        <v>0.2609</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1529</v>
+        <v>0.1399</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2112</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5707,58 +5827,58 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00553</t>
+          <t>CM-26-00774</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
+          <t>La Grande Rue</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Francois Lamarche</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>167</v>
+        <v>24</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>37'269.73</t>
+          <t>12'881.25</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.036</v>
+        <v>0.2501</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.4424</v>
+        <v>0.1529</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1986</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5767,17 +5887,17 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03240</t>
+          <t>CM-26-00553</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -5787,38 +5907,38 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>245</v>
+        <v>167</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>12'603.94</t>
+          <t>37'269.73</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.2202</v>
+        <v>0.036</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1496</v>
+        <v>0.4424</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.192</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5827,58 +5947,58 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00844</t>
+          <t>CM-25-03240</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Château Larcis Ducasse</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>27</v>
+        <v>245</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>10'599.18</t>
+          <t>12'603.94</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.222</v>
+        <v>0.2202</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1258</v>
+        <v>0.1496</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1835</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5887,58 +6007,58 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01219</t>
+          <t>CM-26-00844</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>221</v>
+        <v>27</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>16'099.11</t>
+          <t>10'599.18</t>
         </is>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.1626</v>
+        <v>0.222</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1911</v>
+        <v>0.1258</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.174</v>
+        <v>0.1835</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5947,7 +6067,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02431</t>
+          <t>CM-26-01219</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -5972,33 +6092,33 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>156</v>
+        <v>221</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>11'961.88</t>
+          <t>16'099.11</t>
         </is>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1926</v>
+        <v>0.1626</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.142</v>
+        <v>0.1911</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1724</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6007,7 +6127,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-25-02431</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -6017,48 +6137,48 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>5</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>13'289.90</t>
+          <t>11'961.88</t>
         </is>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.1674</v>
+        <v>0.1926</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1578</v>
+        <v>0.142</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.1636</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6067,58 +6187,58 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00730</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>La Violette</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Château La Violette</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>17'433.26</t>
+          <t>13'038.03</t>
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1266</v>
+        <v>0.1674</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2069</v>
+        <v>0.1548</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1587</v>
+        <v>0.1624</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6127,58 +6247,58 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02972</t>
+          <t>CM-26-00730</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita</t>
+          <t>La Violette</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Château La Violette</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>1'257.15</t>
+          <t>17'433.26</t>
         </is>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.2466</v>
+        <v>0.1266</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.0149</v>
+        <v>0.2069</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1539</v>
+        <v>0.1587</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6187,7 +6307,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02689</t>
+          <t>CM-25-02972</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -6197,7 +6317,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges la Perrière</t>
+          <t>Finca Piedra Infinita</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -6207,38 +6327,38 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Domaine Gouges Henri</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>3'300.53</t>
+          <t>1'269.76</t>
         </is>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.222</v>
+        <v>0.2466</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.0392</v>
+        <v>0.0151</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1489</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6247,58 +6367,58 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-25-02689</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Nuits Saint Georges la Perrière</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Gouges Henri</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>24'547.24</t>
+          <t>3'300.53</t>
         </is>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.0462</v>
+        <v>0.222</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.2914</v>
+        <v>0.0392</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1443</v>
+        <v>0.1489</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6307,58 +6427,58 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00594</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mordorée</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Maison M. Chapoutier</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>12'780.81</t>
+          <t>24'547.24</t>
         </is>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.1362</v>
+        <v>0.0462</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.1517</v>
+        <v>0.2914</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.1424</v>
+        <v>0.1443</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -6367,7 +6487,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02637</t>
+          <t>CM-26-00594</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -6377,48 +6497,48 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Hommage à Jacques Perrin</t>
+          <t>Côte Rôtie La Mordorée</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Château de Beaucastel</t>
+          <t>Maison M. Chapoutier</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>1'587.81</t>
+          <t>12'780.81</t>
         </is>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.2142</v>
+        <v>0.1362</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.0188</v>
+        <v>0.1517</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.136</v>
+        <v>0.1424</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -6427,58 +6547,58 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-25-02637</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Hommage à Jacques Perrin</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château de Beaucastel</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>313</v>
+        <v>28</v>
       </c>
       <c r="I38" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>22'583.46</t>
+          <t>1'587.81</t>
         </is>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.0192</v>
+        <v>0.2142</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.2681</v>
+        <v>0.0188</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.1188</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -6487,58 +6607,58 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02474</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Mazoyères-Chambertin</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Arnaud Mortet</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>150</v>
+        <v>313</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>9'311.67</t>
+          <t>22'583.46</t>
         </is>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.12</v>
+        <v>0.0192</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1105</v>
+        <v>0.2681</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1162</v>
+        <v>0.1188</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -6547,58 +6667,58 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-25-02474</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Mazoyères-Chambertin</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Arnaud Mortet</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>12'848.80</t>
+          <t>9'311.67</t>
         </is>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.081</v>
+        <v>0.12</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.1525</v>
+        <v>0.1105</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.1096</v>
+        <v>0.1162</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -6607,7 +6727,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00779</t>
+          <t>CM-26-00963</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -6617,48 +6737,48 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>10'707.33</t>
+          <t>12'848.80</t>
         </is>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.0936</v>
+        <v>0.081</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1271</v>
+        <v>0.1525</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.107</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -6667,58 +6787,58 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02628</t>
+          <t>CM-26-00779</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Grillet Blanc</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Château Grillet</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>197</v>
+        <v>64</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>6'957.56</t>
+          <t>10'707.33</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.1218</v>
+        <v>0.0936</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.1271</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.1061</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -6727,7 +6847,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-25-02628</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -6737,7 +6857,7 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Grillet Blanc</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -6747,38 +6867,38 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Grillet</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>317</v>
+        <v>197</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>4</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>12'552.76</t>
+          <t>6'957.56</t>
         </is>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.0756</v>
+        <v>0.1218</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.149</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.105</v>
+        <v>0.1061</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -6787,58 +6907,58 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00772</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>198</v>
+        <v>317</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>10'109.38</t>
+          <t>12'552.76</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.0912</v>
+        <v>0.0756</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.12</v>
+        <v>0.149</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.1027</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -6847,7 +6967,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-00772</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -6857,48 +6977,48 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>10'109.38</t>
         </is>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.1248</v>
+        <v>0.0912</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.0684</v>
+        <v>0.12</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.1022</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -6907,7 +7027,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -6917,48 +7037,48 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>487</v>
+        <v>96</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.1248</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.1716</v>
+        <v>0.0684</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.091</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -6967,58 +7087,58 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00658</t>
+          <t>CM-26-01320</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Assortment de Grands Crus (12 bottles)</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Domaine Ponsot</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>7'018.00</t>
+          <t>4'696.54</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.132</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.0833</v>
+        <v>0.0558</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.0862</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -7027,58 +7147,58 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03004</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>10'547.81</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.0504</v>
+        <v>0.0372</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.1252</v>
+        <v>0.1716</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.0803</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -7087,58 +7207,58 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02535</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Meursault Clos des Bouchers</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Domaine Jean Marc Roulot</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>10'885.80</t>
+          <t>2'744.40</t>
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.045</v>
+        <v>0.1278</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.1292</v>
+        <v>0.0326</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -7147,58 +7267,58 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-00658</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Assortment de Grands Crus (12 bottles)</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Ponsot</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>458.10</t>
+          <t>7'018.00</t>
         </is>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.1248</v>
+        <v>0.0882</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.0054</v>
+        <v>0.0833</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.077</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -7207,58 +7327,58 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00483</t>
+          <t>CM-25-03004</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Pie Franco</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Bodegas Casa Castillo</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>53</v>
+        <v>476</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>690.03</t>
+          <t>10'547.81</t>
         </is>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0.1134</v>
+        <v>0.0504</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1252</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.0713</v>
+        <v>0.0803</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -7267,58 +7387,58 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02609</t>
+          <t>CM-25-02535</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Clos de la Roche</t>
+          <t>Meursault Clos des Bouchers</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Lignier</t>
+          <t>Domaine Jean Marc Roulot</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>5'003.90</t>
+          <t>10'885.80</t>
         </is>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.0774</v>
+        <v>0.045</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.0594</v>
+        <v>0.1292</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.0702</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -7327,58 +7447,58 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00851</t>
+          <t>CM-26-00483</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Pie Franco</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Bodegas Casa Castillo</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>271</v>
+        <v>53</v>
       </c>
       <c r="I53" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>4'218.04</t>
+          <t>690.03</t>
         </is>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0.0222</v>
+        <v>0.1134</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.0501</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.0334</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -7387,7 +7507,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02656</t>
+          <t>CM-25-02609</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -7397,48 +7517,48 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
+          <t>Clos de la Roche</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Weingut Markus Molitor</t>
+          <t>Domaine Georges Lignier</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>324</v>
+        <v>233</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>1'865.44</t>
+          <t>5'003.90</t>
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.0774</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.0221</v>
+        <v>0.0594</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -7447,58 +7567,58 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>126</v>
+        <v>257</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3'382.19</t>
         </is>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0</v>
+        <v>0.0468</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0</v>
+        <v>0.0401</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -7507,58 +7627,58 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-26-01265</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>75</v>
+        <v>323</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3'334.13</t>
         </is>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0</v>
+        <v>0.0396</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0</v>
+        <v>0.0382</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -7567,58 +7687,58 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-26-00851</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>362</v>
+        <v>271</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4'218.04</t>
         </is>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0</v>
+        <v>0.0222</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0</v>
+        <v>0.0501</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0</v>
+        <v>0.0334</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -7627,58 +7747,58 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-25-02656</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Weingut Markus Molitor</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>129</v>
+        <v>324</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1'865.44</t>
         </is>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0</v>
+        <v>0.0221</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -7687,58 +7807,58 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>643</v>
+        <v>280</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>576.17</t>
         </is>
       </c>
       <c r="L59" s="6" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -7747,7 +7867,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -7757,12 +7877,12 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -7776,7 +7896,7 @@
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>252</v>
+        <v>126</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>0</v>
@@ -7807,7 +7927,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -7817,26 +7937,26 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="I61" s="6" t="n">
         <v>0</v>
@@ -7867,7 +7987,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -7877,26 +7997,26 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>20</v>
+        <v>362</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>0</v>
@@ -7927,7 +8047,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -7937,26 +8057,26 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="I63" s="6" t="n">
         <v>0</v>
@@ -7987,7 +8107,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -7997,26 +8117,26 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I64" s="4" t="n">
         <v>0</v>
@@ -8047,7 +8167,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -8057,26 +8177,26 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>104</v>
+        <v>252</v>
       </c>
       <c r="I65" s="6" t="n">
         <v>0</v>
@@ -8107,7 +8227,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -8117,26 +8237,26 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>543</v>
+        <v>42</v>
       </c>
       <c r="I66" s="4" t="n">
         <v>0</v>
@@ -8167,7 +8287,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -8177,26 +8297,26 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>49</v>
+        <v>643</v>
       </c>
       <c r="I67" s="6" t="n">
         <v>0</v>
@@ -8227,7 +8347,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -8237,26 +8357,26 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="I68" s="4" t="n">
         <v>0</v>
@@ -8287,7 +8407,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -8297,26 +8417,26 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="I69" s="6" t="n">
         <v>0</v>
@@ -8347,7 +8467,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -8357,26 +8477,26 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="I70" s="4" t="n">
         <v>0</v>
@@ -8407,7 +8527,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -8417,26 +8537,26 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>26</v>
+        <v>543</v>
       </c>
       <c r="I71" s="6" t="n">
         <v>0</v>
@@ -8467,7 +8587,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -8477,26 +8597,26 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I72" s="4" t="n">
         <v>0</v>
@@ -8527,36 +8647,36 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="I73" s="6" t="n">
         <v>0</v>
@@ -8587,36 +8707,36 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="I74" s="4" t="n">
         <v>0</v>
@@ -8647,36 +8767,36 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -8707,62 +8827,362 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
+          <t>CM-26-01158</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>DRC Corton Charlemagne</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01159</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>DRC Corton Charlemagne</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="I77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01288</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Chambertin Clos de Bèze</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Armand Rousseau</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01310</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Georges Roumier</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="I79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01323</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>🟨</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Chambertin Clos de Bèze</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Bruno Clair</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
           <t>CM-25-02438</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>🟣</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>DRC Romanée Conti</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="H76" s="4" t="n">
+      <c r="H81" s="6" t="n">
         <v>410</v>
       </c>
-      <c r="I76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
+      <c r="I81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K76" s="4" t="inlineStr">
+      <c r="K81" s="6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="4" t="n">
+      <c r="L81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="6" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N76"/>
+  <autoFilter ref="A3:N81"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-27 09:11  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -705,17 +705,17 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>5'831.78</t>
+          <t>5'717.80</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.0692</v>
+        <v>0.0679</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6277</v>
+        <v>0.6272</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1564,58 +1564,58 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>13'335.52</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3257</v>
+        <v>0.1278</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1583</v>
+        <v>0.4545</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.2587</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1634,48 +1634,48 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.1224</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.4545</v>
+        <v>0.4309</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2585</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1684,58 +1684,58 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1224</v>
+        <v>0.3155</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4309</v>
+        <v>0.0683</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2458</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1744,58 +1744,58 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01284</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>4.44%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>12'711.50</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2663</v>
+        <v>0.2609</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1509</v>
+        <v>0.1399</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2201</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1804,58 +1804,58 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-00774</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>La Grande Rue</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Domaine Francois Lamarche</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>12'881.25</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.3155</v>
+        <v>0.2501</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0683</v>
+        <v>0.1529</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2166</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1864,39 +1864,39 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -1905,17 +1905,17 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>9'735.26</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
         <v>0.2609</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1399</v>
+        <v>0.1156</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2125</v>
+        <v>0.2028</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1924,58 +1924,58 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-26-00553</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>37'269.73</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2501</v>
+        <v>0.036</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1529</v>
+        <v>0.4424</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2112</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00553</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1994,48 +1994,48 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>37'269.73</t>
+          <t>30'472.80</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.036</v>
+        <v>0.0888</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.4424</v>
+        <v>0.3617</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1986</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 20 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 27 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-27 09:11  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,71 +2221,71 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01284</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>4.44%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>12'711.50</t>
+          <t>30'472.80</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.2663</v>
+        <v>0.0888</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.1509</v>
+        <v>0.3617</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.2201</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -2295,57 +2295,57 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>96</v>
+        <v>348</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>5'147.95</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.1248</v>
+        <v>0.0174</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.0684</v>
+        <v>0.0611</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.1022</v>
+        <v>0.0349</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01320</t>
+          <t>CM-26-01341</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2355,472 +2355,112 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Cathiard Vineyard</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
         <v>91</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>4'696.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.132</v>
+        <v>0</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.0558</v>
+        <v>0</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01350</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>235</v>
+        <v>29</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2'744.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1278</v>
+        <v>0</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.0326</v>
+        <v>0</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.0897</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01266</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Puligny Montrachet</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Pierre Vincent</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>257</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>3'382.19</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0.0468</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0.0401</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0.0441</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01265</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Meursault Crotots</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Domaine Pierre Vincent</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>323</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>0.62%</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>3'334.13</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>0.0372</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>0.0396</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>0.0382</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01268</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>🩷</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Pierre Vincent</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>280</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>0.36%</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>576.17</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0.0216</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0.0068</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>0.0157</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01288</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Chambertin Clos de Bèze</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Domaine Armand Rousseau</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>240</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01310</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Bonnes Mares</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Georges Roumier</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>360</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>77</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01323</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Chambertin Clos de Bèze</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Domaine Bruno Clair</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="6" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N13"/>
+  <autoFilter ref="A3:N7"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2835,7 +2475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2857,14 +2497,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 28 Mar 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 04 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-27 09:11  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2942,71 +2582,71 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01041</t>
+          <t>CM-26-01175</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Viña Tondonia Gran Reserva</t>
+          <t>Côte Rôtie La Mouline</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Bodegas López de Heredia Viña Tondonia</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>10.81%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>5'831.78</t>
+          <t>15'275.79</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1</v>
+        <v>0.6485</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.0692</v>
+        <v>0.1813</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.6277</v>
+        <v>0.4616</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01175</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -3016,57 +2656,57 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>15'275.79</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.6485</v>
+        <v>0.4613</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.1813</v>
+        <v>0.1263</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4616</v>
+        <v>0.3273</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -3076,177 +2716,177 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>4.42%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>10'637.89</t>
+          <t>28'181.48</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.4613</v>
+        <v>0.2651</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1263</v>
+        <v>0.3345</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3273</v>
+        <v>0.2929</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>181</v>
+        <v>135</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>28'181.48</t>
+          <t>30'472.80</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2651</v>
+        <v>0.0888</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3345</v>
+        <v>0.3617</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2929</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>13'335.52</t>
+          <t>14'592.69</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3257</v>
+        <v>0.201</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1583</v>
+        <v>0.1732</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2587</v>
+        <v>0.1899</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01284</t>
+          <t>CM-26-01219</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -3256,187 +2896,187 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>45</v>
+        <v>221</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>4.44%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>12'711.50</t>
+          <t>16'099.11</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2663</v>
+        <v>0.1626</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1509</v>
+        <v>0.1911</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2201</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01219</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>221</v>
+        <v>130</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>16'099.11</t>
+          <t>24'547.24</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1626</v>
+        <v>0.0462</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1911</v>
+        <v>0.2914</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.174</v>
+        <v>0.1443</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>179</v>
+        <v>313</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>13'038.03</t>
+          <t>22'583.46</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1674</v>
+        <v>0.0192</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1548</v>
+        <v>0.2681</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1624</v>
+        <v>0.1188</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -3446,47 +3086,47 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>24'547.24</t>
+          <t>8'112.00</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.1332</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2914</v>
+        <v>0.0963</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1443</v>
+        <v>0.1184</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -3496,187 +3136,187 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>313</v>
+        <v>96</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>22'583.46</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0192</v>
+        <v>0.1248</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2681</v>
+        <v>0.0684</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1188</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-01320</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>4'696.54</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1248</v>
+        <v>0.132</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0684</v>
+        <v>0.0558</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1022</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01320</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>91</v>
+        <v>235</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>4'696.54</t>
+          <t>2'744.40</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.132</v>
+        <v>0.1278</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0558</v>
+        <v>0.0326</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1015</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -3686,43 +3326,43 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>235</v>
+        <v>100</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2'744.40</t>
+          <t>3'049.20</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.06</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0326</v>
+        <v>0.0362</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0897</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
@@ -3782,7 +3422,7 @@
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
@@ -3827,17 +3467,17 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>3'334.13</t>
+          <t>2'925.89</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
         <v>0.0372</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0396</v>
+        <v>0.0347</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0382</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3846,118 +3486,118 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>280</v>
+        <v>348</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>576.17</t>
+          <t>5'147.95</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0216</v>
+        <v>0.0174</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0068</v>
+        <v>0.0611</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0157</v>
+        <v>0.0349</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>104</v>
+        <v>280</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>576.17</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -3966,7 +3606,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -3976,26 +3616,26 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
@@ -4022,11 +3662,11 @@
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -4036,17 +3676,17 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -4055,7 +3695,7 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>0</v>
@@ -4082,11 +3722,11 @@
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -4101,7 +3741,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -4115,7 +3755,7 @@
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
@@ -4142,11 +3782,11 @@
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -4161,7 +3801,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -4171,11 +3811,11 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>0</v>
@@ -4202,11 +3842,11 @@
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01288</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -4216,26 +3856,26 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>240</v>
+        <v>45</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
@@ -4262,11 +3902,11 @@
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01310</t>
+          <t>CM-26-01288</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -4276,26 +3916,26 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>0</v>
@@ -4322,66 +3962,126 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-26-01310</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Georges Roumier</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>716</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01341</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
           <t>🟨</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Chambertin Clos de Bèze</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Domaine Bruno Clair</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Cabernet Sauvignon</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Cathiard Vineyard</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K27" s="6" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="6" t="n">
+      <c r="L28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N27"/>
+  <autoFilter ref="A3:N28"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -4396,7 +4096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4425,7 +4125,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-27 09:11  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4608,17 +4308,17 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>5'831.78</t>
+          <t>5'717.80</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.0692</v>
+        <v>0.0679</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6277</v>
+        <v>0.6272</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -5467,58 +5167,58 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>13'335.52</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3257</v>
+        <v>0.1278</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1583</v>
+        <v>0.4545</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.2587</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -5527,7 +5227,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -5537,48 +5237,48 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.1224</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.4545</v>
+        <v>0.4309</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2585</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -5587,58 +5287,58 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1224</v>
+        <v>0.3155</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4309</v>
+        <v>0.0683</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2458</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -5647,58 +5347,58 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01284</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>4.44%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>12'711.50</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2663</v>
+        <v>0.2609</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1509</v>
+        <v>0.1399</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2201</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -5707,58 +5407,58 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-00774</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>La Grande Rue</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Domaine Francois Lamarche</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>12'881.25</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.3155</v>
+        <v>0.2501</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0683</v>
+        <v>0.1529</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2166</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -5767,39 +5467,39 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -5808,17 +5508,17 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>9'735.26</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
         <v>0.2609</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1399</v>
+        <v>0.1156</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2125</v>
+        <v>0.2028</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5827,58 +5527,58 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-26-00553</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>37'269.73</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2501</v>
+        <v>0.036</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1529</v>
+        <v>0.4424</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2112</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5887,7 +5587,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00553</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -5897,48 +5597,48 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>37'269.73</t>
+          <t>30'472.80</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.036</v>
+        <v>0.0888</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.4424</v>
+        <v>0.3617</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1986</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -6007,58 +5707,58 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00844</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>27</v>
+        <v>179</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>10'599.18</t>
+          <t>14'592.69</t>
         </is>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.222</v>
+        <v>0.201</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1258</v>
+        <v>0.1732</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1835</v>
+        <v>0.1899</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -6067,58 +5767,58 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01219</t>
+          <t>CM-26-00844</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>221</v>
+        <v>27</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>16'099.11</t>
+          <t>10'599.18</t>
         </is>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1626</v>
+        <v>0.222</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.1911</v>
+        <v>0.1258</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.174</v>
+        <v>0.1835</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6127,7 +5827,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02431</t>
+          <t>CM-26-01219</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -6152,33 +5852,33 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>156</v>
+        <v>221</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>11'961.88</t>
+          <t>16'099.11</t>
         </is>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.1926</v>
+        <v>0.1626</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.142</v>
+        <v>0.1911</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.1724</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6187,7 +5887,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-25-02431</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -6197,48 +5897,48 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="I32" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>13'038.03</t>
+          <t>11'961.88</t>
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1674</v>
+        <v>0.1926</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.1548</v>
+        <v>0.142</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1624</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6667,7 +6367,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02474</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -6677,48 +6377,48 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Mazoyères-Chambertin</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Arnaud Mortet</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>9'311.67</t>
+          <t>8'112.00</t>
         </is>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.12</v>
+        <v>0.1332</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.1105</v>
+        <v>0.0963</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.1162</v>
+        <v>0.1184</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -6727,58 +6427,58 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-25-02474</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Mazoyères-Chambertin</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Arnaud Mortet</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>12'848.80</t>
+          <t>9'311.67</t>
         </is>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.081</v>
+        <v>0.12</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1525</v>
+        <v>0.1105</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1096</v>
+        <v>0.1162</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -6787,7 +6487,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00779</t>
+          <t>CM-26-00963</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -6797,48 +6497,48 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="I42" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>10'707.33</t>
+          <t>12'848.80</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.0936</v>
+        <v>0.081</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.1271</v>
+        <v>0.1525</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.107</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -6847,58 +6547,58 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02628</t>
+          <t>CM-26-00779</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Grillet Blanc</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Château Grillet</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>197</v>
+        <v>64</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>6'957.56</t>
+          <t>10'707.33</t>
         </is>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.1218</v>
+        <v>0.0936</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.1271</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1061</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -6907,7 +6607,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-25-02628</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -6917,7 +6617,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Grillet Blanc</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -6927,38 +6627,38 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Grillet</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>317</v>
+        <v>197</v>
       </c>
       <c r="I44" s="4" t="n">
         <v>4</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>12'552.76</t>
+          <t>6'957.56</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.0756</v>
+        <v>0.1218</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.149</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.105</v>
+        <v>0.1061</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -6967,58 +6667,58 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00772</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>198</v>
+        <v>317</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>10'109.38</t>
+          <t>12'552.76</t>
         </is>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.0912</v>
+        <v>0.0756</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.12</v>
+        <v>0.149</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.1027</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -7027,7 +6727,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-00772</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -7037,48 +6737,48 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>10'109.38</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.1248</v>
+        <v>0.0912</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.0684</v>
+        <v>0.12</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.1022</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -7087,58 +6787,58 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01320</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>4'696.54</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.132</v>
+        <v>0.1248</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.0558</v>
+        <v>0.0684</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.1015</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -7147,58 +6847,58 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-26-01320</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>487</v>
+        <v>91</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>4'696.54</t>
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.132</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.1716</v>
+        <v>0.0558</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.091</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -7207,58 +6907,58 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>235</v>
+        <v>487</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2'744.40</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.0372</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.0326</v>
+        <v>0.1716</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.0897</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -7267,58 +6967,58 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00658</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Assortment de Grands Crus (12 bottles)</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Domaine Ponsot</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>68</v>
+        <v>235</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>7'018.00</t>
+          <t>2'744.40</t>
         </is>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.0882</v>
+        <v>0.1278</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.0326</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.0862</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -7327,58 +7027,58 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03004</t>
+          <t>CM-26-00658</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Assortment de Grands Crus (12 bottles)</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine Ponsot</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>10'547.81</t>
+          <t>7'018.00</t>
         </is>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0.0504</v>
+        <v>0.0882</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.1252</v>
+        <v>0.0833</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.0803</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -7387,58 +7087,58 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02535</t>
+          <t>CM-25-03004</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Meursault Clos des Bouchers</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Domaine Jean Marc Roulot</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>268</v>
+        <v>476</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>10'885.80</t>
+          <t>10'547.81</t>
         </is>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.045</v>
+        <v>0.0504</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.1292</v>
+        <v>0.1252</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0803</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -7447,58 +7147,58 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00483</t>
+          <t>CM-25-02535</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Pie Franco</t>
+          <t>Meursault Clos des Bouchers</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Bodegas Casa Castillo</t>
+          <t>Domaine Jean Marc Roulot</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>53</v>
+        <v>268</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>690.03</t>
+          <t>10'885.80</t>
         </is>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0.1134</v>
+        <v>0.045</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1292</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.0713</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -7507,7 +7207,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02609</t>
+          <t>CM-26-00483</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -7517,48 +7217,48 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Clos de la Roche</t>
+          <t>Pie Franco</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Lignier</t>
+          <t>Bodegas Casa Castillo</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>233</v>
+        <v>53</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>5'003.90</t>
+          <t>690.03</t>
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.0774</v>
+        <v>0.1134</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.0594</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.0702</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -7567,7 +7267,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-25-02609</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -7577,48 +7277,48 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Clos de la Roche</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Georges Lignier</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>3'382.19</t>
+          <t>5'003.90</t>
         </is>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.0468</v>
+        <v>0.0774</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.0401</v>
+        <v>0.0594</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.0441</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -7627,58 +7327,58 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>323</v>
+        <v>100</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>3'334.13</t>
+          <t>3'049.20</t>
         </is>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.06</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.0396</v>
+        <v>0.0362</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.0382</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -7687,58 +7387,58 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00851</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>4'218.04</t>
+          <t>3'382.19</t>
         </is>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.0222</v>
+        <v>0.0468</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.0501</v>
+        <v>0.0401</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.0334</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -7747,7 +7447,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02656</t>
+          <t>CM-26-01265</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -7757,26 +7457,26 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Weingut Markus Molitor</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>2</v>
@@ -7788,17 +7488,17 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>1'865.44</t>
+          <t>2'925.89</t>
         </is>
       </c>
       <c r="L58" s="4" t="n">
         <v>0.0372</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.0221</v>
+        <v>0.0347</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -7807,58 +7507,58 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>280</v>
+        <v>348</v>
       </c>
       <c r="I59" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>576.17</t>
+          <t>5'147.95</t>
         </is>
       </c>
       <c r="L59" s="6" t="n">
-        <v>0.0216</v>
+        <v>0.0174</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0.0068</v>
+        <v>0.0611</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.0157</v>
+        <v>0.0349</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -7867,58 +7567,58 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-00851</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>126</v>
+        <v>271</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4'218.04</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0</v>
+        <v>0.0222</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0</v>
+        <v>0.0501</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0</v>
+        <v>0.0334</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -7927,58 +7627,58 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-25-02656</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Weingut Markus Molitor</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>75</v>
+        <v>324</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1'865.44</t>
         </is>
       </c>
       <c r="L61" s="6" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0</v>
+        <v>0.0221</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -7987,58 +7687,58 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>362</v>
+        <v>280</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>576.17</t>
         </is>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -8047,7 +7747,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -8057,26 +7757,26 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>129</v>
+        <v>543</v>
       </c>
       <c r="I63" s="6" t="n">
         <v>0</v>
@@ -8167,7 +7867,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -8177,26 +7877,26 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>252</v>
+        <v>643</v>
       </c>
       <c r="I65" s="6" t="n">
         <v>0</v>
@@ -8287,7 +7987,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -8297,26 +7997,26 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>643</v>
+        <v>252</v>
       </c>
       <c r="I67" s="6" t="n">
         <v>0</v>
@@ -8347,7 +8047,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -8357,26 +8057,26 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="I68" s="4" t="n">
         <v>0</v>
@@ -8407,7 +8107,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -8417,26 +8117,26 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="I69" s="6" t="n">
         <v>0</v>
@@ -8467,7 +8167,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -8477,26 +8177,26 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>104</v>
+        <v>362</v>
       </c>
       <c r="I70" s="4" t="n">
         <v>0</v>
@@ -8527,7 +8227,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -8537,26 +8237,26 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>543</v>
+        <v>75</v>
       </c>
       <c r="I71" s="6" t="n">
         <v>0</v>
@@ -8587,7 +8287,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -8597,26 +8297,26 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="I72" s="4" t="n">
         <v>0</v>
@@ -8647,7 +8347,7 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -8657,26 +8357,26 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="I73" s="6" t="n">
         <v>0</v>
@@ -8707,7 +8407,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -8717,26 +8417,26 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I74" s="4" t="n">
         <v>0</v>
@@ -8767,7 +8467,7 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -8777,26 +8477,26 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -8827,7 +8527,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -8837,26 +8537,26 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="I76" s="4" t="n">
         <v>0</v>
@@ -8887,7 +8587,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -8897,26 +8597,26 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="I77" s="6" t="n">
         <v>0</v>
@@ -8947,7 +8647,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01288</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -8957,26 +8657,26 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>240</v>
+        <v>28</v>
       </c>
       <c r="I78" s="4" t="n">
         <v>0</v>
@@ -9007,7 +8707,7 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01310</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -9017,26 +8717,26 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>360</v>
+        <v>26</v>
       </c>
       <c r="I79" s="6" t="n">
         <v>0</v>
@@ -9067,36 +8767,36 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="I80" s="4" t="n">
         <v>0</v>
@@ -9127,62 +8827,302 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
+          <t>CM-26-01288</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Chambertin Clos de Bèze</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Armand Rousseau</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="I81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01310</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Georges Roumier</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>716</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01341</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>🟨</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Cabernet Sauvignon</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Cathiard Vineyard</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="I83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01350</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>🟨</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Chambertin Clos de Bèze</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Bruno Clair</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
           <t>CM-25-02438</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>🟣</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>DRC Romanée Conti</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="G85" s="6" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="H81" s="6" t="n">
+      <c r="H85" s="6" t="n">
         <v>410</v>
       </c>
-      <c r="I81" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="6" t="inlineStr">
+      <c r="I85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K81" s="6" t="inlineStr">
+      <c r="K85" s="6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L81" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" s="6" t="n">
+      <c r="L85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="6" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N81"/>
+  <autoFilter ref="A3:N85"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$85</definedName>
   </definedNames>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 27 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 28 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -2235,232 +2235,112 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>135</v>
+        <v>348</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>30'472.80</t>
+          <t>5'147.95</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.0888</v>
+        <v>0.0174</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.3617</v>
+        <v>0.0611</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.198</v>
+        <v>0.0349</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01376</t>
+          <t>CM-26-01350</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Bollinger</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>348</v>
+        <v>29</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>5'147.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.0174</v>
+        <v>0</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.0611</v>
+        <v>0</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.0349</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01341</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Cabernet Sauvignon</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Cathiard Vineyard</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="n">
-        <v>81</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01350</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Chambertin Clos de Bèze</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Domaine Bruno Clair</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N7"/>
+  <autoFilter ref="A3:N5"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2497,14 +2377,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 04 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 05 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4005,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-11 14:07  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>48'551.95</t>
+          <t>48'472.47</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
         <v>0.3869</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.5764</v>
+        <v>0.5754</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4627</v>
+        <v>0.4623</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -885,17 +885,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>15'275.79</t>
+          <t>15'204.93</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
         <v>0.6485</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1813</v>
+        <v>0.1805</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4616</v>
+        <v>0.4613</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -1144,58 +1144,58 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00871</t>
+          <t>CM-26-01431</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>29'483.52</t>
+          <t>4'375.02</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.5357</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.35</v>
+        <v>0.0519</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3293</v>
+        <v>0.3422</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1204,58 +1204,58 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02625</t>
+          <t>CM-26-01429</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Rumbo al Norte</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Bodega Comando G</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>37'837.84</t>
+          <t>7'787.54</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2472</v>
+        <v>0.4997</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4492</v>
+        <v>0.0924</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.328</v>
+        <v>0.3368</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1264,58 +1264,58 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-00871</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Chambertin Très Vieilles Vignes</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>10'637.89</t>
+          <t>29'483.52</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.4613</v>
+        <v>0.3155</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.1263</v>
+        <v>0.35</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.3273</v>
+        <v>0.3293</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-25-02625</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1334,48 +1334,48 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Rumbo al Norte</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Bodega Comando G</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>3'508.63</t>
+          <t>37'837.84</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.4895</v>
+        <v>0.2472</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.4492</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3104</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1384,58 +1384,58 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.3827</v>
+        <v>0.4613</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1902</v>
+        <v>0.1263</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3057</v>
+        <v>0.3273</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1454,48 +1454,48 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>28'181.48</t>
+          <t>3'508.63</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2651</v>
+        <v>0.4895</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.3345</v>
+        <v>0.0417</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2929</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1504,58 +1504,58 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>20'974.64</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.2771</v>
+        <v>0.3827</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.249</v>
+        <v>0.1902</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2659</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1564,58 +1564,58 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>47</v>
+        <v>181</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>26'801.63</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.2322</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.3182</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.2585</v>
+        <v>0.2666</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1624,58 +1624,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>49</v>
+        <v>195</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>20'502.14</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1224</v>
+        <v>0.2771</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.4309</v>
+        <v>0.2434</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2458</v>
+        <v>0.2636</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1684,58 +1684,58 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3155</v>
+        <v>0.1278</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0683</v>
+        <v>0.4545</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2166</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1754,48 +1754,48 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2609</v>
+        <v>0.1224</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1399</v>
+        <v>0.4309</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2125</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1804,58 +1804,58 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2501</v>
+        <v>0.3155</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1529</v>
+        <v>0.0683</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2112</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1864,39 +1864,39 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -1905,17 +1905,17 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>9'735.26</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
         <v>0.2609</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1156</v>
+        <v>0.1399</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2028</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1924,58 +1924,58 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00553</t>
+          <t>CM-26-00774</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
+          <t>La Grande Rue</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Francois Lamarche</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>167</v>
+        <v>24</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>37'269.73</t>
+          <t>12'881.25</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.036</v>
+        <v>0.2501</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.4424</v>
+        <v>0.1529</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1986</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1994,48 +1994,48 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>30'472.80</t>
+          <t>21'358.58</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0888</v>
+        <v>0.1692</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.3617</v>
+        <v>0.2535</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.198</v>
+        <v>0.2029</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2044,58 +2044,58 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03240</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>245</v>
+        <v>92</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>12'603.94</t>
+          <t>9'735.26</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2202</v>
+        <v>0.2609</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1496</v>
+        <v>0.1156</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.192</v>
+        <v>0.2028</v>
       </c>
     </row>
   </sheetData>
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 28 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 04 May 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-11 14:07  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,126 +2221,306 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01431</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Ca' Marcanda</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Ca' Marcanda - Gaja</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01376</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Bollinger</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>348</v>
-      </c>
       <c r="I4" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>5'147.95</t>
+          <t>4'375.02</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.0174</v>
+        <v>0.5357</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.0611</v>
+        <v>0.0519</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.0349</v>
+        <v>0.3422</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01350</t>
+          <t>CM-26-01429</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Ca' Marcanda - Gaja</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>8.33%</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>7'787.54</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>0.4997</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>0.0924</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>0.3368</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01423</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Meursault Blanc</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Domaine Bruno Clair</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>0</v>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Coche-Dury</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2.82%</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>21'358.58</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.1692</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.2535</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0.2029</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01439</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Haut Brion</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Château Haut Brion</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>2.78%</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>15'600.00</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>0.1852</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>0.1742</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01254</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Bâtard-Montrachet</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Bernard Dugat-Py</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>5'486.82</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0.0581</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N5"/>
+  <autoFilter ref="A3:N8"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2355,7 +2535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2377,14 +2557,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 05 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 11 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-11 14:07  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2462,131 +2642,131 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01431</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Ca' Marcanda</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Ca' Marcanda - Gaja</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01175</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Côte Rôtie La Mouline</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Guigal</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>15'275.79</t>
+          <t>4'375.02</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.6485</v>
+        <v>0.5357</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.1813</v>
+        <v>0.0519</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.4616</v>
+        <v>0.3422</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-01429</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>10'637.89</t>
+          <t>7'787.54</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.4613</v>
+        <v>0.4997</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.1263</v>
+        <v>0.0924</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.3273</v>
+        <v>0.3368</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2596,48 +2776,48 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>181</v>
+        <v>26</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>28'181.48</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2651</v>
+        <v>0.4613</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.3345</v>
+        <v>0.1263</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2929</v>
+        <v>0.3273</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2646,7 +2826,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -2656,53 +2836,53 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>30'472.80</t>
+          <t>21'358.58</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.0888</v>
+        <v>0.1692</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3617</v>
+        <v>0.2535</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.198</v>
+        <v>0.2029</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
@@ -2762,71 +2942,71 @@
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01219</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>221</v>
+        <v>135</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>16'099.11</t>
+          <t>26'268.00</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1626</v>
+        <v>0.0888</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1911</v>
+        <v>0.3118</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.174</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-26-01439</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -2836,113 +3016,113 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>24'547.24</t>
+          <t>15'600.00</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.1668</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2914</v>
+        <v>0.1852</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1443</v>
+        <v>0.1742</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-01219</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>313</v>
+        <v>221</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>22'583.46</t>
+          <t>16'099.11</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0192</v>
+        <v>0.1626</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2681</v>
+        <v>0.1911</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1188</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
@@ -3002,7 +3182,7 @@
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
@@ -3062,7 +3242,7 @@
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
@@ -3122,81 +3302,81 @@
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>235</v>
+        <v>348</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2'744.40</t>
+          <t>14'566.45</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.0516</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0326</v>
+        <v>0.1729</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0897</v>
+        <v>0.1001</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -3206,57 +3386,57 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>100</v>
+        <v>235</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>3'049.20</t>
+          <t>2'738.04</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.06</v>
+        <v>0.1278</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0362</v>
+        <v>0.0325</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0505</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -3266,177 +3446,177 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>257</v>
+        <v>112</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>3'382.19</t>
+          <t>5'486.82</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0468</v>
+        <v>0.0534</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0401</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0441</v>
+        <v>0.0581</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>323</v>
+        <v>100</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2'925.89</t>
+          <t>3'049.20</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.06</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0347</v>
+        <v>0.0362</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0362</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01376</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Bollinger</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>5'147.95</t>
+          <t>3'382.19</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0174</v>
+        <v>0.0468</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0611</v>
+        <v>0.0401</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0349</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-01265</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -3455,98 +3635,98 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>280</v>
+        <v>323</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>576.17</t>
+          <t>2'912.26</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0216</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0068</v>
+        <v>0.0346</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0157</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>104</v>
+        <v>280</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>568.18</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-01288</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -3556,26 +3736,26 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>103</v>
+        <v>240</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>0</v>
@@ -3602,11 +3782,11 @@
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01310</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -3616,26 +3796,26 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Georges Roumier</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>28</v>
+        <v>716</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
@@ -3662,40 +3842,40 @@
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-26-01341</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Cathiard Vineyard</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>0</v>
@@ -3722,40 +3902,40 @@
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01349</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
@@ -3780,188 +3960,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01288</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Chambertin Clos de Bèze</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Armand Rousseau</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="6" t="n">
-        <v>79</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01310</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Bonnes Mares</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Domaine Georges Roumier</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>716</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01341</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Cabernet Sauvignon</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Cathiard Vineyard</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:N28"/>
+  <autoFilter ref="A3:N25"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3976,7 +3976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4005,7 +4005,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-11 14:07  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4308,17 +4308,17 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>48'551.95</t>
+          <t>48'472.47</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
         <v>0.3869</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.5764</v>
+        <v>0.5754</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4627</v>
+        <v>0.4623</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -4368,17 +4368,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>15'275.79</t>
+          <t>15'204.93</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
         <v>0.6485</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1813</v>
+        <v>0.1805</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4616</v>
+        <v>0.4613</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -4627,58 +4627,58 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00871</t>
+          <t>CM-26-01431</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>29'483.52</t>
+          <t>4'375.02</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.5357</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.35</v>
+        <v>0.0519</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3293</v>
+        <v>0.3422</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -4687,58 +4687,58 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02625</t>
+          <t>CM-26-01429</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Rumbo al Norte</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Bodega Comando G</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>37'837.84</t>
+          <t>7'787.54</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2472</v>
+        <v>0.4997</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4492</v>
+        <v>0.0924</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.328</v>
+        <v>0.3368</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -4747,58 +4747,58 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-00871</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Chambertin Très Vieilles Vignes</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>10'637.89</t>
+          <t>29'483.52</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.4613</v>
+        <v>0.3155</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.1263</v>
+        <v>0.35</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.3273</v>
+        <v>0.3293</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-25-02625</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4817,48 +4817,48 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Rumbo al Norte</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Bodega Comando G</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>3'508.63</t>
+          <t>37'837.84</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.4895</v>
+        <v>0.2472</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.4492</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3104</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -4867,58 +4867,58 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.3827</v>
+        <v>0.4613</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1902</v>
+        <v>0.1263</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3057</v>
+        <v>0.3273</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -4937,48 +4937,48 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>28'181.48</t>
+          <t>3'508.63</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2651</v>
+        <v>0.4895</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.3345</v>
+        <v>0.0417</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2929</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -4987,58 +4987,58 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>20'974.64</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.2771</v>
+        <v>0.3827</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.249</v>
+        <v>0.1902</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2659</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -5047,58 +5047,58 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>47</v>
+        <v>181</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>26'801.63</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.2322</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.3182</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.2585</v>
+        <v>0.2666</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -5107,58 +5107,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>49</v>
+        <v>195</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>20'502.14</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1224</v>
+        <v>0.2771</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.4309</v>
+        <v>0.2434</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2458</v>
+        <v>0.2636</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -5167,58 +5167,58 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3155</v>
+        <v>0.1278</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0683</v>
+        <v>0.4545</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2166</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -5237,48 +5237,48 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2609</v>
+        <v>0.1224</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1399</v>
+        <v>0.4309</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2125</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -5287,58 +5287,58 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2501</v>
+        <v>0.3155</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1529</v>
+        <v>0.0683</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2112</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -5347,39 +5347,39 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -5388,17 +5388,17 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>9'735.26</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
         <v>0.2609</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1156</v>
+        <v>0.1399</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2028</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5407,58 +5407,58 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00553</t>
+          <t>CM-26-00774</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
+          <t>La Grande Rue</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Francois Lamarche</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>167</v>
+        <v>24</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>37'269.73</t>
+          <t>12'881.25</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.036</v>
+        <v>0.2501</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.4424</v>
+        <v>0.1529</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1986</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -5477,48 +5477,48 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>30'472.80</t>
+          <t>21'358.58</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0888</v>
+        <v>0.1692</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.3617</v>
+        <v>0.2535</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.198</v>
+        <v>0.2029</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5527,58 +5527,58 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03240</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>245</v>
+        <v>92</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>12'603.94</t>
+          <t>9'735.26</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2202</v>
+        <v>0.2609</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1496</v>
+        <v>0.1156</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.192</v>
+        <v>0.2028</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5587,58 +5587,58 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-26-00553</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>14'592.69</t>
+          <t>37'269.73</t>
         </is>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.201</v>
+        <v>0.036</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1732</v>
+        <v>0.4424</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1899</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5647,58 +5647,58 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00844</t>
+          <t>CM-25-03240</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Château Larcis Ducasse</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>27</v>
+        <v>245</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>10'599.18</t>
+          <t>12'603.94</t>
         </is>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.222</v>
+        <v>0.2202</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.1258</v>
+        <v>0.1496</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1835</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01219</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -5717,48 +5717,48 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>221</v>
+        <v>179</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>6</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>16'099.11</t>
+          <t>14'592.69</t>
         </is>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.1626</v>
+        <v>0.201</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1911</v>
+        <v>0.1732</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.174</v>
+        <v>0.1899</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -5767,58 +5767,58 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02431</t>
+          <t>CM-26-00844</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>11'961.88</t>
+          <t>10'599.18</t>
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1926</v>
+        <v>0.222</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.142</v>
+        <v>0.1258</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1724</v>
+        <v>0.1835</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00730</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -5837,48 +5837,48 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>La Violette</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Château La Violette</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>17'433.26</t>
+          <t>26'268.00</t>
         </is>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.1266</v>
+        <v>0.0888</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.2069</v>
+        <v>0.3118</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1587</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -5887,58 +5887,58 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02972</t>
+          <t>CM-26-01439</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>1'269.76</t>
+          <t>15'600.00</t>
         </is>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2466</v>
+        <v>0.1668</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.0151</v>
+        <v>0.1852</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.154</v>
+        <v>0.1742</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -5947,58 +5947,58 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02689</t>
+          <t>CM-26-01219</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges la Perrière</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Domaine Gouges Henri</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>3'300.53</t>
+          <t>16'099.11</t>
         </is>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.222</v>
+        <v>0.1626</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.0392</v>
+        <v>0.1911</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1489</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6007,58 +6007,58 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-25-02431</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>24'547.24</t>
+          <t>11'961.88</t>
         </is>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.1926</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.2914</v>
+        <v>0.142</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.1443</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -6067,58 +6067,58 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00594</t>
+          <t>CM-26-00730</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mordorée</t>
+          <t>La Violette</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Maison M. Chapoutier</t>
+          <t>Château La Violette</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>12'780.81</t>
+          <t>17'433.26</t>
         </is>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.1362</v>
+        <v>0.1266</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1517</v>
+        <v>0.2069</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.1424</v>
+        <v>0.1587</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -6127,58 +6127,58 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02637</t>
+          <t>CM-25-02972</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Hommage à Jacques Perrin</t>
+          <t>Finca Piedra Infinita</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Château de Beaucastel</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>1'587.81</t>
+          <t>1'269.76</t>
         </is>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.2466</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.0188</v>
+        <v>0.0151</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.136</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -6187,58 +6187,58 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-25-02689</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Nuits Saint Georges la Perrière</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Gouges Henri</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>313</v>
+        <v>135</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>22'583.46</t>
+          <t>3'300.53</t>
         </is>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.0192</v>
+        <v>0.222</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.2681</v>
+        <v>0.0392</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1188</v>
+        <v>0.1489</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -6247,17 +6247,17 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01284</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -6267,38 +6267,38 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>8'112.00</t>
+          <t>24'547.24</t>
         </is>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.1332</v>
+        <v>0.0462</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.0963</v>
+        <v>0.2914</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.1184</v>
+        <v>0.1443</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02474</t>
+          <t>CM-26-00594</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -6317,48 +6317,48 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Mazoyères-Chambertin</t>
+          <t>Côte Rôtie La Mordorée</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Arnaud Mortet</t>
+          <t>Maison M. Chapoutier</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>150</v>
+        <v>88</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>9'311.67</t>
+          <t>12'780.81</t>
         </is>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.12</v>
+        <v>0.1362</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1105</v>
+        <v>0.1517</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1162</v>
+        <v>0.1424</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -6367,58 +6367,58 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-25-02637</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Hommage à Jacques Perrin</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château de Beaucastel</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="I42" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>12'848.80</t>
+          <t>1'587.81</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.081</v>
+        <v>0.2142</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.1525</v>
+        <v>0.0188</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.1096</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00779</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -6437,48 +6437,48 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>64</v>
+        <v>313</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>10'707.33</t>
+          <t>22'583.46</t>
         </is>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.0936</v>
+        <v>0.0192</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.1271</v>
+        <v>0.2681</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.107</v>
+        <v>0.1188</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02628</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Grillet Blanc</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -6507,38 +6507,38 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Château Grillet</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>6'957.56</t>
+          <t>8'112.00</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.1218</v>
+        <v>0.1332</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0963</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.1061</v>
+        <v>0.1184</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-25-02474</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -6557,48 +6557,48 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Mazoyères-Chambertin</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Arnaud Mortet</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>317</v>
+        <v>150</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>12'552.76</t>
+          <t>9'311.67</t>
         </is>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.0756</v>
+        <v>0.12</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.149</v>
+        <v>0.1105</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.105</v>
+        <v>0.1162</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00772</t>
+          <t>CM-26-00963</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -6617,48 +6617,48 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>10'109.38</t>
+          <t>12'848.80</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.0912</v>
+        <v>0.081</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.12</v>
+        <v>0.1525</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.1027</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-00779</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -6677,48 +6677,48 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>10'707.33</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.1248</v>
+        <v>0.0936</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.0684</v>
+        <v>0.1271</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.1022</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01320</t>
+          <t>CM-25-02628</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -6737,48 +6737,48 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Grillet Blanc</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Château Grillet</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>91</v>
+        <v>197</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>4'696.54</t>
+          <t>6'957.56</t>
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.132</v>
+        <v>0.1218</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.0558</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.1015</v>
+        <v>0.1061</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -6787,27 +6787,27 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -6816,29 +6816,29 @@
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>487</v>
+        <v>317</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>12'118.06</t>
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0756</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.1716</v>
+        <v>0.1439</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.091</v>
+        <v>0.1029</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -6847,58 +6847,58 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-00772</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2'744.40</t>
+          <t>10'109.38</t>
         </is>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.0912</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.0326</v>
+        <v>0.12</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.0897</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00658</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -6917,48 +6917,48 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Assortment de Grands Crus (12 bottles)</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Domaine Ponsot</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>7'018.00</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.1248</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.0833</v>
+        <v>0.0684</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.0862</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03004</t>
+          <t>CM-26-01320</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -6977,48 +6977,48 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>476</v>
+        <v>91</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>10'547.81</t>
+          <t>4'696.54</t>
         </is>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.0504</v>
+        <v>0.132</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.1252</v>
+        <v>0.0558</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.0803</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02535</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -7037,48 +7037,48 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Meursault Clos des Bouchers</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Domaine Jean Marc Roulot</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>268</v>
+        <v>348</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>10'885.80</t>
+          <t>14'566.45</t>
         </is>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0.045</v>
+        <v>0.0516</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.1292</v>
+        <v>0.1729</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.1001</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -7087,58 +7087,58 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00483</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Pie Franco</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Bodegas Casa Castillo</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>53</v>
+        <v>487</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>690.03</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.1134</v>
+        <v>0.0372</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1716</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.0713</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -7147,58 +7147,58 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02609</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Clos de la Roche</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Domaine Georges Lignier</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>5'003.90</t>
+          <t>2'738.04</t>
         </is>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.0774</v>
+        <v>0.1278</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.0594</v>
+        <v>0.0325</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.0702</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -7207,58 +7207,58 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-26-00658</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Assortment de Grands Crus (12 bottles)</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine Ponsot</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="I56" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>3'049.20</t>
+          <t>7'018.00</t>
         </is>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.06</v>
+        <v>0.0882</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.0362</v>
+        <v>0.0833</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.0505</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -7267,58 +7267,58 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-25-03004</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>257</v>
+        <v>476</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>3'382.19</t>
+          <t>10'547.81</t>
         </is>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.0468</v>
+        <v>0.0504</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.0401</v>
+        <v>0.1252</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.0441</v>
+        <v>0.0803</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -7327,58 +7327,58 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-25-02535</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Meursault Clos des Bouchers</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Jean Marc Roulot</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>323</v>
+        <v>268</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2'925.89</t>
+          <t>10'885.80</t>
         </is>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.045</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.0347</v>
+        <v>0.1292</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.0362</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -7387,58 +7387,58 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01376</t>
+          <t>CM-26-00483</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
+          <t>Pie Franco</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Bollinger</t>
+          <t>Bodegas Casa Castillo</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>348</v>
+        <v>53</v>
       </c>
       <c r="I59" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>5'147.95</t>
+          <t>690.03</t>
         </is>
       </c>
       <c r="L59" s="6" t="n">
-        <v>0.0174</v>
+        <v>0.1134</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0.0611</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.0349</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -7447,58 +7447,58 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00851</t>
+          <t>CM-25-02609</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Clos de la Roche</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Georges Lignier</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>4'218.04</t>
+          <t>5'003.90</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.0222</v>
+        <v>0.0774</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.0501</v>
+        <v>0.0594</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.0334</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -7507,58 +7507,58 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02656</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Weingut Markus Molitor</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>324</v>
+        <v>112</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>1'865.44</t>
+          <t>5'486.82</t>
         </is>
       </c>
       <c r="L61" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0534</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.0221</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.0312</v>
+        <v>0.0581</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -7567,58 +7567,58 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>280</v>
+        <v>100</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>576.17</t>
+          <t>3'049.20</t>
         </is>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.0216</v>
+        <v>0.06</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.0068</v>
+        <v>0.0362</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0.0157</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -7627,58 +7627,58 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>543</v>
+        <v>257</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3'382.19</t>
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>0</v>
+        <v>0.0468</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>0</v>
+        <v>0.0401</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>0</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -7687,58 +7687,58 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-26-01265</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>20</v>
+        <v>323</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2'912.26</t>
         </is>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0</v>
+        <v>0.0346</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -7747,58 +7747,58 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-26-00851</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>643</v>
+        <v>271</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4'218.04</t>
         </is>
       </c>
       <c r="L65" s="6" t="n">
-        <v>0</v>
+        <v>0.0222</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>0</v>
+        <v>0.0501</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>0</v>
+        <v>0.0334</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -7807,58 +7807,58 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-25-02656</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Weingut Markus Molitor</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>42</v>
+        <v>324</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1'865.44</t>
         </is>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0</v>
+        <v>0.0221</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -7867,58 +7867,58 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>568.18</t>
         </is>
       </c>
       <c r="L67" s="6" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -7937,26 +7937,26 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I68" s="4" t="n">
         <v>0</v>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -7997,26 +7997,26 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="I69" s="6" t="n">
         <v>0</v>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -8057,26 +8057,26 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>362</v>
+        <v>75</v>
       </c>
       <c r="I70" s="4" t="n">
         <v>0</v>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -8117,26 +8117,26 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>75</v>
+        <v>362</v>
       </c>
       <c r="I71" s="6" t="n">
         <v>0</v>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -8177,26 +8177,26 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I72" s="4" t="n">
         <v>0</v>
@@ -8227,7 +8227,7 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -8237,26 +8237,26 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="I73" s="6" t="n">
         <v>0</v>
@@ -8287,7 +8287,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -8297,26 +8297,26 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>104</v>
+        <v>252</v>
       </c>
       <c r="I74" s="4" t="n">
         <v>0</v>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -8357,26 +8357,26 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -8417,26 +8417,26 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>63</v>
+        <v>643</v>
       </c>
       <c r="I76" s="4" t="n">
         <v>0</v>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -8477,26 +8477,26 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>103</v>
+        <v>543</v>
       </c>
       <c r="I77" s="6" t="n">
         <v>0</v>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -8537,26 +8537,26 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="I78" s="4" t="n">
         <v>0</v>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -8657,26 +8657,26 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I80" s="4" t="n">
         <v>0</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01288</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -8717,26 +8717,26 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>240</v>
+        <v>63</v>
       </c>
       <c r="I81" s="6" t="n">
         <v>0</v>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01310</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -8777,26 +8777,26 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>716</v>
+        <v>103</v>
       </c>
       <c r="I82" s="4" t="n">
         <v>0</v>
@@ -8827,36 +8827,36 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01341</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Cathiard Vineyard</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="I83" s="6" t="n">
         <v>0</v>
@@ -8887,36 +8887,36 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01350</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="I84" s="4" t="n">
         <v>0</v>
@@ -8947,62 +8947,362 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
+          <t>CM-26-01167</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Pétrus</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>Château Pétrus</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="I85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01288</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Chambertin Clos de Bèze</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Armand Rousseau</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01310</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Georges Roumier</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>716</v>
+      </c>
+      <c r="I87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01341</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>🟨</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Cabernet Sauvignon</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>Cathiard Vineyard</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01349</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>🟨</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Chambertin Clos de Bèze</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Bruno Clair</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="I89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
           <t>CM-25-02438</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>🟣</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>DRC Romanée Conti</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="F90" s="4" t="inlineStr">
         <is>
           <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="G90" s="4" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="H85" s="6" t="n">
+      <c r="H90" s="4" t="n">
         <v>410</v>
       </c>
-      <c r="I85" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="6" t="inlineStr">
+      <c r="I90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K85" s="6" t="inlineStr">
+      <c r="K90" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L85" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" s="6" t="n">
+      <c r="L90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N85"/>
+  <autoFilter ref="A3:N90"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-11 14:07  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-13 08:18  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00771</t>
+          <t>CM-26-01439</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -974,48 +974,48 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>10'123.30</t>
+          <t>23'465.00</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.5453</v>
+        <v>0.4997</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1202</v>
+        <v>0.2785</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3753</v>
+        <v>0.4112</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -1024,58 +1024,58 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00293</t>
+          <t>CM-26-01461</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Latour (Ex-Château)</t>
+          <t>Côte Rôtie La Landonne</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
         <v>31</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>9.68%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>51'964.65</t>
+          <t>8'968.19</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1938</v>
+        <v>0.5807</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.6169</v>
+        <v>0.1065</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.363</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00724</t>
+          <t>CM-26-00771</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1094,48 +1094,48 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Cheval Blanc</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Cheval Blanc</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>53'840.62</t>
+          <t>10'123.30</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1698</v>
+        <v>0.5453</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6391</v>
+        <v>0.1202</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3575</v>
+        <v>0.3753</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1144,58 +1144,58 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01431</t>
+          <t>CM-26-00293</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Latour (Ex-Château)</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>4'375.02</t>
+          <t>51'964.65</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.5357</v>
+        <v>0.1938</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0519</v>
+        <v>0.6169</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3422</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1204,58 +1204,58 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01429</t>
+          <t>CM-26-00724</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Cheval Blanc</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Château Cheval Blanc</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>7'787.54</t>
+          <t>53'840.62</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.4997</v>
+        <v>0.1698</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0924</v>
+        <v>0.6391</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3368</v>
+        <v>0.3575</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1264,58 +1264,58 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00871</t>
+          <t>CM-26-01431</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>29'483.52</t>
+          <t>4'317.50</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.5357</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.35</v>
+        <v>0.0513</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.3293</v>
+        <v>0.3419</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1324,58 +1324,58 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02625</t>
+          <t>CM-26-01429</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Rumbo al Norte</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Bodega Comando G</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>37'837.84</t>
+          <t>6'652.43</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.2472</v>
+        <v>0.4997</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.4492</v>
+        <v>0.079</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.328</v>
+        <v>0.3314</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1384,58 +1384,58 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-00871</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Chambertin Très Vieilles Vignes</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>10'637.89</t>
+          <t>29'483.52</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.4613</v>
+        <v>0.3155</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1263</v>
+        <v>0.35</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3273</v>
+        <v>0.3293</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-25-02625</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1454,48 +1454,48 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Rumbo al Norte</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Bodega Comando G</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>3'508.63</t>
+          <t>37'837.84</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4895</v>
+        <v>0.2472</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.4492</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3104</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1504,58 +1504,58 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.3827</v>
+        <v>0.4613</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1902</v>
+        <v>0.1263</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.3057</v>
+        <v>0.3273</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1574,48 +1574,48 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>26'801.63</t>
+          <t>3'508.63</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.2322</v>
+        <v>0.4895</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.3182</v>
+        <v>0.0417</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.2666</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1624,58 +1624,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>20'502.14</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.2771</v>
+        <v>0.3827</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2434</v>
+        <v>0.1902</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2636</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1694,48 +1694,48 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>34'832.71</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.2142</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.4135</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2585</v>
+        <v>0.2939</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1744,58 +1744,58 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>26'801.63</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.1224</v>
+        <v>0.2322</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.4309</v>
+        <v>0.3182</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2458</v>
+        <v>0.2666</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1804,58 +1804,58 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>76</v>
+        <v>195</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>20'502.14</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.3155</v>
+        <v>0.2771</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0683</v>
+        <v>0.2434</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2166</v>
+        <v>0.2636</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1884,38 +1884,38 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.2609</v>
+        <v>0.1278</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1399</v>
+        <v>0.4545</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2125</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1924,58 +1924,58 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2501</v>
+        <v>0.1224</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1529</v>
+        <v>0.4309</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2112</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1984,58 +1984,58 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>21'358.58</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1692</v>
+        <v>0.3155</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.2535</v>
+        <v>0.0683</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2029</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2044,39 +2044,39 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -2085,17 +2085,17 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>9'735.26</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
         <v>0.2609</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1156</v>
+        <v>0.1399</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2028</v>
+        <v>0.2125</v>
       </c>
     </row>
   </sheetData>
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 04 May 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 06 May 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-11 14:07  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-13 08:18  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,31 +2221,31 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01431</t>
+          <t>CM-26-01439</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -2254,178 +2254,178 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>4'375.02</t>
+          <t>23'465.00</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.5357</v>
+        <v>0.4997</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.0519</v>
+        <v>0.2785</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.3422</v>
+        <v>0.4112</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01429</t>
+          <t>CM-26-01461</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Côte Rôtie La Landonne</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>9.68%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>7'787.54</t>
+          <t>8'968.19</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.4997</v>
+        <v>0.5807</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.0924</v>
+        <v>0.1065</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.3368</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-26-01431</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>21'358.58</t>
+          <t>4'317.50</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1692</v>
+        <v>0.5357</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2535</v>
+        <v>0.0513</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2029</v>
+        <v>0.3419</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01439</t>
+          <t>CM-26-01429</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -2434,34 +2434,34 @@
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>15'600.00</t>
+          <t>6'652.43</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1668</v>
+        <v>0.4997</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1852</v>
+        <v>0.079</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1742</v>
+        <v>0.3314</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
@@ -2497,30 +2497,330 @@
         <v>112</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>5'486.82</t>
+          <t>34'832.71</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0534</v>
+        <v>0.2142</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.4135</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.0581</v>
+        <v>0.2939</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01423</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Meursault Blanc</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Coche-Dury</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>2.82%</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>21'358.58</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>0.1692</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>0.2535</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>0.2029</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01477</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Chambolle-Musigny Les Amoureuses</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01479</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01480</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01482</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N8"/>
+  <autoFilter ref="A3:N13"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2535,7 +2835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2557,14 +2857,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 11 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 13 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-11 14:07  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-13 08:18  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2642,31 +2942,31 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01431</t>
+          <t>CM-26-01439</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -2675,218 +2975,218 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>4'375.02</t>
+          <t>23'465.00</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.5357</v>
+        <v>0.4997</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.0519</v>
+        <v>0.2785</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.3422</v>
+        <v>0.4112</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01429</t>
+          <t>CM-26-01461</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Côte Rôtie La Landonne</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>9.68%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>7'787.54</t>
+          <t>8'968.19</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.4997</v>
+        <v>0.5807</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.0924</v>
+        <v>0.1065</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.3368</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-01431</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>10'637.89</t>
+          <t>4'317.50</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.4613</v>
+        <v>0.5357</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1263</v>
+        <v>0.0513</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3273</v>
+        <v>0.3419</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-26-01429</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>21'358.58</t>
+          <t>6'652.43</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1692</v>
+        <v>0.4997</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2535</v>
+        <v>0.079</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2029</v>
+        <v>0.3314</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -2901,7 +3201,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -2915,38 +3215,38 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>179</v>
+        <v>26</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>14'592.69</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.201</v>
+        <v>0.4613</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1732</v>
+        <v>0.1263</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1899</v>
+        <v>0.3273</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -2956,57 +3256,57 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>26'268.00</t>
+          <t>34'832.71</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0888</v>
+        <v>0.2142</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.3118</v>
+        <v>0.4135</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.178</v>
+        <v>0.2939</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01439</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -3016,57 +3316,57 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>15'600.00</t>
+          <t>21'358.58</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1668</v>
+        <v>0.1692</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1852</v>
+        <v>0.2535</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1742</v>
+        <v>0.2029</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01219</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -3076,177 +3376,177 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>221</v>
+        <v>179</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>6</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>16'099.11</t>
+          <t>14'592.69</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1626</v>
+        <v>0.201</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1911</v>
+        <v>0.1732</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.174</v>
+        <v>0.1899</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01284</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>8'112.00</t>
+          <t>26'268.00</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1332</v>
+        <v>0.0888</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0963</v>
+        <v>0.3118</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1184</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-01219</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>96</v>
+        <v>221</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>16'099.11</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1248</v>
+        <v>0.1626</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0684</v>
+        <v>0.1911</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1022</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01320</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3256,48 +3556,48 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>4'696.54</t>
+          <t>8'112.00</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.132</v>
+        <v>0.1332</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0558</v>
+        <v>0.0963</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1015</v>
+        <v>0.1184</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3306,7 +3606,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01376</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -3316,117 +3616,117 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Bollinger</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>348</v>
+        <v>96</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>14'566.45</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0516</v>
+        <v>0.1248</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.1729</v>
+        <v>0.0684</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1001</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01320</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>235</v>
+        <v>91</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2'738.04</t>
+          <t>4'696.54</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.132</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0325</v>
+        <v>0.0558</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0897</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -3436,67 +3736,67 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>112</v>
+        <v>348</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>5'486.82</t>
+          <t>14'566.45</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0534</v>
+        <v>0.0516</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.1729</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0581</v>
+        <v>0.1001</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -3506,38 +3806,38 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>100</v>
+        <v>235</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>3'049.20</t>
+          <t>2'738.04</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.06</v>
+        <v>0.1278</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0362</v>
+        <v>0.0325</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0505</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3546,17 +3846,17 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -3566,38 +3866,38 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>257</v>
+        <v>100</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>3'382.19</t>
+          <t>3'049.20</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0468</v>
+        <v>0.06</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0401</v>
+        <v>0.0362</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0441</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -3606,7 +3906,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3616,12 +3916,12 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -3635,48 +3935,48 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>323</v>
+        <v>257</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2'912.26</t>
+          <t>3'382.19</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.0468</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0346</v>
+        <v>0.0401</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0362</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-01265</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -3695,89 +3995,89 @@
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>280</v>
+        <v>323</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>568.18</t>
+          <t>2'912.26</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0216</v>
+        <v>0.0372</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0067</v>
+        <v>0.0346</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0156</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01288</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>568.18</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -3786,7 +4086,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01310</t>
+          <t>CM-26-01288</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -3796,26 +4096,26 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>716</v>
+        <v>240</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
@@ -3846,36 +4146,36 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01341</t>
+          <t>CM-26-01310</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Cathiard Vineyard</t>
+          <t>Domaine Georges Roumier</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>91</v>
+        <v>716</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>0</v>
@@ -3906,62 +4206,242 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
+          <t>CM-26-01341</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>🟨</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Cabernet Sauvignon</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Cathiard Vineyard</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
           <t>CM-26-01349</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>🟨</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Domaine Bruno Clair</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H26" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="I25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
+      <c r="I26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K25" s="6" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="6" t="n">
+      <c r="L26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01477</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Chambolle-Musigny Les Amoureuses</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01479</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N25"/>
+  <autoFilter ref="A3:N28"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3976,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4005,7 +4485,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-11 14:07  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-13 08:18  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4927,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00771</t>
+          <t>CM-26-01439</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -4457,48 +4937,48 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>10'123.30</t>
+          <t>23'465.00</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.5453</v>
+        <v>0.4997</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1202</v>
+        <v>0.2785</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3753</v>
+        <v>0.4112</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -4507,58 +4987,58 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00293</t>
+          <t>CM-26-01461</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Latour (Ex-Château)</t>
+          <t>Côte Rôtie La Landonne</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
         <v>31</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>9.68%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>51'964.65</t>
+          <t>8'968.19</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1938</v>
+        <v>0.5807</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.6169</v>
+        <v>0.1065</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.363</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -4567,7 +5047,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00724</t>
+          <t>CM-26-00771</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -4577,48 +5057,48 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Cheval Blanc</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Cheval Blanc</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>53'840.62</t>
+          <t>10'123.30</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1698</v>
+        <v>0.5453</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6391</v>
+        <v>0.1202</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3575</v>
+        <v>0.3753</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -4627,58 +5107,58 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01431</t>
+          <t>CM-26-00293</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Latour (Ex-Château)</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>4'375.02</t>
+          <t>51'964.65</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.5357</v>
+        <v>0.1938</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0519</v>
+        <v>0.6169</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3422</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -4687,58 +5167,58 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01429</t>
+          <t>CM-26-00724</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Cheval Blanc</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Château Cheval Blanc</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>7'787.54</t>
+          <t>53'840.62</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.4997</v>
+        <v>0.1698</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0924</v>
+        <v>0.6391</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3368</v>
+        <v>0.3575</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -4747,58 +5227,58 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00871</t>
+          <t>CM-26-01431</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>29'483.52</t>
+          <t>4'317.50</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.5357</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.35</v>
+        <v>0.0513</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.3293</v>
+        <v>0.3419</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -4807,58 +5287,58 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02625</t>
+          <t>CM-26-01429</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Rumbo al Norte</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Bodega Comando G</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>37'837.84</t>
+          <t>6'652.43</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.2472</v>
+        <v>0.4997</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.4492</v>
+        <v>0.079</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.328</v>
+        <v>0.3314</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -4867,58 +5347,58 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-00871</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Chambertin Très Vieilles Vignes</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>10'637.89</t>
+          <t>29'483.52</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.4613</v>
+        <v>0.3155</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1263</v>
+        <v>0.35</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3273</v>
+        <v>0.3293</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -4927,7 +5407,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-25-02625</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -4937,48 +5417,48 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Rumbo al Norte</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Bodega Comando G</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>3'508.63</t>
+          <t>37'837.84</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4895</v>
+        <v>0.2472</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.4492</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3104</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -4987,58 +5467,58 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.3827</v>
+        <v>0.4613</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1902</v>
+        <v>0.1263</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.3057</v>
+        <v>0.3273</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -5047,7 +5527,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -5057,48 +5537,48 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>26'801.63</t>
+          <t>3'508.63</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.2322</v>
+        <v>0.4895</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.3182</v>
+        <v>0.0417</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.2666</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -5107,58 +5587,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>20'502.14</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.2771</v>
+        <v>0.3827</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2434</v>
+        <v>0.1902</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2636</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -5167,7 +5647,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -5177,48 +5657,48 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>34'832.71</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.2142</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.4135</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2585</v>
+        <v>0.2939</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -5227,58 +5707,58 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>26'801.63</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.1224</v>
+        <v>0.2322</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.4309</v>
+        <v>0.3182</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2458</v>
+        <v>0.2666</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -5287,58 +5767,58 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>76</v>
+        <v>195</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>20'502.14</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.3155</v>
+        <v>0.2771</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0683</v>
+        <v>0.2434</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2166</v>
+        <v>0.2636</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -5347,7 +5827,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -5357,7 +5837,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -5367,38 +5847,38 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.2609</v>
+        <v>0.1278</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1399</v>
+        <v>0.4545</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2125</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5407,58 +5887,58 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2501</v>
+        <v>0.1224</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1529</v>
+        <v>0.4309</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2112</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5467,58 +5947,58 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>21'358.58</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1692</v>
+        <v>0.3155</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.2535</v>
+        <v>0.0683</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2029</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5527,39 +6007,39 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -5568,17 +6048,17 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>9'735.26</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
         <v>0.2609</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1156</v>
+        <v>0.1399</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2028</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5587,58 +6067,58 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00553</t>
+          <t>CM-26-00774</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
+          <t>La Grande Rue</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Francois Lamarche</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>167</v>
+        <v>24</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>37'269.73</t>
+          <t>12'881.25</t>
         </is>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.036</v>
+        <v>0.2501</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.4424</v>
+        <v>0.1529</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1986</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5647,17 +6127,17 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03240</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -5667,38 +6147,38 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>245</v>
+        <v>71</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>12'603.94</t>
+          <t>21'358.58</t>
         </is>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.2202</v>
+        <v>0.1692</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.1496</v>
+        <v>0.2535</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.192</v>
+        <v>0.2029</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -5707,58 +6187,58 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>179</v>
+        <v>92</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>14'592.69</t>
+          <t>9'735.26</t>
         </is>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.201</v>
+        <v>0.2609</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1732</v>
+        <v>0.1156</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.1899</v>
+        <v>0.2028</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -5767,7 +6247,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00844</t>
+          <t>CM-26-00553</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -5777,48 +6257,48 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="I32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>10'599.18</t>
+          <t>37'269.73</t>
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.222</v>
+        <v>0.036</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.1258</v>
+        <v>0.4424</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1835</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -5827,58 +6307,58 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-25-03240</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Larcis Ducasse</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>135</v>
+        <v>245</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>26'268.00</t>
+          <t>12'603.94</t>
         </is>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.0888</v>
+        <v>0.2202</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.3118</v>
+        <v>0.1496</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.178</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -5887,58 +6367,58 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01439</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>36</v>
+        <v>179</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>15'600.00</t>
+          <t>14'592.69</t>
         </is>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1668</v>
+        <v>0.201</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1852</v>
+        <v>0.1732</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1742</v>
+        <v>0.1899</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -5947,58 +6427,58 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01219</t>
+          <t>CM-26-00844</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>221</v>
+        <v>27</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>16'099.11</t>
+          <t>10'599.18</t>
         </is>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.1626</v>
+        <v>0.222</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1911</v>
+        <v>0.1258</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.174</v>
+        <v>0.1835</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6007,58 +6487,58 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02431</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>11'961.88</t>
+          <t>26'268.00</t>
         </is>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.1926</v>
+        <v>0.0888</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.142</v>
+        <v>0.3118</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.1724</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -6067,58 +6547,58 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00730</t>
+          <t>CM-26-01219</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>La Violette</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Château La Violette</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>95</v>
+        <v>221</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>17'433.26</t>
+          <t>16'099.11</t>
         </is>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.1266</v>
+        <v>0.1626</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.2069</v>
+        <v>0.1911</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.1587</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -6127,58 +6607,58 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02972</t>
+          <t>CM-25-02431</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>1'269.76</t>
+          <t>11'961.88</t>
         </is>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.2466</v>
+        <v>0.1926</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.0151</v>
+        <v>0.142</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.154</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -6187,58 +6667,58 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02689</t>
+          <t>CM-26-00730</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges la Perrière</t>
+          <t>La Violette</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Domaine Gouges Henri</t>
+          <t>Château La Violette</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>3'300.53</t>
+          <t>17'433.26</t>
         </is>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.222</v>
+        <v>0.1266</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.0392</v>
+        <v>0.2069</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1489</v>
+        <v>0.1587</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -6247,58 +6727,58 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-25-02972</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Finca Piedra Infinita</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>24'547.24</t>
+          <t>1'277.97</t>
         </is>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.2466</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.2914</v>
+        <v>0.0152</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.1443</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -6307,58 +6787,58 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00594</t>
+          <t>CM-25-02689</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mordorée</t>
+          <t>Nuits Saint Georges la Perrière</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Maison M. Chapoutier</t>
+          <t>Domaine Gouges Henri</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>12'780.81</t>
+          <t>3'300.53</t>
         </is>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.1362</v>
+        <v>0.222</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1517</v>
+        <v>0.0392</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1424</v>
+        <v>0.1489</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -6367,58 +6847,58 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02637</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Hommage à Jacques Perrin</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Château de Beaucastel</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="I42" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>1'587.81</t>
+          <t>24'206.56</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.0462</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.0188</v>
+        <v>0.2874</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.136</v>
+        <v>0.1427</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -6427,58 +6907,58 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-00594</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Côte Rôtie La Mordorée</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Maison M. Chapoutier</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>313</v>
+        <v>88</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>22'583.46</t>
+          <t>12'780.81</t>
         </is>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.0192</v>
+        <v>0.1362</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.2681</v>
+        <v>0.1517</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1188</v>
+        <v>0.1424</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -6487,7 +6967,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01284</t>
+          <t>CM-25-02637</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -6497,48 +6977,48 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Hommage à Jacques Perrin</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Château de Beaucastel</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="I44" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>8'112.00</t>
+          <t>1'587.81</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.1332</v>
+        <v>0.2142</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.0963</v>
+        <v>0.0188</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.1184</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -6547,58 +7027,58 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02474</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Mazoyères-Chambertin</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Arnaud Mortet</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>150</v>
+        <v>313</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>9'311.67</t>
+          <t>22'583.46</t>
         </is>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.12</v>
+        <v>0.0192</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.1105</v>
+        <v>0.2681</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.1162</v>
+        <v>0.1188</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -6607,58 +7087,58 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>12'848.80</t>
+          <t>8'112.00</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.081</v>
+        <v>0.1332</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.1525</v>
+        <v>0.0963</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.1096</v>
+        <v>0.1184</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -6667,58 +7147,58 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00779</t>
+          <t>CM-25-02474</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Mazoyères-Chambertin</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Arnaud Mortet</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>10'707.33</t>
+          <t>9'311.67</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.0936</v>
+        <v>0.12</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.1271</v>
+        <v>0.1105</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.107</v>
+        <v>0.1162</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -6727,58 +7207,58 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02628</t>
+          <t>CM-26-00963</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Grillet Blanc</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Château Grillet</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>6'957.56</t>
+          <t>12'848.80</t>
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.1218</v>
+        <v>0.081</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.1525</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.1061</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -6787,58 +7267,58 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-26-00779</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>317</v>
+        <v>64</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>12'118.06</t>
+          <t>10'707.33</t>
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.0756</v>
+        <v>0.0936</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.1439</v>
+        <v>0.1271</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.1029</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -6847,58 +7327,58 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00772</t>
+          <t>CM-25-02628</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Grillet Blanc</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Château Grillet</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>10'109.38</t>
+          <t>6'957.56</t>
         </is>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.0912</v>
+        <v>0.1218</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.12</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.1027</v>
+        <v>0.1061</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -6907,58 +7387,58 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>96</v>
+        <v>317</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>12'118.06</t>
         </is>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0.1248</v>
+        <v>0.0756</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.0684</v>
+        <v>0.1439</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.1022</v>
+        <v>0.1029</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -6967,58 +7447,58 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01320</t>
+          <t>CM-26-00772</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>91</v>
+        <v>198</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>4'696.54</t>
+          <t>10'109.38</t>
         </is>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.132</v>
+        <v>0.0912</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.0558</v>
+        <v>0.12</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.1015</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -7027,7 +7507,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01376</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -7037,48 +7517,48 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Bollinger</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>348</v>
+        <v>96</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>14'566.45</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0.0516</v>
+        <v>0.1248</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.1729</v>
+        <v>0.0684</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.1001</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -7087,58 +7567,58 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-26-01320</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>487</v>
+        <v>91</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>4'696.54</t>
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.132</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.1716</v>
+        <v>0.0558</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.091</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -7147,58 +7627,58 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>235</v>
+        <v>348</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2'738.04</t>
+          <t>14'566.45</t>
         </is>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.0516</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.0325</v>
+        <v>0.1729</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.0897</v>
+        <v>0.1001</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -7207,7 +7687,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00658</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -7217,48 +7697,48 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Assortment de Grands Crus (12 bottles)</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Domaine Ponsot</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>68</v>
+        <v>487</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>7'018.00</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.0882</v>
+        <v>0.0372</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.1716</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.0862</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -7267,58 +7747,58 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03004</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>476</v>
+        <v>235</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>10'547.81</t>
+          <t>2'738.04</t>
         </is>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.0504</v>
+        <v>0.1278</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.1252</v>
+        <v>0.0325</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.0803</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -7327,7 +7807,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02535</t>
+          <t>CM-26-00658</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -7337,48 +7817,48 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Meursault Clos des Bouchers</t>
+          <t>Assortment de Grands Crus (12 bottles)</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Domaine Jean Marc Roulot</t>
+          <t>Domaine Ponsot</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>268</v>
+        <v>68</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>10'885.80</t>
+          <t>7'018.00</t>
         </is>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.045</v>
+        <v>0.0882</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.1292</v>
+        <v>0.0833</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -7387,58 +7867,58 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00483</t>
+          <t>CM-25-03004</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Pie Franco</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Bodegas Casa Castillo</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>53</v>
+        <v>476</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>690.03</t>
+          <t>10'547.81</t>
         </is>
       </c>
       <c r="L59" s="6" t="n">
-        <v>0.1134</v>
+        <v>0.0504</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1252</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.0713</v>
+        <v>0.0803</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -7447,58 +7927,58 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02609</t>
+          <t>CM-25-02535</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Clos de la Roche</t>
+          <t>Meursault Clos des Bouchers</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Lignier</t>
+          <t>Domaine Jean Marc Roulot</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>5'003.90</t>
+          <t>10'885.80</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.0774</v>
+        <v>0.045</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.0594</v>
+        <v>0.1292</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.0702</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -7507,58 +7987,58 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-00483</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Pie Franco</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Bodegas Casa Castillo</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>112</v>
+        <v>53</v>
       </c>
       <c r="I61" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>5'486.82</t>
+          <t>690.03</t>
         </is>
       </c>
       <c r="L61" s="6" t="n">
-        <v>0.0534</v>
+        <v>0.1134</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.0581</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -7567,58 +8047,58 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-25-02609</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Clos de la Roche</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine Georges Lignier</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>100</v>
+        <v>233</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>3'049.20</t>
+          <t>5'003.90</t>
         </is>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.06</v>
+        <v>0.0774</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.0362</v>
+        <v>0.0594</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0.0505</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -7627,17 +8107,17 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -7647,38 +8127,38 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>257</v>
+        <v>100</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>3'382.19</t>
+          <t>3'049.20</t>
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>0.0468</v>
+        <v>0.06</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>0.0401</v>
+        <v>0.0362</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>0.0441</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -7687,7 +8167,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -7697,12 +8177,12 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -7716,29 +8196,29 @@
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>323</v>
+        <v>257</v>
       </c>
       <c r="I64" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2'912.26</t>
+          <t>3'382.19</t>
         </is>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.0468</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.0346</v>
+        <v>0.0401</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.0362</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -7747,58 +8227,58 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00851</t>
+          <t>CM-26-01265</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>4'218.04</t>
+          <t>2'912.26</t>
         </is>
       </c>
       <c r="L65" s="6" t="n">
-        <v>0.0222</v>
+        <v>0.0372</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>0.0501</v>
+        <v>0.0346</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>0.0334</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -7807,58 +8287,58 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02656</t>
+          <t>CM-26-00851</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Weingut Markus Molitor</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>1'865.44</t>
+          <t>4'218.04</t>
         </is>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.0222</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.0221</v>
+        <v>0.0501</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0334</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -7867,58 +8347,58 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-25-02656</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Weingut Markus Molitor</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>280</v>
+        <v>324</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>568.18</t>
+          <t>1'865.44</t>
         </is>
       </c>
       <c r="L67" s="6" t="n">
-        <v>0.0216</v>
+        <v>0.0372</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>0.0067</v>
+        <v>0.0221</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>0.0156</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -7927,58 +8407,58 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>129</v>
+        <v>280</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>568.18</t>
         </is>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -7987,7 +8467,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -7997,26 +8477,26 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>11</v>
+        <v>362</v>
       </c>
       <c r="I69" s="6" t="n">
         <v>0</v>
@@ -8047,7 +8527,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -8057,26 +8537,26 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>75</v>
+        <v>543</v>
       </c>
       <c r="I70" s="4" t="n">
         <v>0</v>
@@ -8107,7 +8587,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -8117,26 +8597,26 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>362</v>
+        <v>92</v>
       </c>
       <c r="I71" s="6" t="n">
         <v>0</v>
@@ -8167,7 +8647,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -8177,26 +8657,26 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I72" s="4" t="n">
         <v>0</v>
@@ -8227,7 +8707,7 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -8237,26 +8717,26 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="I73" s="6" t="n">
         <v>0</v>
@@ -8287,7 +8767,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -8312,11 +8792,11 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>252</v>
+        <v>42</v>
       </c>
       <c r="I74" s="4" t="n">
         <v>0</v>
@@ -8347,7 +8827,7 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -8357,26 +8837,26 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -8407,7 +8887,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -8417,7 +8897,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -8427,16 +8907,16 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>643</v>
+        <v>126</v>
       </c>
       <c r="I76" s="4" t="n">
         <v>0</v>
@@ -8467,7 +8947,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -8477,26 +8957,26 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>543</v>
+        <v>252</v>
       </c>
       <c r="I77" s="6" t="n">
         <v>0</v>
@@ -8527,7 +9007,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -8537,26 +9017,26 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="I78" s="4" t="n">
         <v>0</v>
@@ -8587,7 +9067,7 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -8597,26 +9077,26 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>26</v>
+        <v>643</v>
       </c>
       <c r="I79" s="6" t="n">
         <v>0</v>
@@ -8647,7 +9127,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -8657,26 +9137,26 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I80" s="4" t="n">
         <v>0</v>
@@ -8707,7 +9187,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -8717,26 +9197,26 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="I81" s="6" t="n">
         <v>0</v>
@@ -8767,7 +9247,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -8777,26 +9257,26 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="I82" s="4" t="n">
         <v>0</v>
@@ -8827,7 +9307,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -8837,17 +9317,17 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
@@ -8856,7 +9336,7 @@
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="I83" s="6" t="n">
         <v>0</v>
@@ -8887,7 +9367,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -8902,7 +9382,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -8912,11 +9392,11 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="I84" s="4" t="n">
         <v>0</v>
@@ -8947,7 +9427,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -8957,26 +9437,26 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="I85" s="6" t="n">
         <v>0</v>
@@ -9007,7 +9487,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01288</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -9017,26 +9497,26 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>240</v>
+        <v>104</v>
       </c>
       <c r="I86" s="4" t="n">
         <v>0</v>
@@ -9067,7 +9547,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01310</t>
+          <t>CM-26-01288</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -9077,26 +9557,26 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>716</v>
+        <v>240</v>
       </c>
       <c r="I87" s="6" t="n">
         <v>0</v>
@@ -9127,36 +9607,36 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01341</t>
+          <t>CM-26-01310</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Cathiard Vineyard</t>
+          <t>Domaine Georges Roumier</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>91</v>
+        <v>716</v>
       </c>
       <c r="I88" s="4" t="n">
         <v>0</v>
@@ -9187,7 +9667,7 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01349</t>
+          <t>CM-26-01341</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -9197,26 +9677,26 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Cathiard Vineyard</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I89" s="6" t="n">
         <v>0</v>
@@ -9247,62 +9727,362 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
+          <t>CM-26-01349</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>🟨</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Chambertin Clos de Bèze</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Bruno Clair</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01477</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Chambolle-Musigny Les Amoureuses</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="I91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01479</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01480</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="I93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01482</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
           <t>CM-25-02438</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>🟣</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>DRC Romanée Conti</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
-      <c r="G90" s="4" t="inlineStr">
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="H90" s="4" t="n">
+      <c r="H95" s="6" t="n">
         <v>410</v>
       </c>
-      <c r="I90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
+      <c r="I95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K90" s="4" t="inlineStr">
+      <c r="K95" s="6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="4" t="n">
+      <c r="L95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="6" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N90"/>
+  <autoFilter ref="A3:N95"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-13 08:18  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-18 08:43  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00749</t>
+          <t>CM-26-01439</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -734,48 +734,48 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>9.33%</t>
+          <t>11.11%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>39'362.80</t>
+          <t>42'341.00</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.5597</v>
+        <v>0.6665</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.4673</v>
+        <v>0.5026</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.6009</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -784,58 +784,58 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02970</t>
+          <t>CM-26-00749</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita Gravascal</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>512</v>
+        <v>75</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>9.33%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>48'472.47</t>
+          <t>39'362.80</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3869</v>
+        <v>0.5597</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.5754</v>
+        <v>0.4673</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4623</v>
+        <v>0.5227000000000001</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -844,7 +844,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01175</t>
+          <t>CM-26-01461</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Côte Rôtie La Landonne</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -869,33 +869,33 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>4</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>12.90%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>15'204.93</t>
+          <t>11'271.04</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.6485</v>
+        <v>0.7738</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1805</v>
+        <v>0.1338</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4613</v>
+        <v>0.5178</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -904,58 +904,58 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02472</t>
+          <t>CM-25-02970</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Clos de Vougeot</t>
+          <t>Finca Piedra Infinita Gravascal</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leroy</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>6.45%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>84'240.00</t>
+          <t>48'472.47</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0516</v>
+        <v>0.3869</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>1</v>
+        <v>0.5754</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.431</v>
+        <v>0.4623</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -964,58 +964,58 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01439</t>
+          <t>CM-26-01175</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Côte Rôtie La Mouline</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>10.81%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>23'465.00</t>
+          <t>15'204.93</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.4997</v>
+        <v>0.6485</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2785</v>
+        <v>0.1805</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.4112</v>
+        <v>0.4613</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -1024,58 +1024,58 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01461</t>
+          <t>CM-25-02472</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Landonne</t>
+          <t>Clos de Vougeot</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine Leroy</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>9.68%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>8'968.19</t>
+          <t>84'240.00</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.5807</v>
+        <v>0.0516</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1065</v>
+        <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.391</v>
+        <v>0.431</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>4'317.50</t>
+          <t>4'317.52</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1694,48 +1694,48 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>34'832.71</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.0324</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4135</v>
+        <v>0.6896</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2939</v>
+        <v>0.2953</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1744,58 +1744,58 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>181</v>
+        <v>112</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>26'801.63</t>
+          <t>34'832.71</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2322</v>
+        <v>0.2142</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.3182</v>
+        <v>0.4135</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2666</v>
+        <v>0.2939</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1804,58 +1804,58 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>20'502.14</t>
+          <t>43'696.73</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2771</v>
+        <v>0.1332</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.2434</v>
+        <v>0.5187</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2636</v>
+        <v>0.2874</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1864,58 +1864,58 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>47</v>
+        <v>181</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>26'801.63</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.2322</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.4545</v>
+        <v>0.3182</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2585</v>
+        <v>0.2666</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1924,58 +1924,58 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>49</v>
+        <v>195</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>20'502.14</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.1224</v>
+        <v>0.2771</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.4309</v>
+        <v>0.2434</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2458</v>
+        <v>0.2636</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1984,58 +1984,58 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.1278</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0683</v>
+        <v>0.4545</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2166</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2054,48 +2054,48 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2609</v>
+        <v>0.1224</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1399</v>
+        <v>0.4309</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2125</v>
+        <v>0.2458</v>
       </c>
     </row>
   </sheetData>
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 06 May 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 11 May 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-13 08:18  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-18 08:43  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,131 +2221,131 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01439</t>
+          <t>CM-26-01461</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Côte Rôtie La Landonne</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>12.90%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>23'465.00</t>
+          <t>11'271.04</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.4997</v>
+        <v>0.7738</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.2785</v>
+        <v>0.1338</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.4112</v>
+        <v>0.5178</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01461</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Landonne</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>9.68%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>8'968.19</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.5807</v>
+        <v>0.0324</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.1065</v>
+        <v>0.6896</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.391</v>
+        <v>0.2953</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01431</t>
+          <t>CM-26-01486</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2355,177 +2355,177 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>4'317.50</t>
+          <t>3'838.19</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.5357</v>
+        <v>0.2729</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.0513</v>
+        <v>0.0456</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3419</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01429</t>
+          <t>CM-26-01494</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>6'652.43</t>
+          <t>17'751.48</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.4997</v>
+        <v>0.1464</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.079</v>
+        <v>0.2107</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3314</v>
+        <v>0.1721</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01500</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>4</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>34'832.71</t>
+          <t>2'258.69</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.2244</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4135</v>
+        <v>0.0268</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2939</v>
+        <v>0.1454</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-26-01480</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -2535,292 +2535,592 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>21'358.58</t>
+          <t>7'997.08</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1692</v>
+        <v>0.0882</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2535</v>
+        <v>0.0949</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2029</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01477</t>
+          <t>CM-26-01495</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>70</v>
+        <v>393</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4'368.68</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0</v>
+        <v>0.0762</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0</v>
+        <v>0.0519</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0</v>
+        <v>0.0665</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01479</t>
+          <t>CM-26-01481</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3'223.09</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0</v>
+        <v>0.0383</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0</v>
+        <v>0.0582</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01480</t>
+          <t>CM-26-01497</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>48</v>
+        <v>389</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1'046.69</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0</v>
+        <v>0.0124</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
+          <t>CM-26-01477</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Chambolle-Musigny Les Amoureuses</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01479</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
           <t>CM-26-01482</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>💎</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H15" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="I13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="I15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="6" t="n">
+      <c r="L15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01508</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>L'Ermita</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Alvaro Palacios</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01512</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01513</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N13"/>
+  <autoFilter ref="A3:N18"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2857,14 +3157,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 13 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 18 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-13 08:18  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-18 08:43  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2942,7 +3242,7 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
@@ -2978,31 +3278,31 @@
         <v>36</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>11.11%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>23'465.00</t>
+          <t>42'341.00</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.4997</v>
+        <v>0.6665</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.2785</v>
+        <v>0.5026</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.4112</v>
+        <v>0.6009</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
@@ -3038,26 +3338,26 @@
         <v>31</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>9.68%</t>
+          <t>12.90%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>8'968.19</t>
+          <t>11'271.04</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.5807</v>
+        <v>0.7738</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.1065</v>
+        <v>0.1338</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.391</v>
+        <v>0.5178</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -3107,7 +3407,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>4'317.50</t>
+          <t>4'317.52</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
@@ -3182,67 +3482,67 @@
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>26</v>
+        <v>184</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>10'637.89</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.4613</v>
+        <v>0.0324</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1263</v>
+        <v>0.6896</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3273</v>
+        <v>0.2953</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
@@ -3302,11 +3602,11 @@
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -3316,607 +3616,607 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>21'358.58</t>
+          <t>43'696.73</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1692</v>
+        <v>0.1332</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2535</v>
+        <v>0.5187</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2029</v>
+        <v>0.2874</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>179</v>
+        <v>71</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>14'592.69</t>
+          <t>21'358.58</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.201</v>
+        <v>0.1692</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1732</v>
+        <v>0.2535</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1899</v>
+        <v>0.2029</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-26-01486</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>135</v>
+        <v>22</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>26'268.00</t>
+          <t>3'838.19</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0888</v>
+        <v>0.2729</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3118</v>
+        <v>0.0456</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.178</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01219</t>
+          <t>CM-26-01494</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>221</v>
+        <v>41</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>16'099.11</t>
+          <t>17'751.48</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1626</v>
+        <v>0.1464</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1911</v>
+        <v>0.2107</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.174</v>
+        <v>0.1721</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01284</t>
+          <t>CM-26-01500</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>8'112.00</t>
+          <t>2'258.69</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1332</v>
+        <v>0.2244</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0963</v>
+        <v>0.0268</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1184</v>
+        <v>0.1454</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>8'112.00</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1248</v>
+        <v>0.1332</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0684</v>
+        <v>0.0963</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1022</v>
+        <v>0.1184</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01320</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>4'696.54</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.132</v>
+        <v>0.1248</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0558</v>
+        <v>0.0684</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1015</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01376</t>
+          <t>CM-26-01320</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Bollinger</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>348</v>
+        <v>91</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>14'566.45</t>
+          <t>4'696.54</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0516</v>
+        <v>0.132</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1729</v>
+        <v>0.0558</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1001</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>235</v>
+        <v>348</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2'738.04</t>
+          <t>14'566.45</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.0516</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0325</v>
+        <v>0.1729</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0897</v>
+        <v>0.1001</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-26-01480</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>3'049.20</t>
+          <t>7'997.08</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.06</v>
+        <v>0.0882</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.0949</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0505</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -3935,48 +4235,48 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>3'382.19</t>
+          <t>2'738.04</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0468</v>
+        <v>0.1278</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0401</v>
+        <v>0.0325</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0441</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-26-01495</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -3991,107 +4291,107 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>323</v>
+        <v>393</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2'912.26</t>
+          <t>4'368.68</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0762</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0346</v>
+        <v>0.0519</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.0665</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-01481</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>568.18</t>
+          <t>3'223.09</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0216</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0067</v>
+        <v>0.0383</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0156</v>
+        <v>0.0582</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01288</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -4101,292 +4401,292 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3'049.20</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0</v>
+        <v>0.0362</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01310</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>716</v>
+        <v>257</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3'382.19</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0</v>
+        <v>0.0468</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0</v>
+        <v>0.0401</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01341</t>
+          <t>CM-26-01265</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Cathiard Vineyard</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>91</v>
+        <v>323</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2'912.26</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0</v>
+        <v>0.0346</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01349</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>86</v>
+        <v>280</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>568.18</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01477</t>
+          <t>CM-26-01497</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>70</v>
+        <v>389</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1'046.69</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0</v>
+        <v>0.0124</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01479</t>
+          <t>CM-26-01288</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -4396,26 +4696,26 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>0</v>
@@ -4456,7 +4756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N95"/>
+  <dimension ref="A1:N105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4485,7 +4785,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-13 08:18  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-18 08:43  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4987,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00749</t>
+          <t>CM-26-01439</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -4697,48 +4997,48 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>9.33%</t>
+          <t>11.11%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>39'362.80</t>
+          <t>42'341.00</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.5597</v>
+        <v>0.6665</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.4673</v>
+        <v>0.5026</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.6009</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -4747,58 +5047,58 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02970</t>
+          <t>CM-26-00749</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita Gravascal</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>512</v>
+        <v>75</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>9.33%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>48'472.47</t>
+          <t>39'362.80</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3869</v>
+        <v>0.5597</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.5754</v>
+        <v>0.4673</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4623</v>
+        <v>0.5227000000000001</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -4807,7 +5107,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01175</t>
+          <t>CM-26-01461</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -4817,12 +5117,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Côte Rôtie La Landonne</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -4832,33 +5132,33 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>4</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>12.90%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>15'204.93</t>
+          <t>11'271.04</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.6485</v>
+        <v>0.7738</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1805</v>
+        <v>0.1338</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4613</v>
+        <v>0.5178</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -4867,58 +5167,58 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02472</t>
+          <t>CM-25-02970</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Clos de Vougeot</t>
+          <t>Finca Piedra Infinita Gravascal</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leroy</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>6.45%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>84'240.00</t>
+          <t>48'472.47</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0516</v>
+        <v>0.3869</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>1</v>
+        <v>0.5754</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.431</v>
+        <v>0.4623</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -4927,58 +5227,58 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01439</t>
+          <t>CM-26-01175</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Côte Rôtie La Mouline</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>10.81%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>23'465.00</t>
+          <t>15'204.93</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.4997</v>
+        <v>0.6485</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2785</v>
+        <v>0.1805</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.4112</v>
+        <v>0.4613</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -4987,58 +5287,58 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01461</t>
+          <t>CM-25-02472</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Landonne</t>
+          <t>Clos de Vougeot</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine Leroy</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>9.68%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>8'968.19</t>
+          <t>84'240.00</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.5807</v>
+        <v>0.0516</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1065</v>
+        <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.391</v>
+        <v>0.431</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -5268,7 +5568,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>4'317.50</t>
+          <t>4'317.52</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
@@ -5647,7 +5947,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -5657,48 +5957,48 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>34'832.71</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.0324</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4135</v>
+        <v>0.6896</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2939</v>
+        <v>0.2953</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -5707,58 +6007,58 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>181</v>
+        <v>112</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>26'801.63</t>
+          <t>34'832.71</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2322</v>
+        <v>0.2142</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.3182</v>
+        <v>0.4135</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2666</v>
+        <v>0.2939</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -5767,58 +6067,58 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>20'502.14</t>
+          <t>43'696.73</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2771</v>
+        <v>0.1332</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.2434</v>
+        <v>0.5187</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2636</v>
+        <v>0.2874</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -5827,58 +6127,58 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>47</v>
+        <v>181</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>26'801.63</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.2322</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.4545</v>
+        <v>0.3182</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2585</v>
+        <v>0.2666</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5887,58 +6187,58 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>49</v>
+        <v>195</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>20'502.14</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.1224</v>
+        <v>0.2771</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.4309</v>
+        <v>0.2434</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2458</v>
+        <v>0.2636</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5947,58 +6247,58 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.1278</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0683</v>
+        <v>0.4545</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2166</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -6007,7 +6307,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -6017,48 +6317,48 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2609</v>
+        <v>0.1224</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1399</v>
+        <v>0.4309</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2125</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -6067,58 +6367,58 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.2501</v>
+        <v>0.3155</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1529</v>
+        <v>0.0683</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2112</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -6127,7 +6427,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -6137,7 +6437,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -6147,38 +6447,38 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>21'358.58</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1692</v>
+        <v>0.2609</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.2535</v>
+        <v>0.1399</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2029</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6187,58 +6487,58 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-00774</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>La Grande Rue</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Domaine Francois Lamarche</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>9'735.26</t>
+          <t>12'881.25</t>
         </is>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.2609</v>
+        <v>0.2501</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1156</v>
+        <v>0.1529</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2028</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6247,7 +6547,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00553</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -6257,7 +6557,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -6267,38 +6567,38 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>37'269.73</t>
+          <t>21'358.58</t>
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.036</v>
+        <v>0.1692</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.4424</v>
+        <v>0.2535</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1986</v>
+        <v>0.2029</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6307,58 +6607,58 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03240</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>245</v>
+        <v>92</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>12'603.94</t>
+          <t>9'735.26</t>
         </is>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.2202</v>
+        <v>0.2609</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1496</v>
+        <v>0.1156</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.192</v>
+        <v>0.2028</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6367,58 +6667,58 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-26-00553</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>14'592.69</t>
+          <t>37'269.73</t>
         </is>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.201</v>
+        <v>0.036</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1732</v>
+        <v>0.4424</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1899</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6427,58 +6727,58 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00844</t>
+          <t>CM-25-03240</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Château Larcis Ducasse</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>27</v>
+        <v>245</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>10'599.18</t>
+          <t>12'603.94</t>
         </is>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.222</v>
+        <v>0.2202</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1258</v>
+        <v>0.1496</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1835</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6487,58 +6787,58 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>26'268.00</t>
+          <t>14'592.69</t>
         </is>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.0888</v>
+        <v>0.201</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.3118</v>
+        <v>0.1732</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.178</v>
+        <v>0.1899</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -6547,58 +6847,58 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01219</t>
+          <t>CM-26-00844</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>221</v>
+        <v>27</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>16'099.11</t>
+          <t>10'599.18</t>
         </is>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.1626</v>
+        <v>0.222</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1911</v>
+        <v>0.1258</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.174</v>
+        <v>0.1835</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -6607,58 +6907,58 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02431</t>
+          <t>CM-26-01486</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>156</v>
+        <v>22</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>11'961.88</t>
+          <t>3'838.19</t>
         </is>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.1926</v>
+        <v>0.2729</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.142</v>
+        <v>0.0456</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.1724</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -6667,58 +6967,58 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00730</t>
+          <t>CM-26-01219</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>La Violette</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Château La Violette</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>95</v>
+        <v>221</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>17'433.26</t>
+          <t>16'040.28</t>
         </is>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.1266</v>
+        <v>0.1626</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.2069</v>
+        <v>0.1904</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1587</v>
+        <v>0.1737</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -6727,58 +7027,58 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02972</t>
+          <t>CM-25-02431</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>1'277.97</t>
+          <t>11'961.88</t>
         </is>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.2466</v>
+        <v>0.1926</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.0152</v>
+        <v>0.142</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.154</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -6787,58 +7087,58 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02689</t>
+          <t>CM-26-01494</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges la Perrière</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Domaine Gouges Henri</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>135</v>
+        <v>41</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>3'300.53</t>
+          <t>17'751.48</t>
         </is>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.222</v>
+        <v>0.1464</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.0392</v>
+        <v>0.2107</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1489</v>
+        <v>0.1721</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -6847,7 +7147,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-26-00730</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -6857,48 +7157,48 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>La Violette</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château La Violette</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>24'206.56</t>
+          <t>17'433.26</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.1266</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.2874</v>
+        <v>0.2069</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.1427</v>
+        <v>0.1587</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -6907,58 +7207,58 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00594</t>
+          <t>CM-25-02972</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mordorée</t>
+          <t>Finca Piedra Infinita</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Maison M. Chapoutier</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>12'780.81</t>
+          <t>1'277.97</t>
         </is>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.1362</v>
+        <v>0.2466</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.1517</v>
+        <v>0.0152</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1424</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -6967,58 +7267,58 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02637</t>
+          <t>CM-25-02689</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Hommage à Jacques Perrin</t>
+          <t>Nuits Saint Georges la Perrière</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Château de Beaucastel</t>
+          <t>Domaine Gouges Henri</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>1'587.81</t>
+          <t>3'300.53</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.222</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.0188</v>
+        <v>0.0392</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.136</v>
+        <v>0.1489</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -7027,58 +7327,58 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-01500</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>313</v>
+        <v>107</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>22'583.46</t>
+          <t>2'258.69</t>
         </is>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.0192</v>
+        <v>0.2244</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.2681</v>
+        <v>0.0268</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.1188</v>
+        <v>0.1454</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -7087,17 +7387,17 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01284</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -7107,38 +7407,38 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>8'112.00</t>
+          <t>24'206.56</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.1332</v>
+        <v>0.0462</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.0963</v>
+        <v>0.2874</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.1184</v>
+        <v>0.1427</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -7147,7 +7447,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02474</t>
+          <t>CM-26-00594</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -7157,48 +7457,48 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Mazoyères-Chambertin</t>
+          <t>Côte Rôtie La Mordorée</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Arnaud Mortet</t>
+          <t>Maison M. Chapoutier</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>150</v>
+        <v>88</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>9'311.67</t>
+          <t>12'780.81</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.12</v>
+        <v>0.1362</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.1105</v>
+        <v>0.1517</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.1162</v>
+        <v>0.1424</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -7207,58 +7507,58 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-25-02637</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Hommage à Jacques Perrin</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château de Beaucastel</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="I48" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>12'848.80</t>
+          <t>1'587.81</t>
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.081</v>
+        <v>0.2142</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.1525</v>
+        <v>0.0188</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.1096</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -7267,7 +7567,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00779</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -7277,48 +7577,48 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>64</v>
+        <v>313</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>10'707.33</t>
+          <t>22'583.46</t>
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.0936</v>
+        <v>0.0192</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.1271</v>
+        <v>0.2681</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.107</v>
+        <v>0.1188</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -7327,7 +7627,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02628</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -7337,7 +7637,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Grillet Blanc</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -7347,38 +7647,38 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Château Grillet</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>6'957.56</t>
+          <t>8'112.00</t>
         </is>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.1218</v>
+        <v>0.1332</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0963</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.1061</v>
+        <v>0.1184</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -7387,7 +7687,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-25-02474</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -7397,48 +7697,48 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Mazoyères-Chambertin</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Arnaud Mortet</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>317</v>
+        <v>150</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>12'118.06</t>
+          <t>9'311.67</t>
         </is>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0.0756</v>
+        <v>0.12</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.1439</v>
+        <v>0.1105</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.1029</v>
+        <v>0.1162</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -7447,7 +7747,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00772</t>
+          <t>CM-26-00963</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -7457,48 +7757,48 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>10'109.38</t>
+          <t>12'848.80</t>
         </is>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.0912</v>
+        <v>0.081</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.12</v>
+        <v>0.1525</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.1027</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -7507,7 +7807,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-00779</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -7517,48 +7817,48 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>10'707.33</t>
         </is>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0.1248</v>
+        <v>0.0936</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.0684</v>
+        <v>0.1271</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.1022</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -7567,7 +7867,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01320</t>
+          <t>CM-25-02628</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -7577,48 +7877,48 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Grillet Blanc</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Château Grillet</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>91</v>
+        <v>197</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>4'696.54</t>
+          <t>6'957.56</t>
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.132</v>
+        <v>0.1218</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.0558</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.1015</v>
+        <v>0.1061</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -7627,58 +7927,58 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01376</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Bollinger</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>14'566.45</t>
+          <t>12'118.06</t>
         </is>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.0516</v>
+        <v>0.0756</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.1729</v>
+        <v>0.1439</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.1001</v>
+        <v>0.1029</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -7687,7 +7987,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-26-00772</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -7697,48 +7997,48 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>487</v>
+        <v>198</v>
       </c>
       <c r="I56" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>10'109.38</t>
         </is>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.0912</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.1716</v>
+        <v>0.12</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.091</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -7747,58 +8047,58 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>235</v>
+        <v>96</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2'738.04</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.1248</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.0325</v>
+        <v>0.0684</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.0897</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -7807,58 +8107,58 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00658</t>
+          <t>CM-26-01320</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Assortment de Grands Crus (12 bottles)</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Domaine Ponsot</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>7'018.00</t>
+          <t>4'696.54</t>
         </is>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.0882</v>
+        <v>0.132</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.0558</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.0862</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -7867,58 +8167,58 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03004</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>476</v>
+        <v>348</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>10'547.81</t>
+          <t>14'566.45</t>
         </is>
       </c>
       <c r="L59" s="6" t="n">
-        <v>0.0504</v>
+        <v>0.0516</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0.1252</v>
+        <v>0.1729</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.0803</v>
+        <v>0.1001</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -7927,7 +8227,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02535</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -7937,48 +8237,48 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Meursault Clos des Bouchers</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Domaine Jean Marc Roulot</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>268</v>
+        <v>487</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>10'885.80</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.045</v>
+        <v>0.0372</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.1292</v>
+        <v>0.1716</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -7987,58 +8287,58 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00483</t>
+          <t>CM-26-01480</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Pie Franco</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Bodegas Casa Castillo</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="I61" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>690.03</t>
+          <t>7'997.08</t>
         </is>
       </c>
       <c r="L61" s="6" t="n">
-        <v>0.1134</v>
+        <v>0.0882</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0949</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.0713</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -8047,58 +8347,58 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02609</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Clos de la Roche</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Lignier</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>5'003.90</t>
+          <t>2'738.04</t>
         </is>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.0774</v>
+        <v>0.1278</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.0594</v>
+        <v>0.0325</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0.0702</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -8107,58 +8407,58 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-26-00658</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Assortment de Grands Crus (12 bottles)</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine Ponsot</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="I63" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>3'049.20</t>
+          <t>7'018.00</t>
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>0.06</v>
+        <v>0.0882</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.0833</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>0.0505</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -8167,58 +8467,58 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-25-03004</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>257</v>
+        <v>476</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>3'382.19</t>
+          <t>10'547.81</t>
         </is>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.0468</v>
+        <v>0.0504</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.0401</v>
+        <v>0.1252</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.0441</v>
+        <v>0.0803</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -8227,58 +8527,58 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-25-02535</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Meursault Clos des Bouchers</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Jean Marc Roulot</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>323</v>
+        <v>268</v>
       </c>
       <c r="I65" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2'912.26</t>
+          <t>10'885.80</t>
         </is>
       </c>
       <c r="L65" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.045</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>0.0346</v>
+        <v>0.1292</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -8287,58 +8587,58 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00851</t>
+          <t>CM-26-00483</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Pie Franco</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Bodegas Casa Castillo</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>271</v>
+        <v>53</v>
       </c>
       <c r="I66" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>4'218.04</t>
+          <t>690.03</t>
         </is>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.0222</v>
+        <v>0.1134</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.0501</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.0334</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -8347,7 +8647,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02656</t>
+          <t>CM-25-02609</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -8357,48 +8657,48 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
+          <t>Clos de la Roche</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Weingut Markus Molitor</t>
+          <t>Domaine Georges Lignier</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>324</v>
+        <v>233</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>1'865.44</t>
+          <t>5'003.90</t>
         </is>
       </c>
       <c r="L67" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0774</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>0.0221</v>
+        <v>0.0594</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>0.0312</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -8407,7 +8707,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-01495</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -8432,33 +8732,33 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>280</v>
+        <v>393</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>568.18</t>
+          <t>4'368.68</t>
         </is>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.0216</v>
+        <v>0.0762</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0.0067</v>
+        <v>0.0519</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.0156</v>
+        <v>0.0665</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -8467,58 +8767,58 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-26-01481</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>362</v>
+        <v>252</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3'223.09</t>
         </is>
       </c>
       <c r="L69" s="6" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>0</v>
+        <v>0.0383</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>0</v>
+        <v>0.0582</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -8527,58 +8827,58 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>543</v>
+        <v>100</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3'049.20</t>
         </is>
       </c>
       <c r="L70" s="4" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0</v>
+        <v>0.0362</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -8587,58 +8887,58 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>92</v>
+        <v>257</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3'382.19</t>
         </is>
       </c>
       <c r="L71" s="6" t="n">
-        <v>0</v>
+        <v>0.0468</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>0</v>
+        <v>0.0401</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>0</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -8647,58 +8947,58 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-26-01265</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>11</v>
+        <v>323</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2'912.26</t>
         </is>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0</v>
+        <v>0.0346</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -8707,58 +9007,58 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-26-00851</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>75</v>
+        <v>271</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4'218.04</t>
         </is>
       </c>
       <c r="L73" s="6" t="n">
-        <v>0</v>
+        <v>0.0222</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>0</v>
+        <v>0.0501</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>0</v>
+        <v>0.0334</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -8767,58 +9067,58 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-25-02656</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Weingut Markus Molitor</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>42</v>
+        <v>324</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1'865.44</t>
         </is>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0</v>
+        <v>0.0221</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -8827,58 +9127,58 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>129</v>
+        <v>280</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>568.18</t>
         </is>
       </c>
       <c r="L75" s="6" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M75" s="6" t="n">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="N75" s="6" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -8887,58 +9187,58 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-01497</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>126</v>
+        <v>389</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1'046.69</t>
         </is>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0</v>
+        <v>0.0124</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -8947,7 +9247,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -8962,7 +9262,7 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -8972,11 +9272,11 @@
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>252</v>
+        <v>362</v>
       </c>
       <c r="I77" s="6" t="n">
         <v>0</v>
@@ -9007,7 +9307,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -9017,26 +9317,26 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="I78" s="4" t="n">
         <v>0</v>
@@ -9067,7 +9367,7 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -9077,26 +9377,26 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>643</v>
+        <v>543</v>
       </c>
       <c r="I79" s="6" t="n">
         <v>0</v>
@@ -9127,7 +9427,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -9137,26 +9437,26 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="I80" s="4" t="n">
         <v>0</v>
@@ -9187,7 +9487,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -9197,26 +9497,26 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="I81" s="6" t="n">
         <v>0</v>
@@ -9247,7 +9547,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -9257,26 +9557,26 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I82" s="4" t="n">
         <v>0</v>
@@ -9307,7 +9607,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -9317,26 +9617,26 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="I83" s="6" t="n">
         <v>0</v>
@@ -9367,7 +9667,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -9377,17 +9677,17 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -9396,7 +9696,7 @@
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="I84" s="4" t="n">
         <v>0</v>
@@ -9427,7 +9727,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -9437,12 +9737,12 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
@@ -9452,11 +9752,11 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="I85" s="6" t="n">
         <v>0</v>
@@ -9487,7 +9787,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -9497,26 +9797,26 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>104</v>
+        <v>252</v>
       </c>
       <c r="I86" s="4" t="n">
         <v>0</v>
@@ -9547,7 +9847,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01288</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -9557,26 +9857,26 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>240</v>
+        <v>42</v>
       </c>
       <c r="I87" s="6" t="n">
         <v>0</v>
@@ -9607,7 +9907,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01310</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -9617,26 +9917,26 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>716</v>
+        <v>643</v>
       </c>
       <c r="I88" s="4" t="n">
         <v>0</v>
@@ -9667,36 +9967,36 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01341</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>Cathiard Vineyard</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I89" s="6" t="n">
         <v>0</v>
@@ -9727,36 +10027,36 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01349</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="I90" s="4" t="n">
         <v>0</v>
@@ -9787,7 +10087,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01477</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -9797,26 +10097,26 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="I91" s="6" t="n">
         <v>0</v>
@@ -9847,7 +10147,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01479</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -9857,26 +10157,26 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H92" s="4" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="I92" s="4" t="n">
         <v>0</v>
@@ -9907,7 +10207,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01480</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -9917,26 +10217,26 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I93" s="6" t="n">
         <v>0</v>
@@ -9967,36 +10267,36 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01482</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H94" s="4" t="n">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="I94" s="4" t="n">
         <v>0</v>
@@ -10027,62 +10327,662 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
+          <t>CM-26-01288</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Chambertin Clos de Bèze</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Armand Rousseau</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="I95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01310</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Georges Roumier</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>716</v>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01341</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>🟨</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Cabernet Sauvignon</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>Cathiard Vineyard</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="I97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01349</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>🟨</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Chambertin Clos de Bèze</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Bruno Clair</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01477</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Chambolle-Musigny Les Amoureuses</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="I99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01479</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="I100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01482</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="I101" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L101" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01508</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>L'Ermita</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>Alvaro Palacios</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01512</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01513</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
           <t>CM-25-02438</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
         <is>
           <t>🟣</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>DRC Romanée Conti</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E105" s="6" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G105" s="6" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="H95" s="6" t="n">
+      <c r="H105" s="6" t="n">
         <v>410</v>
       </c>
-      <c r="I95" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="6" t="inlineStr">
+      <c r="I105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K95" s="6" t="inlineStr">
+      <c r="K105" s="6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L95" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="6" t="n">
+      <c r="L105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="6" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N95"/>
+  <autoFilter ref="A3:N105"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 08:43  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-21 13:59  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -945,17 +945,17 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>48'472.47</t>
+          <t>48'501.32</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
         <v>0.3869</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.5754</v>
+        <v>0.5758</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4623</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -1084,58 +1084,58 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00771</t>
+          <t>CM-26-01431</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>10.71%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>10'123.30</t>
+          <t>5'680.00</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5453</v>
+        <v>0.6425</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1202</v>
+        <v>0.0674</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3753</v>
+        <v>0.4125</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00293</t>
+          <t>CM-26-00771</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1154,48 +1154,48 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Latour (Ex-Château)</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>51'964.65</t>
+          <t>10'123.30</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1938</v>
+        <v>0.5453</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.6169</v>
+        <v>0.1202</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.363</v>
+        <v>0.3753</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00724</t>
+          <t>CM-26-00293</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1214,48 +1214,48 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Cheval Blanc</t>
+          <t>Latour (Ex-Château)</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Cheval Blanc</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>53'840.62</t>
+          <t>51'964.65</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1698</v>
+        <v>0.1938</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.6391</v>
+        <v>0.6169</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3575</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1264,58 +1264,58 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01431</t>
+          <t>CM-26-00724</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Cheval Blanc</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Château Cheval Blanc</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>4'317.52</t>
+          <t>53'840.62</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.5357</v>
+        <v>0.1698</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0513</v>
+        <v>0.6391</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.3419</v>
+        <v>0.3575</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-26-01535</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1574,48 +1574,48 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>3'508.63</t>
+          <t>31'223.10</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.4895</v>
+        <v>0.2729</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.3706</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.3104</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1624,58 +1624,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>3'517.88</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.3827</v>
+        <v>0.4895</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1902</v>
+        <v>0.0418</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.3057</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1694,48 +1694,48 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>184</v>
+        <v>47</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0324</v>
+        <v>0.3827</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6896</v>
+        <v>0.1902</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2953</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1754,48 +1754,48 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>34'832.71</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2142</v>
+        <v>0.0324</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.4135</v>
+        <v>0.6896</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2939</v>
+        <v>0.2953</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1814,48 +1814,48 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>43'696.73</t>
+          <t>34'832.71</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1332</v>
+        <v>0.2142</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5187</v>
+        <v>0.4135</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2874</v>
+        <v>0.2939</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1864,58 +1864,58 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>181</v>
+        <v>135</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>26'801.63</t>
+          <t>43'696.73</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.2322</v>
+        <v>0.1332</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.3182</v>
+        <v>0.5187</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2666</v>
+        <v>0.2874</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1934,48 +1934,48 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>20'502.14</t>
+          <t>26'801.63</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2771</v>
+        <v>0.2322</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2434</v>
+        <v>0.3182</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2636</v>
+        <v>0.2666</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1984,58 +1984,58 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>47</v>
+        <v>195</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>20'502.14</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.2771</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.4545</v>
+        <v>0.2434</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2585</v>
+        <v>0.2636</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2054,48 +2054,48 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1224</v>
+        <v>0.1278</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4309</v>
+        <v>0.4545</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2458</v>
+        <v>0.2585</v>
       </c>
     </row>
   </sheetData>
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 11 May 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 14 May 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 08:43  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-21 13:59  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,67 +2221,67 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01535</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>🟨</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Chambolle Musigny Les Amoureuses</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01461</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Côte Rôtie La Landonne</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Guigal</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>12.90%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>11'271.04</t>
+          <t>31'223.10</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.7738</v>
+        <v>0.2729</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.1338</v>
+        <v>0.3706</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.5178</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
@@ -2341,141 +2341,141 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01486</t>
+          <t>CM-26-01550</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>3'838.19</t>
+          <t>8'731.46</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.099</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.0456</v>
+        <v>0.1036</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.182</v>
+        <v>0.1008</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01494</t>
+          <t>CM-26-01542</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>17'751.48</t>
+          <t>2'427.03</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1464</v>
+        <v>0.138</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2107</v>
+        <v>0.0288</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1721</v>
+        <v>0.09429999999999999</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01500</t>
+          <t>CM-26-01508</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>L'Ermita</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2485,47 +2485,47 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Alvaro Palacios</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>107</v>
+        <v>30</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2'258.69</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2244</v>
+        <v>0</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0268</v>
+        <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01480</t>
+          <t>CM-26-01512</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -2550,577 +2550,97 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>7'997.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0882</v>
+        <v>0</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0949</v>
+        <v>0</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.09089999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01495</t>
+          <t>CM-26-01513</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>393</v>
+        <v>22</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>4'368.68</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0762</v>
+        <v>0</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0519</v>
+        <v>0</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0665</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01481</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Ca' Marcanda</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Ca' Marcanda - Gaja</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>252</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>1.19%</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>3'223.09</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>0.07140000000000001</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>0.0383</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>0.0582</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01497</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Meursault Crotots</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Pierre Vincent</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>389</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>0.26%</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>1'046.69</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0.0156</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0.0143</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>96</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01477</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Mugnier Jacques-Frederic</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>81</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01479</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Bonnes Mares</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Mugnier Jacques-Frederic</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>152</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>98</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01482</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Mugnier Jacques-Frederic</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01508</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>L'Ermita</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Alvaro Palacios</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01512</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Bonnes Mares</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Mugnier Jacques-Frederic</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01513</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Mugnier Jacques-Frederic</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N18"/>
+  <autoFilter ref="A3:N10"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3157,14 +2677,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 18 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 21 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 08:43  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-21 13:59  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -3362,7 +2882,7 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -3398,26 +2918,26 @@
         <v>56</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>10.71%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>4'317.52</t>
+          <t>5'680.00</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.5357</v>
+        <v>0.6425</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.0513</v>
+        <v>0.0674</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3419</v>
+        <v>0.4125</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -3482,62 +3002,62 @@
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-01535</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>31'223.10</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0324</v>
+        <v>0.2729</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.6896</v>
+        <v>0.3706</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2953</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -3546,7 +3066,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -3556,48 +3076,48 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>34'832.71</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2142</v>
+        <v>0.0324</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.4135</v>
+        <v>0.6896</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2939</v>
+        <v>0.2953</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -3606,7 +3126,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -3616,57 +3136,57 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>43'696.73</t>
+          <t>34'832.71</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1332</v>
+        <v>0.2142</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.5187</v>
+        <v>0.4135</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2874</v>
+        <v>0.2939</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -3676,48 +3196,48 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>21'358.58</t>
+          <t>43'696.73</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1692</v>
+        <v>0.1332</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2535</v>
+        <v>0.5187</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2029</v>
+        <v>0.2874</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -3767,17 +3287,17 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>3'838.19</t>
+          <t>3'550.60</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
         <v>0.2729</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0456</v>
+        <v>0.0421</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.182</v>
+        <v>0.1806</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -3962,11 +3482,11 @@
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3976,53 +3496,53 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>11'095.00</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1248</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0684</v>
+        <v>0.1317</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1022</v>
+        <v>0.1034</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
@@ -4082,62 +3602,62 @@
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01376</t>
+          <t>CM-26-01550</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Bollinger</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>348</v>
+        <v>121</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>14'566.45</t>
+          <t>8'731.46</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0516</v>
+        <v>0.099</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1729</v>
+        <v>0.1036</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.1001</v>
+        <v>0.1008</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -4146,7 +3666,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01480</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -4156,7 +3676,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -4166,38 +3686,38 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>68</v>
+        <v>348</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>7'997.08</t>
+          <t>14'566.45</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.0516</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0949</v>
+        <v>0.1729</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1001</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4206,67 +3726,67 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01542</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2'738.04</t>
+          <t>2'427.03</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.138</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0325</v>
+        <v>0.0288</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0897</v>
+        <v>0.09429999999999999</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01495</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -4276,12 +3796,12 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -4291,52 +3811,52 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>393</v>
+        <v>235</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>5</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>4'368.68</t>
+          <t>2'738.04</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0762</v>
+        <v>0.1278</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0519</v>
+        <v>0.0325</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0665</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01481</t>
+          <t>CM-26-01480</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -4346,117 +3866,117 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>252</v>
+        <v>68</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>3'223.09</t>
+          <t>7'397.86</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0882</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0383</v>
+        <v>0.0878</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0582</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-26-01481</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>100</v>
+        <v>252</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>3'049.20</t>
+          <t>2'329.06</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.06</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.0276</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0505</v>
+        <v>0.0539</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -4466,57 +3986,57 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>257</v>
+        <v>100</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>3'382.19</t>
+          <t>3'049.20</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0468</v>
+        <v>0.06</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0401</v>
+        <v>0.0362</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0441</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-26-01495</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -4531,57 +4051,57 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>323</v>
+        <v>393</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2'912.26</t>
+          <t>2'846.36</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0612</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.0346</v>
+        <v>0.0338</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -4595,38 +4115,38 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>568.18</t>
+          <t>3'382.19</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0216</v>
+        <v>0.0468</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0067</v>
+        <v>0.0401</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0156</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01497</t>
+          <t>CM-26-01265</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -4651,93 +4171,93 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>389</v>
+        <v>323</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>1'046.69</t>
+          <t>2'912.26</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0156</v>
+        <v>0.0372</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0124</v>
+        <v>0.0346</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0143</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01288</t>
+          <t>CM-26-01497</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>240</v>
+        <v>483</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1'936.52</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0</v>
+        <v>0.0246</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
     </row>
   </sheetData>
@@ -4756,7 +4276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N105"/>
+  <dimension ref="A1:N108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4785,7 +4305,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 08:43  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-21 13:59  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -5208,17 +4728,17 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>48'472.47</t>
+          <t>48'501.32</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
         <v>0.3869</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.5754</v>
+        <v>0.5758</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4623</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -5347,58 +4867,58 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00771</t>
+          <t>CM-26-01431</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>10.71%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>10'123.30</t>
+          <t>5'680.00</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5453</v>
+        <v>0.6425</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1202</v>
+        <v>0.0674</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3753</v>
+        <v>0.4125</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -5407,7 +4927,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00293</t>
+          <t>CM-26-00771</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -5417,48 +4937,48 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Latour (Ex-Château)</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>51'964.65</t>
+          <t>10'123.30</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1938</v>
+        <v>0.5453</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.6169</v>
+        <v>0.1202</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.363</v>
+        <v>0.3753</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -5467,7 +4987,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00724</t>
+          <t>CM-26-00293</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -5477,48 +4997,48 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Cheval Blanc</t>
+          <t>Latour (Ex-Château)</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Cheval Blanc</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>53'840.62</t>
+          <t>51'964.65</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1698</v>
+        <v>0.1938</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.6391</v>
+        <v>0.6169</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3575</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -5527,58 +5047,58 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01431</t>
+          <t>CM-26-00724</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Cheval Blanc</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Château Cheval Blanc</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>4'317.52</t>
+          <t>53'840.62</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.5357</v>
+        <v>0.1698</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0513</v>
+        <v>0.6391</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.3419</v>
+        <v>0.3575</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -5827,7 +5347,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-26-01535</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -5837,48 +5357,48 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>3'508.63</t>
+          <t>31'223.10</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.4895</v>
+        <v>0.2729</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.3706</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.3104</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -5887,58 +5407,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>3'517.88</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.3827</v>
+        <v>0.4895</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1902</v>
+        <v>0.0418</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.3057</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -5947,7 +5467,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -5957,48 +5477,48 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>184</v>
+        <v>47</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0324</v>
+        <v>0.3827</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6896</v>
+        <v>0.1902</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2953</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -6007,7 +5527,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -6017,48 +5537,48 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>34'832.71</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2142</v>
+        <v>0.0324</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.4135</v>
+        <v>0.6896</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2939</v>
+        <v>0.2953</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -6067,7 +5587,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -6077,48 +5597,48 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>43'696.73</t>
+          <t>34'832.71</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1332</v>
+        <v>0.2142</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5187</v>
+        <v>0.4135</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2874</v>
+        <v>0.2939</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -6127,58 +5647,58 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>181</v>
+        <v>135</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>26'801.63</t>
+          <t>43'696.73</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.2322</v>
+        <v>0.1332</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.3182</v>
+        <v>0.5187</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2666</v>
+        <v>0.2874</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -6187,7 +5707,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -6197,48 +5717,48 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>20'502.14</t>
+          <t>26'801.63</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2771</v>
+        <v>0.2322</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2434</v>
+        <v>0.3182</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2636</v>
+        <v>0.2666</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -6247,58 +5767,58 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>47</v>
+        <v>195</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>20'502.14</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.2771</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.4545</v>
+        <v>0.2434</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2585</v>
+        <v>0.2636</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -6307,7 +5827,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -6317,48 +5837,48 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1224</v>
+        <v>0.1278</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4309</v>
+        <v>0.4545</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2458</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -6367,58 +5887,58 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.1224</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.0683</v>
+        <v>0.4309</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2166</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -6427,58 +5947,58 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.2609</v>
+        <v>0.3155</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.1399</v>
+        <v>0.0683</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2125</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6487,58 +6007,58 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.2501</v>
+        <v>0.2609</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1529</v>
+        <v>0.1399</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2112</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6547,58 +6067,58 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-26-00774</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>La Grande Rue</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Domaine Francois Lamarche</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>21'358.58</t>
+          <t>12'881.25</t>
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1692</v>
+        <v>0.2501</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2535</v>
+        <v>0.1529</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2029</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6948,17 +6468,17 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>3'838.19</t>
+          <t>3'550.60</t>
         </is>
       </c>
       <c r="L38" s="4" t="n">
         <v>0.2729</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.0456</v>
+        <v>0.0421</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.182</v>
+        <v>0.1806</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7927,58 +7447,58 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>317</v>
+        <v>71</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>12'118.06</t>
+          <t>11'095.00</t>
         </is>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.0756</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.1439</v>
+        <v>0.1317</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.1029</v>
+        <v>0.1034</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -7987,58 +7507,58 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00772</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>198</v>
+        <v>317</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>10'109.38</t>
+          <t>12'118.06</t>
         </is>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.0912</v>
+        <v>0.0756</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.12</v>
+        <v>0.1439</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.1027</v>
+        <v>0.1029</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -8047,7 +7567,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-00772</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -8057,48 +7577,48 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>10'109.38</t>
         </is>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.1248</v>
+        <v>0.0912</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.0684</v>
+        <v>0.12</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.1022</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -8107,58 +7627,58 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01320</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>4'696.54</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.132</v>
+        <v>0.1248</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.0558</v>
+        <v>0.0684</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.1015</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -8167,58 +7687,58 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01376</t>
+          <t>CM-26-01320</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Bollinger</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>348</v>
+        <v>91</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>14'566.45</t>
+          <t>4'696.54</t>
         </is>
       </c>
       <c r="L59" s="6" t="n">
-        <v>0.0516</v>
+        <v>0.132</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0.1729</v>
+        <v>0.0558</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.1001</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -8227,58 +7747,58 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-26-01550</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>487</v>
+        <v>121</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>8'731.46</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.099</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.1716</v>
+        <v>0.1036</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.091</v>
+        <v>0.1008</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -8287,7 +7807,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01480</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -8297,7 +7817,7 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -8307,38 +7827,38 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>68</v>
+        <v>348</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>7'997.08</t>
+          <t>14'566.45</t>
         </is>
       </c>
       <c r="L61" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.0516</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.0949</v>
+        <v>0.1729</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1001</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -8347,58 +7867,58 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01542</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2'738.04</t>
+          <t>2'427.03</t>
         </is>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.138</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.0325</v>
+        <v>0.0288</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0.0897</v>
+        <v>0.09429999999999999</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -8407,7 +7927,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00658</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -8417,48 +7937,48 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Assortment de Grands Crus (12 bottles)</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Domaine Ponsot</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>68</v>
+        <v>487</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>7'018.00</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.0372</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>0.0833</v>
+        <v>0.1716</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>0.0862</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -8467,58 +7987,58 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03004</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>476</v>
+        <v>235</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>10'547.81</t>
+          <t>2'738.04</t>
         </is>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.0504</v>
+        <v>0.1278</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.1252</v>
+        <v>0.0325</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.0803</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -8527,7 +8047,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02535</t>
+          <t>CM-26-01480</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -8537,48 +8057,48 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Meursault Clos des Bouchers</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Domaine Jean Marc Roulot</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>268</v>
+        <v>68</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>10'885.80</t>
+          <t>7'397.86</t>
         </is>
       </c>
       <c r="L65" s="6" t="n">
-        <v>0.045</v>
+        <v>0.0882</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>0.1292</v>
+        <v>0.0878</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -8587,58 +8107,58 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00483</t>
+          <t>CM-26-00658</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Pie Franco</t>
+          <t>Assortment de Grands Crus (12 bottles)</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Bodegas Casa Castillo</t>
+          <t>Domaine Ponsot</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="I66" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>690.03</t>
+          <t>7'018.00</t>
         </is>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.1134</v>
+        <v>0.0882</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0833</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.0713</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -8647,58 +8167,58 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02609</t>
+          <t>CM-25-03004</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Clos de la Roche</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Domaine Georges Lignier</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>233</v>
+        <v>476</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>5'003.90</t>
+          <t>10'547.81</t>
         </is>
       </c>
       <c r="L67" s="6" t="n">
-        <v>0.0774</v>
+        <v>0.0504</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>0.0594</v>
+        <v>0.1252</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>0.0702</v>
+        <v>0.0803</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -8707,58 +8227,58 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01495</t>
+          <t>CM-25-02535</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Meursault Clos des Bouchers</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Jean Marc Roulot</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>393</v>
+        <v>268</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>4'368.68</t>
+          <t>10'885.80</t>
         </is>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.0762</v>
+        <v>0.045</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0.0519</v>
+        <v>0.1292</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.0665</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -8767,7 +8287,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01481</t>
+          <t>CM-26-00483</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -8777,48 +8297,48 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Pie Franco</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Bodegas Casa Castillo</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>252</v>
+        <v>53</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>3'223.09</t>
+          <t>690.03</t>
         </is>
       </c>
       <c r="L69" s="6" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1134</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>0.0383</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>0.0582</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -8827,58 +8347,58 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-25-02609</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Clos de la Roche</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine Georges Lignier</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>100</v>
+        <v>233</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>3'049.20</t>
+          <t>5'003.90</t>
         </is>
       </c>
       <c r="L70" s="4" t="n">
-        <v>0.06</v>
+        <v>0.0774</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.0362</v>
+        <v>0.0594</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.0505</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -8887,7 +8407,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-26-01481</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -8897,48 +8417,48 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>3'382.19</t>
+          <t>2'329.06</t>
         </is>
       </c>
       <c r="L71" s="6" t="n">
-        <v>0.0468</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>0.0401</v>
+        <v>0.0276</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>0.0441</v>
+        <v>0.0539</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -8947,58 +8467,58 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>323</v>
+        <v>100</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2'912.26</t>
+          <t>3'049.20</t>
         </is>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.06</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.0346</v>
+        <v>0.0362</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.0362</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -9007,58 +8527,58 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00851</t>
+          <t>CM-26-01495</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>271</v>
+        <v>393</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>4'218.04</t>
+          <t>2'846.36</t>
         </is>
       </c>
       <c r="L73" s="6" t="n">
-        <v>0.0222</v>
+        <v>0.0612</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>0.0501</v>
+        <v>0.0338</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>0.0334</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -9067,7 +8587,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02656</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -9077,48 +8597,48 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Weingut Markus Molitor</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>324</v>
+        <v>257</v>
       </c>
       <c r="I74" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>1'865.44</t>
+          <t>3'382.19</t>
         </is>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.0468</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.0221</v>
+        <v>0.0401</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -9127,17 +8647,17 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-01265</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -9156,29 +8676,29 @@
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>280</v>
+        <v>323</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>568.18</t>
+          <t>2'912.26</t>
         </is>
       </c>
       <c r="L75" s="6" t="n">
-        <v>0.0216</v>
+        <v>0.0372</v>
       </c>
       <c r="M75" s="6" t="n">
-        <v>0.0067</v>
+        <v>0.0346</v>
       </c>
       <c r="N75" s="6" t="n">
-        <v>0.0156</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -9187,58 +8707,58 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01497</t>
+          <t>CM-26-00851</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>389</v>
+        <v>271</v>
       </c>
       <c r="I76" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>1'046.69</t>
+          <t>4'218.04</t>
         </is>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.0156</v>
+        <v>0.0222</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.0124</v>
+        <v>0.0501</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.0143</v>
+        <v>0.0334</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -9247,58 +8767,58 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-25-02656</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Weingut Markus Molitor</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1'865.44</t>
         </is>
       </c>
       <c r="L77" s="6" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M77" s="6" t="n">
-        <v>0</v>
+        <v>0.0221</v>
       </c>
       <c r="N77" s="6" t="n">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -9307,58 +8827,58 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-26-01497</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>49</v>
+        <v>483</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1'936.52</t>
         </is>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0</v>
+        <v>0.0246</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -9367,58 +8887,58 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>543</v>
+        <v>280</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>568.18</t>
         </is>
       </c>
       <c r="L79" s="6" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M79" s="6" t="n">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="N79" s="6" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -9547,7 +9067,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -9557,26 +9077,26 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I82" s="4" t="n">
         <v>0</v>
@@ -9607,7 +9127,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -9617,26 +9137,26 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>129</v>
+        <v>543</v>
       </c>
       <c r="I83" s="6" t="n">
         <v>0</v>
@@ -9667,7 +9187,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -9677,26 +9197,26 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>103</v>
+        <v>362</v>
       </c>
       <c r="I84" s="4" t="n">
         <v>0</v>
@@ -9727,7 +9247,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -9737,26 +9257,26 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="I85" s="6" t="n">
         <v>0</v>
@@ -9787,7 +9307,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -9797,26 +9317,26 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="I86" s="4" t="n">
         <v>0</v>
@@ -9847,7 +9367,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -9857,26 +9377,26 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="I87" s="6" t="n">
         <v>0</v>
@@ -9907,7 +9427,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -9917,7 +9437,7 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -9927,16 +9447,16 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>643</v>
+        <v>126</v>
       </c>
       <c r="I88" s="4" t="n">
         <v>0</v>
@@ -9967,7 +9487,7 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -9977,26 +9497,26 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>20</v>
+        <v>252</v>
       </c>
       <c r="I89" s="6" t="n">
         <v>0</v>
@@ -10027,7 +9547,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -10037,26 +9557,26 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="I90" s="4" t="n">
         <v>0</v>
@@ -10087,7 +9607,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -10097,26 +9617,26 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>26</v>
+        <v>643</v>
       </c>
       <c r="I91" s="6" t="n">
         <v>0</v>
@@ -10147,7 +9667,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -10157,17 +9677,17 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -10176,7 +9696,7 @@
         </is>
       </c>
       <c r="H92" s="4" t="n">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="I92" s="4" t="n">
         <v>0</v>
@@ -10207,7 +9727,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -10217,26 +9737,26 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="I93" s="6" t="n">
         <v>0</v>
@@ -10267,7 +9787,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01479</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -10277,26 +9797,26 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H94" s="4" t="n">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="I94" s="4" t="n">
         <v>0</v>
@@ -10327,7 +9847,7 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01288</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -10337,26 +9857,26 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H95" s="6" t="n">
-        <v>240</v>
+        <v>28</v>
       </c>
       <c r="I95" s="6" t="n">
         <v>0</v>
@@ -10387,7 +9907,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01310</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -10397,26 +9917,26 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H96" s="4" t="n">
-        <v>716</v>
+        <v>26</v>
       </c>
       <c r="I96" s="4" t="n">
         <v>0</v>
@@ -10447,17 +9967,17 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01341</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -10467,16 +9987,16 @@
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>Cathiard Vineyard</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H97" s="6" t="n">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="I97" s="6" t="n">
         <v>0</v>
@@ -10507,36 +10027,36 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01349</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H98" s="4" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="I98" s="4" t="n">
         <v>0</v>
@@ -10567,7 +10087,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01477</t>
+          <t>CM-26-01288</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -10577,26 +10097,26 @@
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H99" s="6" t="n">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="I99" s="6" t="n">
         <v>0</v>
@@ -10627,7 +10147,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01479</t>
+          <t>CM-26-01310</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -10642,21 +10162,21 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Georges Roumier</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H100" s="4" t="n">
-        <v>152</v>
+        <v>716</v>
       </c>
       <c r="I100" s="4" t="n">
         <v>0</v>
@@ -10687,36 +10207,36 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01482</t>
+          <t>CM-26-01341</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Cathiard Vineyard</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H101" s="6" t="n">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="I101" s="6" t="n">
         <v>0</v>
@@ -10747,36 +10267,36 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01508</t>
+          <t>CM-26-01349</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>L'Ermita</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Alvaro Palacios</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="H102" s="4" t="n">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="I102" s="4" t="n">
         <v>0</v>
@@ -10807,7 +10327,7 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01512</t>
+          <t>CM-26-01477</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -10817,7 +10337,7 @@
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -10832,11 +10352,11 @@
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H103" s="6" t="n">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="I103" s="6" t="n">
         <v>0</v>
@@ -10867,7 +10387,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01513</t>
+          <t>CM-26-01482</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -10892,11 +10412,11 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H104" s="4" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I104" s="4" t="n">
         <v>0</v>
@@ -10927,62 +10447,242 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
+          <t>CM-26-01508</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>L'Ermita</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>Alvaro Palacios</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01512</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01513</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="I107" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L107" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
           <t>CM-25-02438</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
+      <c r="C108" s="4" t="inlineStr">
         <is>
           <t>🟣</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>DRC Romanée Conti</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E108" s="4" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F105" s="6" t="inlineStr">
+      <c r="F108" s="4" t="inlineStr">
         <is>
           <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
-      <c r="G105" s="6" t="inlineStr">
+      <c r="G108" s="4" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="H105" s="6" t="n">
+      <c r="H108" s="4" t="n">
         <v>410</v>
       </c>
-      <c r="I105" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="6" t="inlineStr">
+      <c r="I108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K105" s="6" t="inlineStr">
+      <c r="K108" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L105" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="6" t="n">
+      <c r="L108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N105"/>
+  <autoFilter ref="A3:N108"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-21 13:59  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-26 08:35  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>42'341.00</t>
+          <t>39'065.00</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
         <v>0.6665</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.5026</v>
+        <v>0.4637</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.6009</v>
+        <v>0.5854</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -945,14 +945,14 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>48'501.32</t>
+          <t>48'512.22</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
         <v>0.3869</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.5758</v>
+        <v>0.5759</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>0.4625</v>
@@ -1485,14 +1485,14 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>37'837.84</t>
+          <t>37'852.12</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
         <v>0.2472</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.4492</v>
+        <v>0.4493</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.328</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01535</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1574,48 +1574,48 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>31'223.10</t>
+          <t>3'517.88</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.4895</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.3706</v>
+        <v>0.0418</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.312</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1624,58 +1624,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>3'517.88</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.4895</v>
+        <v>0.3827</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0418</v>
+        <v>0.1902</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.3104</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1694,48 +1694,48 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>47</v>
+        <v>184</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.0324</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.1902</v>
+        <v>0.6896</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.3057</v>
+        <v>0.2953</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1754,48 +1754,48 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>34'832.71</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0324</v>
+        <v>0.2142</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.6896</v>
+        <v>0.4135</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2953</v>
+        <v>0.2939</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1804,58 +1804,58 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01535</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>34'832.71</t>
+          <t>26'304.45</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.2729</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4135</v>
+        <v>0.3123</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2939</v>
+        <v>0.2887</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2025,17 +2025,17 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>20'502.14</t>
+          <t>20'518.08</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
         <v>0.2771</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.2434</v>
+        <v>0.2436</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2636</v>
+        <v>0.2637</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 14 May 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 19 May 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-21 13:59  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-26 08:35  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01535</t>
+          <t>CM-26-01582</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -2235,412 +2235,172 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>110</v>
+        <v>443</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>31'223.10</t>
+          <t>17'926.78</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.081</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.3706</v>
+        <v>0.2128</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.312</v>
+        <v>0.1337</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-01550</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>184</v>
+        <v>121</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>4'195.80</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.0324</v>
+        <v>0.0498</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.6896</v>
+        <v>0.0498</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.2953</v>
+        <v>0.0498</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01550</t>
+          <t>CM-26-01614</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>121</v>
+        <v>461</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>8'731.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1036</v>
+        <v>0</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1008</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01542</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Ca' Marcanda</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Ca' Marcanda - Gaja</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>87</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>2.30%</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>2'427.03</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>0.0288</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>0.09429999999999999</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01508</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>L'Ermita</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Alvaro Palacios</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>103</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01512</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Bonnes Mares</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Mugnier Jacques-Frederic</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01513</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Mugnier Jacques-Frederic</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N10"/>
+  <autoFilter ref="A3:N6"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2677,14 +2437,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 21 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 26 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-21 13:59  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-26 08:35  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2807,17 +2567,17 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>42'341.00</t>
+          <t>39'065.00</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
         <v>0.6665</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.5026</v>
+        <v>0.4637</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.6009</v>
+        <v>0.5854</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -3002,62 +2762,62 @@
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01535</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>110</v>
+        <v>184</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>31'223.10</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.0324</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.3706</v>
+        <v>0.6896</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.312</v>
+        <v>0.2953</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -3066,7 +2826,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -3076,48 +2836,48 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>34'832.71</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0324</v>
+        <v>0.2142</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.6896</v>
+        <v>0.4135</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2953</v>
+        <v>0.2939</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -3126,58 +2886,58 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01535</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>34'832.71</t>
+          <t>26'304.45</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.2729</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4135</v>
+        <v>0.3123</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2939</v>
+        <v>0.2887</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -3242,86 +3002,86 @@
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01486</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>3'550.60</t>
+          <t>21'358.58</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.1692</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0421</v>
+        <v>0.2535</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1806</v>
+        <v>0.2029</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01494</t>
+          <t>CM-26-01486</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3335,58 +3095,58 @@
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>17'751.48</t>
+          <t>3'550.60</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1464</v>
+        <v>0.2729</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2107</v>
+        <v>0.0421</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1721</v>
+        <v>0.1806</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01500</t>
+          <t>CM-26-01494</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -3395,278 +3155,278 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2'258.69</t>
+          <t>17'751.48</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2244</v>
+        <v>0.1464</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0268</v>
+        <v>0.2107</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1454</v>
+        <v>0.1721</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01284</t>
+          <t>CM-26-01500</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>8'112.00</t>
+          <t>2'258.69</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1332</v>
+        <v>0.2244</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0963</v>
+        <v>0.0268</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1184</v>
+        <v>0.1454</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-26-01582</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>71</v>
+        <v>443</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>11'095.00</t>
+          <t>17'926.78</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1317</v>
+        <v>0.2128</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1034</v>
+        <v>0.1337</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01320</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>91</v>
+        <v>348</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>4'696.54</t>
+          <t>14'566.45</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.132</v>
+        <v>0.0516</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0558</v>
+        <v>0.1729</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1015</v>
+        <v>0.1001</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01550</t>
+          <t>CM-26-01542</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>8'731.46</t>
+          <t>2'427.03</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.099</v>
+        <v>0.138</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1036</v>
+        <v>0.0288</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.1008</v>
+        <v>0.09429999999999999</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01376</t>
+          <t>CM-26-01480</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -3676,7 +3436,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -3686,47 +3446,47 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Bollinger</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>348</v>
+        <v>68</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>14'566.45</t>
+          <t>7'397.86</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0516</v>
+        <v>0.0882</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1729</v>
+        <v>0.0878</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1001</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01542</t>
+          <t>CM-26-01481</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3741,7 +3501,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -3751,42 +3511,42 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>87</v>
+        <v>252</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2'427.03</t>
+          <t>2'329.06</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.138</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0288</v>
+        <v>0.0276</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0539</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01495</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -3796,12 +3556,12 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -3811,102 +3571,102 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>235</v>
+        <v>393</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2'738.04</t>
+          <t>2'846.36</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.0612</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0325</v>
+        <v>0.0338</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0897</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01480</t>
+          <t>CM-26-01550</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>7'397.86</t>
+          <t>4'195.80</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0882</v>
+        <v>0.0498</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0878</v>
+        <v>0.0498</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.0498</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01481</t>
+          <t>CM-26-01497</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -3916,17 +3676,17 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -3935,38 +3695,38 @@
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>252</v>
+        <v>483</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2'329.06</t>
+          <t>1'936.52</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0246</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0276</v>
+        <v>0.023</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0539</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-26-01349</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -3991,222 +3751,222 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>3'049.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0362</v>
+        <v>0</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01495</t>
+          <t>CM-26-01341</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Cathiard Vineyard</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>393</v>
+        <v>91</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2'846.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0612</v>
+        <v>0</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.0338</v>
+        <v>0</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0502</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-26-01477</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>257</v>
+        <v>81</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>3'382.19</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0468</v>
+        <v>0</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0401</v>
+        <v>0</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0441</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-26-01479</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>323</v>
+        <v>152</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2'912.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0372</v>
+        <v>0</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0346</v>
+        <v>0</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0362</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01497</t>
+          <t>CM-26-01482</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -4216,48 +3976,48 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>483</v>
+        <v>36</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>1'936.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0246</v>
+        <v>0</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4276,7 +4036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N108"/>
+  <dimension ref="A1:N110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4305,7 +4065,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-21 13:59  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-05-26 08:35  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4548,17 +4308,17 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>42'341.00</t>
+          <t>39'065.00</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
         <v>0.6665</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.5026</v>
+        <v>0.4637</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.6009</v>
+        <v>0.5854</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -4728,14 +4488,14 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>48'501.32</t>
+          <t>48'512.22</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
         <v>0.3869</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.5758</v>
+        <v>0.5759</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>0.4625</v>
@@ -5268,14 +5028,14 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>37'837.84</t>
+          <t>37'852.12</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
         <v>0.2472</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.4492</v>
+        <v>0.4493</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.328</v>
@@ -5347,7 +5107,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01535</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -5357,48 +5117,48 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>31'223.10</t>
+          <t>3'517.88</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.4895</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.3706</v>
+        <v>0.0418</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.312</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -5407,58 +5167,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>3'517.88</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.4895</v>
+        <v>0.3827</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0418</v>
+        <v>0.1902</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.3104</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -5467,7 +5227,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -5477,48 +5237,48 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>47</v>
+        <v>184</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.0324</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.1902</v>
+        <v>0.6896</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.3057</v>
+        <v>0.2953</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -5527,7 +5287,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -5537,48 +5297,48 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>34'832.71</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0324</v>
+        <v>0.2142</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.6896</v>
+        <v>0.4135</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2953</v>
+        <v>0.2939</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -5587,58 +5347,58 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01535</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>34'832.71</t>
+          <t>26'304.45</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.2729</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4135</v>
+        <v>0.3123</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2939</v>
+        <v>0.2887</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -5808,17 +5568,17 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>20'502.14</t>
+          <t>20'518.08</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
         <v>0.2771</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.2434</v>
+        <v>0.2436</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2636</v>
+        <v>0.2637</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -6127,58 +5887,58 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>9'735.26</t>
+          <t>21'358.58</t>
         </is>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.2609</v>
+        <v>0.1692</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1156</v>
+        <v>0.2535</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.2028</v>
+        <v>0.2029</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6187,58 +5947,58 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00553</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>167</v>
+        <v>92</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>37'269.73</t>
+          <t>9'735.26</t>
         </is>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.036</v>
+        <v>0.2609</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.4424</v>
+        <v>0.1156</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1986</v>
+        <v>0.2028</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6247,17 +6007,17 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03240</t>
+          <t>CM-26-00553</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -6267,38 +6027,38 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>245</v>
+        <v>167</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>12'603.94</t>
+          <t>37'269.73</t>
         </is>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.2202</v>
+        <v>0.036</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1496</v>
+        <v>0.4424</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.192</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6307,58 +6067,58 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-25-03240</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Château Larcis Ducasse</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>14'592.69</t>
+          <t>12'609.72</t>
         </is>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.201</v>
+        <v>0.2202</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.1732</v>
+        <v>0.1497</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.1899</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -6367,58 +6127,58 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00844</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>27</v>
+        <v>179</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>10'599.18</t>
+          <t>14'592.69</t>
         </is>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.222</v>
+        <v>0.201</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1258</v>
+        <v>0.1732</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.1835</v>
+        <v>0.1899</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -6427,58 +6187,58 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01486</t>
+          <t>CM-26-00844</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I38" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>3'550.60</t>
+          <t>10'599.18</t>
         </is>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.222</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.0421</v>
+        <v>0.1258</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.1806</v>
+        <v>0.1835</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -6487,58 +6247,58 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01219</t>
+          <t>CM-26-01486</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>221</v>
+        <v>22</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>16'040.28</t>
+          <t>3'550.60</t>
         </is>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.1626</v>
+        <v>0.2729</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1904</v>
+        <v>0.0421</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1737</v>
+        <v>0.1806</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -6547,7 +6307,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02431</t>
+          <t>CM-26-01219</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -6572,33 +6332,33 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>156</v>
+        <v>221</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>11'961.88</t>
+          <t>16'040.28</t>
         </is>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.1926</v>
+        <v>0.1626</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.142</v>
+        <v>0.1904</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.1724</v>
+        <v>0.1737</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -6607,58 +6367,58 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01494</t>
+          <t>CM-25-02431</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>41</v>
+        <v>156</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>17'751.48</t>
+          <t>11'961.88</t>
         </is>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.1464</v>
+        <v>0.1926</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.2107</v>
+        <v>0.142</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1721</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -6667,7 +6427,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00730</t>
+          <t>CM-26-01494</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -6677,48 +6437,48 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>La Violette</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Château La Violette</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>17'433.26</t>
+          <t>17'751.48</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.1266</v>
+        <v>0.1464</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.2069</v>
+        <v>0.2107</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.1587</v>
+        <v>0.1721</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -6727,58 +6487,58 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02972</t>
+          <t>CM-26-00730</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita</t>
+          <t>La Violette</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Château La Violette</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>1'277.97</t>
+          <t>17'433.26</t>
         </is>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.2466</v>
+        <v>0.1266</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.0152</v>
+        <v>0.2069</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.154</v>
+        <v>0.1587</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -6787,7 +6547,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02689</t>
+          <t>CM-25-02972</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -6797,7 +6557,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges la Perrière</t>
+          <t>Finca Piedra Infinita</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -6807,38 +6567,38 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Domaine Gouges Henri</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>3'300.53</t>
+          <t>1'277.97</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.222</v>
+        <v>0.2466</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.0392</v>
+        <v>0.0152</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.1489</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -6847,7 +6607,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01500</t>
+          <t>CM-25-02689</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -6857,48 +6617,48 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Nuits Saint Georges la Perrière</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Gouges Henri</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2'258.69</t>
+          <t>3'300.53</t>
         </is>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.2244</v>
+        <v>0.222</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.0268</v>
+        <v>0.0392</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.1454</v>
+        <v>0.1489</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -6907,58 +6667,58 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-26-01500</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>24'206.56</t>
+          <t>2'258.69</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.2244</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.2874</v>
+        <v>0.0268</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.1427</v>
+        <v>0.1454</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -6967,58 +6727,58 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00594</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mordorée</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Maison M. Chapoutier</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>12'780.81</t>
+          <t>24'206.56</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.1362</v>
+        <v>0.0462</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.1517</v>
+        <v>0.2874</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.1424</v>
+        <v>0.1427</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -7027,7 +6787,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02637</t>
+          <t>CM-26-00594</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -7037,48 +6797,48 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Hommage à Jacques Perrin</t>
+          <t>Côte Rôtie La Mordorée</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Château de Beaucastel</t>
+          <t>Maison M. Chapoutier</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>1'587.81</t>
+          <t>12'780.81</t>
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.1362</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.0188</v>
+        <v>0.1517</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.136</v>
+        <v>0.1424</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -7087,58 +6847,58 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-25-02637</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Hommage à Jacques Perrin</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château de Beaucastel</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>313</v>
+        <v>28</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>22'583.46</t>
+          <t>1'587.81</t>
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.0192</v>
+        <v>0.2142</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.2681</v>
+        <v>0.0188</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.1188</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -7147,7 +6907,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01284</t>
+          <t>CM-26-01582</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -7157,48 +6917,48 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>45</v>
+        <v>443</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>8'112.00</t>
+          <t>17'926.78</t>
         </is>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.1332</v>
+        <v>0.081</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.0963</v>
+        <v>0.2128</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.1184</v>
+        <v>0.1337</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -7207,58 +6967,58 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02474</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Mazoyères-Chambertin</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Arnaud Mortet</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>150</v>
+        <v>313</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>9'311.67</t>
+          <t>22'583.46</t>
         </is>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0.12</v>
+        <v>0.0192</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.1105</v>
+        <v>0.2681</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.1162</v>
+        <v>0.1188</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -7267,58 +7027,58 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="I52" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>12'848.80</t>
+          <t>8'112.00</t>
         </is>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.081</v>
+        <v>0.1332</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.1525</v>
+        <v>0.0963</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.1096</v>
+        <v>0.1184</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -7327,58 +7087,58 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00779</t>
+          <t>CM-25-02474</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Mazoyères-Chambertin</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Arnaud Mortet</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>10'707.33</t>
+          <t>9'311.67</t>
         </is>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0.0936</v>
+        <v>0.12</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.1271</v>
+        <v>0.1105</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.107</v>
+        <v>0.1162</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -7387,58 +7147,58 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02628</t>
+          <t>CM-26-00963</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Grillet Blanc</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Château Grillet</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>6'957.56</t>
+          <t>12'848.80</t>
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.1218</v>
+        <v>0.081</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.1525</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.1061</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -7447,7 +7207,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-26-00779</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -7457,48 +7217,48 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>11'095.00</t>
+          <t>10'707.33</t>
         </is>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0936</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.1317</v>
+        <v>0.1271</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.1034</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -7507,7 +7267,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-25-02628</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -7517,7 +7277,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Grillet Blanc</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -7527,38 +7287,38 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Grillet</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>317</v>
+        <v>197</v>
       </c>
       <c r="I56" s="4" t="n">
         <v>4</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>12'118.06</t>
+          <t>6'957.56</t>
         </is>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.0756</v>
+        <v>0.1218</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.1439</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.1029</v>
+        <v>0.1061</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -7567,58 +7327,58 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00772</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>198</v>
+        <v>317</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>10'109.38</t>
+          <t>12'118.06</t>
         </is>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.0912</v>
+        <v>0.0756</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.12</v>
+        <v>0.1439</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.1027</v>
+        <v>0.1029</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -7627,7 +7387,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-00772</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -7637,48 +7397,48 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>10'109.38</t>
         </is>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.1248</v>
+        <v>0.0912</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.0684</v>
+        <v>0.12</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.1022</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -7687,58 +7447,58 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01320</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I59" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>4'696.54</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L59" s="6" t="n">
-        <v>0.132</v>
+        <v>0.1248</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0.0558</v>
+        <v>0.0684</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.1015</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -7747,7 +7507,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01550</t>
+          <t>CM-26-01320</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -7757,48 +7517,48 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>8'731.46</t>
+          <t>4'696.54</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.099</v>
+        <v>0.132</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.1036</v>
+        <v>0.0558</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.1008</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -8328,17 +8088,17 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>690.03</t>
+          <t>697.16</t>
         </is>
       </c>
       <c r="L69" s="6" t="n">
         <v>0.1134</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>0.0713</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -8587,58 +8347,58 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-26-01550</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>257</v>
+        <v>121</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>3'382.19</t>
+          <t>4'195.80</t>
         </is>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.0468</v>
+        <v>0.0498</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.0401</v>
+        <v>0.0498</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.0441</v>
+        <v>0.0498</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -8647,7 +8407,7 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -8657,12 +8417,12 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -8676,29 +8436,29 @@
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>323</v>
+        <v>257</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2'912.26</t>
+          <t>3'382.19</t>
         </is>
       </c>
       <c r="L75" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0468</v>
       </c>
       <c r="M75" s="6" t="n">
-        <v>0.0346</v>
+        <v>0.0401</v>
       </c>
       <c r="N75" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -8707,58 +8467,58 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00851</t>
+          <t>CM-26-01265</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>4'218.04</t>
+          <t>2'912.26</t>
         </is>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.0222</v>
+        <v>0.0372</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.0501</v>
+        <v>0.0346</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.0334</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -8767,58 +8527,58 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02656</t>
+          <t>CM-26-00851</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>Weingut Markus Molitor</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>1'865.44</t>
+          <t>4'218.04</t>
         </is>
       </c>
       <c r="L77" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0222</v>
       </c>
       <c r="M77" s="6" t="n">
-        <v>0.0221</v>
+        <v>0.0501</v>
       </c>
       <c r="N77" s="6" t="n">
-        <v>0.0312</v>
+        <v>0.0334</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -8827,7 +8587,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01497</t>
+          <t>CM-25-02656</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -8837,48 +8597,48 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Weingut Markus Molitor</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>483</v>
+        <v>324</v>
       </c>
       <c r="I78" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>1'936.52</t>
+          <t>1'865.44</t>
         </is>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0.0246</v>
+        <v>0.0372</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>0.023</v>
+        <v>0.0221</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>0.024</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -8887,17 +8647,17 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-01497</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -8912,33 +8672,33 @@
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>280</v>
+        <v>483</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>568.18</t>
+          <t>1'936.52</t>
         </is>
       </c>
       <c r="L79" s="6" t="n">
-        <v>0.0216</v>
+        <v>0.0246</v>
       </c>
       <c r="M79" s="6" t="n">
-        <v>0.0067</v>
+        <v>0.023</v>
       </c>
       <c r="N79" s="6" t="n">
-        <v>0.0156</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -8947,58 +8707,58 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>92</v>
+        <v>280</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>568.18</t>
         </is>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -9007,7 +8767,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -9017,26 +8777,26 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I81" s="6" t="n">
         <v>0</v>
@@ -9067,7 +8827,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -9077,26 +8837,26 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>49</v>
+        <v>643</v>
       </c>
       <c r="I82" s="4" t="n">
         <v>0</v>
@@ -9127,7 +8887,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -9137,26 +8897,26 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>543</v>
+        <v>42</v>
       </c>
       <c r="I83" s="6" t="n">
         <v>0</v>
@@ -9187,7 +8947,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -9202,7 +8962,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -9212,11 +8972,11 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>362</v>
+        <v>252</v>
       </c>
       <c r="I84" s="4" t="n">
         <v>0</v>
@@ -9247,7 +9007,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -9257,26 +9017,26 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="I85" s="6" t="n">
         <v>0</v>
@@ -9307,7 +9067,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -9317,26 +9077,26 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="I86" s="4" t="n">
         <v>0</v>
@@ -9367,7 +9127,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -9377,26 +9137,26 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>129</v>
+        <v>362</v>
       </c>
       <c r="I87" s="6" t="n">
         <v>0</v>
@@ -9427,7 +9187,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -9437,26 +9197,26 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I88" s="4" t="n">
         <v>0</v>
@@ -9487,7 +9247,7 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -9497,26 +9257,26 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>252</v>
+        <v>75</v>
       </c>
       <c r="I89" s="6" t="n">
         <v>0</v>
@@ -9547,7 +9307,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -9557,26 +9317,26 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="I90" s="4" t="n">
         <v>0</v>
@@ -9607,7 +9367,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -9617,26 +9377,26 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>643</v>
+        <v>92</v>
       </c>
       <c r="I91" s="6" t="n">
         <v>0</v>
@@ -9667,7 +9427,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -9677,26 +9437,26 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H92" s="4" t="n">
-        <v>103</v>
+        <v>543</v>
       </c>
       <c r="I92" s="4" t="n">
         <v>0</v>
@@ -9727,7 +9487,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -9737,26 +9497,26 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="I93" s="6" t="n">
         <v>0</v>
@@ -9787,7 +9547,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01479</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -9797,26 +9557,26 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H94" s="4" t="n">
-        <v>152</v>
+        <v>63</v>
       </c>
       <c r="I94" s="4" t="n">
         <v>0</v>
@@ -9847,36 +9607,36 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01349</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="H95" s="6" t="n">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="I95" s="6" t="n">
         <v>0</v>
@@ -9907,7 +9667,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -9922,7 +9682,7 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -9936,7 +9696,7 @@
         </is>
       </c>
       <c r="H96" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I96" s="4" t="n">
         <v>0</v>
@@ -9967,7 +9727,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -9982,7 +9742,7 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
@@ -9992,11 +9752,11 @@
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H97" s="6" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="I97" s="6" t="n">
         <v>0</v>
@@ -10027,7 +9787,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -10037,17 +9797,17 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -10056,7 +9816,7 @@
         </is>
       </c>
       <c r="H98" s="4" t="n">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="I98" s="4" t="n">
         <v>0</v>
@@ -10087,7 +9847,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01288</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -10097,26 +9857,26 @@
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H99" s="6" t="n">
-        <v>240</v>
+        <v>104</v>
       </c>
       <c r="I99" s="6" t="n">
         <v>0</v>
@@ -10147,7 +9907,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01310</t>
+          <t>CM-26-01288</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -10157,26 +9917,26 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H100" s="4" t="n">
-        <v>716</v>
+        <v>240</v>
       </c>
       <c r="I100" s="4" t="n">
         <v>0</v>
@@ -10207,36 +9967,36 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01341</t>
+          <t>CM-26-01310</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>Cathiard Vineyard</t>
+          <t>Domaine Georges Roumier</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H101" s="6" t="n">
-        <v>91</v>
+        <v>716</v>
       </c>
       <c r="I101" s="6" t="n">
         <v>0</v>
@@ -10267,7 +10027,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01349</t>
+          <t>CM-26-01341</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -10277,26 +10037,26 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Cathiard Vineyard</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H102" s="4" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I102" s="4" t="n">
         <v>0</v>
@@ -10387,22 +10147,22 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01482</t>
+          <t>CM-26-01479</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -10416,7 +10176,7 @@
         </is>
       </c>
       <c r="H104" s="4" t="n">
-        <v>36</v>
+        <v>152</v>
       </c>
       <c r="I104" s="4" t="n">
         <v>0</v>
@@ -10447,36 +10207,36 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01508</t>
+          <t>CM-26-01482</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>L'Ermita</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>Alvaro Palacios</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H105" s="6" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I105" s="6" t="n">
         <v>0</v>
@@ -10507,7 +10267,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01512</t>
+          <t>CM-26-01508</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -10517,17 +10277,17 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>L'Ermita</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Alvaro Palacios</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -10536,7 +10296,7 @@
         </is>
       </c>
       <c r="H106" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I106" s="4" t="n">
         <v>0</v>
@@ -10567,22 +10327,22 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01513</t>
+          <t>CM-26-01512</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
@@ -10596,7 +10356,7 @@
         </is>
       </c>
       <c r="H107" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I107" s="6" t="n">
         <v>0</v>
@@ -10627,62 +10387,182 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
+          <t>CM-26-01513</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01614</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>DRC la Tâche</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="n">
+        <v>461</v>
+      </c>
+      <c r="I109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
           <t>CM-25-02438</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C110" s="4" t="inlineStr">
         <is>
           <t>🟣</t>
         </is>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
         <is>
           <t>DRC Romanée Conti</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
+      <c r="E110" s="4" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr">
+      <c r="F110" s="4" t="inlineStr">
         <is>
           <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
-      <c r="G108" s="4" t="inlineStr">
+      <c r="G110" s="4" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="H108" s="4" t="n">
+      <c r="H110" s="4" t="n">
         <v>410</v>
       </c>
-      <c r="I108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
+      <c r="I110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K108" s="4" t="inlineStr">
+      <c r="K110" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" s="4" t="n">
+      <c r="L110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N108"/>
+  <autoFilter ref="A3:N110"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-26 08:35  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-06-02 15:38  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -825,14 +825,14 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>39'362.80</t>
+          <t>39'353.86</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
         <v>0.5597</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.4673</v>
+        <v>0.4672</v>
       </c>
       <c r="N7" s="6" t="n">
         <v>0.5227000000000001</v>
@@ -1365,17 +1365,17 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>6'652.43</t>
+          <t>6'458.03</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
         <v>0.4997</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.079</v>
+        <v>0.0767</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3314</v>
+        <v>0.3305</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-26-01535</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1574,48 +1574,48 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>3'517.88</t>
+          <t>31'223.10</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.4895</v>
+        <v>0.2729</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0418</v>
+        <v>0.3706</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.3104</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1624,58 +1624,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>3'517.88</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.3827</v>
+        <v>0.4895</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1902</v>
+        <v>0.0418</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.3057</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1694,48 +1694,48 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>184</v>
+        <v>47</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0324</v>
+        <v>0.3827</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6896</v>
+        <v>0.1902</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2953</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1754,48 +1754,48 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>34'832.71</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2142</v>
+        <v>0.0324</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.4135</v>
+        <v>0.6896</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2939</v>
+        <v>0.2953</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1804,58 +1804,58 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01535</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>26'304.45</t>
+          <t>34'794.10</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.2142</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.3123</v>
+        <v>0.413</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2887</v>
+        <v>0.2937</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1984,58 +1984,58 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>20'518.08</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.2771</v>
+        <v>0.1278</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.2436</v>
+        <v>0.4545</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2637</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2054,48 +2054,48 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.1224</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.4309</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2585</v>
+        <v>0.2458</v>
       </c>
     </row>
   </sheetData>
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 19 May 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 26 May 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-26 08:35  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-06-02 15:38  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,186 +2221,66 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01582</t>
+          <t>CM-26-01680</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>DRC Richebourg</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>443</v>
+        <v>205</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>17'926.78</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.2128</v>
+        <v>0</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.1337</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="6" t="n">
-        <v>71</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01550</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>121</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>0.83%</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>4'195.80</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>0.0498</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>0.0498</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>0.0498</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01614</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>DRC la Tâche</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>461</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N6"/>
+  <autoFilter ref="A3:N4"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2437,14 +2317,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 26 Apr 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 03 May 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-26 08:35  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-06-02 15:38  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2747,77 +2627,77 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>6'652.43</t>
+          <t>6'458.03</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
         <v>0.4997</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.079</v>
+        <v>0.0767</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3314</v>
+        <v>0.3305</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-01535</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>31'223.10</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0324</v>
+        <v>0.2729</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.6896</v>
+        <v>0.3706</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2953</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2826,7 +2706,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -2836,48 +2716,48 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>34'832.71</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2142</v>
+        <v>0.0324</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.4135</v>
+        <v>0.6896</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2939</v>
+        <v>0.2953</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2886,67 +2766,67 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01535</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>26'304.45</t>
+          <t>34'794.10</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.2142</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3123</v>
+        <v>0.413</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2887</v>
+        <v>0.2937</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -2956,132 +2836,132 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>43'696.73</t>
+          <t>21'358.58</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1332</v>
+        <v>0.1692</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.5187</v>
+        <v>0.2535</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2874</v>
+        <v>0.2029</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-26-01486</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>21'358.58</t>
+          <t>3'550.60</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1692</v>
+        <v>0.2729</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2535</v>
+        <v>0.0421</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.2029</v>
+        <v>0.1806</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01486</t>
+          <t>CM-26-01494</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3095,94 +2975,94 @@
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>3'550.60</t>
+          <t>17'751.48</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2729</v>
+        <v>0.1464</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0421</v>
+        <v>0.2107</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1806</v>
+        <v>0.1721</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01494</t>
+          <t>CM-26-01582</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>41</v>
+        <v>940</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>17'751.48</t>
+          <t>23'435.32</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1464</v>
+        <v>0.0636</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2107</v>
+        <v>0.2782</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1721</v>
+        <v>0.1494</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
@@ -3227,7 +3107,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2'258.69</t>
+          <t>2'260.35</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
@@ -3242,11 +3122,11 @@
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01582</t>
+          <t>CM-26-01550</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3256,187 +3136,187 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>443</v>
+        <v>121</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>17'926.78</t>
+          <t>8'391.60</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.081</v>
+        <v>0.099</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2128</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1337</v>
+        <v>0.0992</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01376</t>
+          <t>CM-26-01542</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Bollinger</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>348</v>
+        <v>87</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>14'566.45</t>
+          <t>2'427.03</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0516</v>
+        <v>0.138</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1729</v>
+        <v>0.0288</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1001</v>
+        <v>0.09429999999999999</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01542</t>
+          <t>CM-26-01480</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2'427.03</t>
+          <t>7'358.85</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.138</v>
+        <v>0.0882</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0288</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.08790000000000001</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01480</t>
+          <t>CM-26-01481</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -3446,67 +3326,67 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>68</v>
+        <v>252</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>7'397.86</t>
+          <t>2'329.06</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0878</v>
+        <v>0.0276</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.0539</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01481</t>
+          <t>CM-26-01495</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -3515,48 +3395,48 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>252</v>
+        <v>393</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2'329.06</t>
+          <t>2'846.36</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0612</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0276</v>
+        <v>0.0338</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0539</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01495</t>
+          <t>CM-26-01497</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -3575,187 +3455,187 @@
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>393</v>
+        <v>483</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2'846.36</t>
+          <t>2'014.95</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0612</v>
+        <v>0.0246</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0338</v>
+        <v>0.0239</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0502</v>
+        <v>0.0243</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01550</t>
+          <t>CM-26-01477</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>4'195.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0498</v>
+        <v>0</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0498</v>
+        <v>0</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01497</t>
+          <t>CM-26-01479</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>483</v>
+        <v>152</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>1'936.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0246</v>
+        <v>0</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01349</t>
+          <t>CM-26-01482</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>0</v>
@@ -3782,40 +3662,40 @@
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01341</t>
+          <t>CM-26-01508</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>L'Ermita</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Cathiard Vineyard</t>
+          <t>Alvaro Palacios</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
@@ -3842,11 +3722,11 @@
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01477</t>
+          <t>CM-26-01512</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -3856,7 +3736,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -3871,11 +3751,11 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>0</v>
@@ -3902,26 +3782,26 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01479</t>
+          <t>CM-26-01513</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -3931,11 +3811,11 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
@@ -3962,40 +3842,40 @@
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01482</t>
+          <t>CM-26-01614</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>36</v>
+        <v>613</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>0</v>
@@ -4036,7 +3916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N110"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4065,7 +3945,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-26 08:35  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-06-02 15:38  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4368,14 +4248,14 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>39'362.80</t>
+          <t>39'353.86</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
         <v>0.5597</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.4673</v>
+        <v>0.4672</v>
       </c>
       <c r="N7" s="6" t="n">
         <v>0.5227000000000001</v>
@@ -4908,17 +4788,17 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>6'652.43</t>
+          <t>6'458.03</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
         <v>0.4997</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.079</v>
+        <v>0.0767</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3314</v>
+        <v>0.3305</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -5107,7 +4987,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-26-01535</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -5117,48 +4997,48 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>3'517.88</t>
+          <t>31'223.10</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.4895</v>
+        <v>0.2729</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0418</v>
+        <v>0.3706</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.3104</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -5167,58 +5047,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>16'018.57</t>
+          <t>3'517.88</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.3827</v>
+        <v>0.4895</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1902</v>
+        <v>0.0418</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.3057</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -5227,7 +5107,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -5237,48 +5117,48 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>184</v>
+        <v>47</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>16'018.57</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0324</v>
+        <v>0.3827</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6896</v>
+        <v>0.1902</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2953</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -5287,7 +5167,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -5297,48 +5177,48 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>34'832.71</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2142</v>
+        <v>0.0324</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.4135</v>
+        <v>0.6896</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2939</v>
+        <v>0.2953</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -5347,58 +5227,58 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01535</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>26'304.45</t>
+          <t>34'794.10</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.2142</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.3123</v>
+        <v>0.413</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2887</v>
+        <v>0.2937</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -5527,58 +5407,58 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>20'518.08</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.2771</v>
+        <v>0.1278</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.2436</v>
+        <v>0.4545</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2637</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5587,7 +5467,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -5597,48 +5477,48 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.1224</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.4309</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2585</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5647,58 +5527,58 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>49</v>
+        <v>195</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>4.10%</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>18'268.08</t>
         </is>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.1224</v>
+        <v>0.246</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.4309</v>
+        <v>0.2169</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2458</v>
+        <v>0.2344</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -6607,58 +6487,58 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02689</t>
+          <t>CM-26-01582</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges la Perrière</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Domaine Gouges Henri</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>135</v>
+        <v>940</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>3'300.53</t>
+          <t>23'435.32</t>
         </is>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.222</v>
+        <v>0.0636</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.0392</v>
+        <v>0.2782</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.1489</v>
+        <v>0.1494</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -6667,7 +6547,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01500</t>
+          <t>CM-25-02689</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -6677,48 +6557,48 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Nuits Saint Georges la Perrière</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Gouges Henri</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2'258.69</t>
+          <t>3'300.53</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.2244</v>
+        <v>0.222</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.0268</v>
+        <v>0.0392</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.1454</v>
+        <v>0.1489</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -6727,58 +6607,58 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-26-01500</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>24'206.56</t>
+          <t>2'260.35</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.0462</v>
+        <v>0.2244</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.2874</v>
+        <v>0.0268</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.1427</v>
+        <v>0.1454</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -6787,58 +6667,58 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00594</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mordorée</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Maison M. Chapoutier</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>12'780.81</t>
+          <t>24'206.56</t>
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.1362</v>
+        <v>0.0462</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.1517</v>
+        <v>0.2874</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.1424</v>
+        <v>0.1427</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -6847,7 +6727,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02637</t>
+          <t>CM-26-00594</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -6857,48 +6737,48 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Hommage à Jacques Perrin</t>
+          <t>Côte Rôtie La Mordorée</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Château de Beaucastel</t>
+          <t>Maison M. Chapoutier</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>1'587.81</t>
+          <t>12'780.81</t>
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.2142</v>
+        <v>0.1362</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.0188</v>
+        <v>0.1517</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.136</v>
+        <v>0.1424</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -6907,7 +6787,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01582</t>
+          <t>CM-25-02637</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -6917,48 +6797,48 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Hommage à Jacques Perrin</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Château de Beaucastel</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>443</v>
+        <v>28</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>17'926.78</t>
+          <t>1'587.81</t>
         </is>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.081</v>
+        <v>0.2142</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.2128</v>
+        <v>0.0188</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.1337</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -7368,14 +7248,14 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>12'118.06</t>
+          <t>12'111.33</t>
         </is>
       </c>
       <c r="L57" s="6" t="n">
         <v>0.0756</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.1439</v>
+        <v>0.1438</v>
       </c>
       <c r="N57" s="6" t="n">
         <v>0.1029</v>
@@ -7627,58 +7507,58 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01542</t>
+          <t>CM-26-01550</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2'427.03</t>
+          <t>8'391.60</t>
         </is>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.138</v>
+        <v>0.099</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.0288</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0992</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -7687,58 +7567,58 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-26-01542</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>487</v>
+        <v>87</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>2'427.03</t>
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.138</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>0.1716</v>
+        <v>0.0288</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>0.091</v>
+        <v>0.09429999999999999</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -7747,58 +7627,58 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>235</v>
+        <v>487</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2'738.04</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.0372</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.0325</v>
+        <v>0.1716</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.0897</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -7807,58 +7687,58 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01480</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>68</v>
+        <v>235</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>7'397.86</t>
+          <t>2'738.04</t>
         </is>
       </c>
       <c r="L65" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.1278</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>0.0878</v>
+        <v>0.0325</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -7867,7 +7747,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00658</t>
+          <t>CM-26-01480</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -7877,7 +7757,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Assortment de Grands Crus (12 bottles)</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -7887,12 +7767,12 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Domaine Ponsot</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
@@ -7908,17 +7788,17 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>7'018.00</t>
+          <t>7'358.85</t>
         </is>
       </c>
       <c r="L66" s="4" t="n">
         <v>0.0882</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.0862</v>
+        <v>0.08790000000000001</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -7927,58 +7807,58 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03004</t>
+          <t>CM-26-00658</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Assortment de Grands Crus (12 bottles)</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine Ponsot</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>10'547.81</t>
+          <t>7'018.00</t>
         </is>
       </c>
       <c r="L67" s="6" t="n">
-        <v>0.0504</v>
+        <v>0.0882</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>0.1252</v>
+        <v>0.0833</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>0.0803</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -7987,58 +7867,58 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02535</t>
+          <t>CM-25-03004</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Meursault Clos des Bouchers</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Domaine Jean Marc Roulot</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>268</v>
+        <v>476</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>10'885.80</t>
+          <t>10'547.81</t>
         </is>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.045</v>
+        <v>0.0504</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0.1292</v>
+        <v>0.1252</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0803</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -8047,58 +7927,58 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00483</t>
+          <t>CM-25-02535</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Pie Franco</t>
+          <t>Meursault Clos des Bouchers</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Bodegas Casa Castillo</t>
+          <t>Domaine Jean Marc Roulot</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>53</v>
+        <v>268</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>697.16</t>
+          <t>10'885.80</t>
         </is>
       </c>
       <c r="L69" s="6" t="n">
-        <v>0.1134</v>
+        <v>0.045</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>0.0083</v>
+        <v>0.1292</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -8107,7 +7987,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02609</t>
+          <t>CM-26-00483</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -8117,48 +7997,48 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Clos de la Roche</t>
+          <t>Pie Franco</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Lignier</t>
+          <t>Bodegas Casa Castillo</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>233</v>
+        <v>53</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>5'003.90</t>
+          <t>697.16</t>
         </is>
       </c>
       <c r="L70" s="4" t="n">
-        <v>0.0774</v>
+        <v>0.1134</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.0594</v>
+        <v>0.0083</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.0702</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -8167,7 +8047,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01481</t>
+          <t>CM-25-02609</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -8177,48 +8057,48 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Clos de la Roche</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Domaine Georges Lignier</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="I71" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2'329.06</t>
+          <t>5'003.90</t>
         </is>
       </c>
       <c r="L71" s="6" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0774</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>0.0276</v>
+        <v>0.0594</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>0.0539</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -8227,58 +8107,58 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-26-01481</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>100</v>
+        <v>252</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>3'049.20</t>
+          <t>2'329.06</t>
         </is>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.06</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.0362</v>
+        <v>0.0276</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.0505</v>
+        <v>0.0539</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -8287,58 +8167,58 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01495</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>393</v>
+        <v>100</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2'846.36</t>
+          <t>3'049.20</t>
         </is>
       </c>
       <c r="L73" s="6" t="n">
-        <v>0.0612</v>
+        <v>0.06</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>0.0338</v>
+        <v>0.0362</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>0.0502</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -8347,58 +8227,58 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01550</t>
+          <t>CM-26-01495</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>121</v>
+        <v>393</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>4'195.80</t>
+          <t>2'846.36</t>
         </is>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.0498</v>
+        <v>0.0612</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.0498</v>
+        <v>0.0338</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.0498</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -8688,17 +8568,17 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>1'936.52</t>
+          <t>2'014.95</t>
         </is>
       </c>
       <c r="L79" s="6" t="n">
         <v>0.0246</v>
       </c>
       <c r="M79" s="6" t="n">
-        <v>0.023</v>
+        <v>0.0239</v>
       </c>
       <c r="N79" s="6" t="n">
-        <v>0.024</v>
+        <v>0.0243</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -8767,7 +8647,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -8777,26 +8657,26 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="I81" s="6" t="n">
         <v>0</v>
@@ -8827,7 +8707,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -8837,26 +8717,26 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>643</v>
+        <v>63</v>
       </c>
       <c r="I82" s="4" t="n">
         <v>0</v>
@@ -8887,7 +8767,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -8897,26 +8777,26 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I83" s="6" t="n">
         <v>0</v>
@@ -8947,7 +8827,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -8957,26 +8837,26 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>252</v>
+        <v>543</v>
       </c>
       <c r="I84" s="4" t="n">
         <v>0</v>
@@ -9007,7 +8887,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -9017,26 +8897,26 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="I85" s="6" t="n">
         <v>0</v>
@@ -9067,7 +8947,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -9077,26 +8957,26 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="I86" s="4" t="n">
         <v>0</v>
@@ -9127,7 +9007,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -9137,26 +9017,26 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="I87" s="6" t="n">
         <v>0</v>
@@ -9187,7 +9067,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -9197,26 +9077,26 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>103</v>
+        <v>362</v>
       </c>
       <c r="I88" s="4" t="n">
         <v>0</v>
@@ -9247,7 +9127,7 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -9257,26 +9137,26 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="I89" s="6" t="n">
         <v>0</v>
@@ -9307,7 +9187,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -9317,26 +9197,26 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="I90" s="4" t="n">
         <v>0</v>
@@ -9367,7 +9247,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -9377,26 +9257,26 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>92</v>
+        <v>252</v>
       </c>
       <c r="I91" s="6" t="n">
         <v>0</v>
@@ -9427,7 +9307,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -9437,26 +9317,26 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H92" s="4" t="n">
-        <v>543</v>
+        <v>42</v>
       </c>
       <c r="I92" s="4" t="n">
         <v>0</v>
@@ -9487,7 +9367,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -9497,26 +9377,26 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
-        <v>49</v>
+        <v>643</v>
       </c>
       <c r="I93" s="6" t="n">
         <v>0</v>
@@ -9547,7 +9427,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -9557,26 +9437,26 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H94" s="4" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I94" s="4" t="n">
         <v>0</v>
@@ -9607,36 +9487,36 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01349</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H95" s="6" t="n">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="I95" s="6" t="n">
         <v>0</v>
@@ -9667,36 +9547,36 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01349</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="H96" s="4" t="n">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="I96" s="4" t="n">
         <v>0</v>
@@ -10476,7 +10356,7 @@
         </is>
       </c>
       <c r="H109" s="6" t="n">
-        <v>461</v>
+        <v>613</v>
       </c>
       <c r="I109" s="6" t="n">
         <v>0</v>
@@ -10507,62 +10387,122 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
+          <t>CM-26-01680</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>DRC Richebourg</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="I110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
           <t>CM-25-02438</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>🟣</t>
         </is>
       </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="D111" s="7" t="inlineStr">
         <is>
           <t>DRC Romanée Conti</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
+      <c r="E111" s="6" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
-      <c r="G110" s="4" t="inlineStr">
+      <c r="G111" s="6" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="H110" s="4" t="n">
+      <c r="H111" s="6" t="n">
         <v>410</v>
       </c>
-      <c r="I110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
+      <c r="I111" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K110" s="4" t="inlineStr">
+      <c r="K111" s="6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N110" s="4" t="n">
+      <c r="L111" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="6" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N110"/>
+  <autoFilter ref="A3:N111"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-08 14:52  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-06-10 15:58  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -645,17 +645,17 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>35'444.01</t>
+          <t>37'482.23</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.4208</v>
+        <v>0.6452</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.7683</v>
+        <v>0.8581</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -712,10 +712,10 @@
         <v>0.769</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4418</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6381</v>
+        <v>0.7176</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -724,58 +724,58 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01041</t>
+          <t>CM-26-01439</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Viña Tondonia Gran Reserva</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Bodegas López de Heredia Viña Tondonia</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>11.11%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>5'717.80</t>
+          <t>39'065.00</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.8335</v>
+        <v>0.5555</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.0679</v>
+        <v>0.6724</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.5273</v>
+        <v>0.6022999999999999</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -784,7 +784,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01439</t>
+          <t>CM-26-00749</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -794,48 +794,48 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>11.11%</t>
+          <t>9.33%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>39'065.00</t>
+          <t>39'344.92</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.5555</v>
+        <v>0.4665</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.4637</v>
+        <v>0.6772</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5188</v>
+        <v>0.5508</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -844,58 +844,58 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00749</t>
+          <t>CM-26-01041</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Viña Tondonia Gran Reserva</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Bodegas López de Heredia Viña Tondonia</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>9.33%</t>
+          <t>16.67%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>39'344.92</t>
+          <t>5'717.80</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.4665</v>
+        <v>0.8335</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4671</v>
+        <v>0.0984</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4667</v>
+        <v>0.5395</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -904,58 +904,58 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01461</t>
+          <t>CM-25-02970</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Landonne</t>
+          <t>Finca Piedra Infinita Gravascal</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>31</v>
+        <v>512</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>12.90%</t>
+          <t>6.45%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>11'271.04</t>
+          <t>48'377.02</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.645</v>
+        <v>0.3225</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1338</v>
+        <v>0.8327</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4405</v>
+        <v>0.5266</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -964,58 +964,58 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02472</t>
+          <t>CM-26-01461</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Clos de Vougeot</t>
+          <t>Côte Rôtie La Landonne</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leroy</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>12.90%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>84'240.00</t>
+          <t>11'271.04</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.043</v>
+        <v>0.645</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1</v>
+        <v>0.194</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.4258</v>
+        <v>0.4646</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -1024,58 +1024,58 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02970</t>
+          <t>CM-26-00724</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita Gravascal</t>
+          <t>Cheval Blanc</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Château Cheval Blanc</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>512</v>
+        <v>106</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>48'512.22</t>
+          <t>53'840.62</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3225</v>
+        <v>0.1415</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.5759</v>
+        <v>0.9268</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4239</v>
+        <v>0.4556</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1084,58 +1084,58 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01175</t>
+          <t>CM-26-00293</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Latour (Ex-Château)</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>15'223.41</t>
+          <t>51'964.65</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5405</v>
+        <v>0.1615</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1807</v>
+        <v>0.8945</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3966</v>
+        <v>0.4547</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01757</t>
+          <t>CM-26-01175</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Duclot 9 bottles Case Bordeaux Collection (1 x 75cl of each Petrus, Mouton, Lafite, Latour, Margaux, Haut Brion, Mission, Cheval, Yquem)</t>
+          <t>Côte Rôtie La Mouline</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1164,38 +1164,38 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Groupe Duclot</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>8.70%</t>
+          <t>10.81%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>22'358.22</t>
+          <t>15'223.41</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.435</v>
+        <v>0.5405</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2654</v>
+        <v>0.262</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3672</v>
+        <v>0.4291</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1204,58 +1204,58 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01431</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>56</v>
+        <v>184</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>10.71%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>5'680.00</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5355</v>
+        <v>0.027</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0674</v>
+        <v>1</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.4162</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00293</t>
+          <t>CM-26-01757</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1274,48 +1274,48 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Latour (Ex-Château)</t>
+          <t>Duclot 9 bottles Case Bordeaux Collection (1 x 75cl of each Petrus, Mouton, Lafite, Latour, Margaux, Haut Brion, Mission, Cheval, Yquem)</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Groupe Duclot</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>8.70%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>51'964.65</t>
+          <t>21'487.96</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1615</v>
+        <v>0.435</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.6169</v>
+        <v>0.3699</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.3437</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1324,58 +1324,58 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00724</t>
+          <t>CM-25-02625</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Cheval Blanc</t>
+          <t>Rumbo al Norte</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Château Cheval Blanc</t>
+          <t>Bodega Comando G</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>53'840.62</t>
+          <t>37'852.12</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1415</v>
+        <v>0.206</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.6391</v>
+        <v>0.6515</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3405</v>
+        <v>0.3842</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00771</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1394,48 +1394,48 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>10'123.30</t>
+          <t>43'696.73</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.4545</v>
+        <v>0.111</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1202</v>
+        <v>0.7522</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3208</v>
+        <v>0.3675</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1444,58 +1444,58 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02625</t>
+          <t>CM-26-00871</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Rumbo al Norte</t>
+          <t>Chambertin Très Vieilles Vignes</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Bodega Comando G</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>170</v>
+        <v>38</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>37'852.12</t>
+          <t>29'483.52</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.206</v>
+        <v>0.263</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.4493</v>
+        <v>0.5075</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3033</v>
+        <v>0.3608</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1504,58 +1504,58 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00871</t>
+          <t>CM-26-01431</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>10.71%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>29'483.52</t>
+          <t>5'680.00</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.263</v>
+        <v>0.5355</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.35</v>
+        <v>0.0978</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2978</v>
+        <v>0.3604</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1564,58 +1564,58 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-01535</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>31'223.10</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.027</v>
+        <v>0.2275</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.6896</v>
+        <v>0.5374</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.292</v>
+        <v>0.3515</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1624,58 +1624,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01535</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>31'223.10</t>
+          <t>34'794.10</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.2275</v>
+        <v>0.1785</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.3706</v>
+        <v>0.5989</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2847</v>
+        <v>0.3467</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1684,58 +1684,58 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-00771</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>10'637.89</t>
+          <t>10'123.30</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3845</v>
+        <v>0.4545</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.1263</v>
+        <v>0.1743</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2812</v>
+        <v>0.3424</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1744,58 +1744,58 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01429</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>6'458.03</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.4165</v>
+        <v>0.1065</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0767</v>
+        <v>0.659</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2806</v>
+        <v>0.3275</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1814,48 +1814,48 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>43'696.73</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.111</v>
+        <v>0.102</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5187</v>
+        <v>0.6248</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2741</v>
+        <v>0.3111</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1864,58 +1864,58 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>112</v>
+        <v>26</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>34'794.10</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1785</v>
+        <v>0.3845</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.413</v>
+        <v>0.1831</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2723</v>
+        <v>0.3039</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1972,10 +1972,10 @@
         <v>0.319</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1902</v>
+        <v>0.2757</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2675</v>
+        <v>0.3017</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1994,48 +1994,48 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>3'517.88</t>
+          <t>26'801.63</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.408</v>
+        <v>0.1935</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0418</v>
+        <v>0.4613</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2615</v>
+        <v>0.3006</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2044,58 +2044,58 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01429</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>6'458.03</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1065</v>
+        <v>0.4165</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.1112</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2457</v>
+        <v>0.2944</v>
       </c>
     </row>
   </sheetData>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 01 Jun 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 03 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-08 14:52  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-06-10 15:58  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2266,22 +2266,22 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>35'444.01</t>
+          <t>37'482.23</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.4208</v>
+        <v>0.6452</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.7683</v>
+        <v>0.8581</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
@@ -2326,22 +2326,22 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>22'358.22</t>
+          <t>21'487.96</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
         <v>0.435</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.2654</v>
+        <v>0.3699</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.3672</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -2393,10 +2393,10 @@
         <v>0.023</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1</v>
+        <v>0.145</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.0538</v>
+        <v>0.0718</v>
       </c>
     </row>
   </sheetData>
@@ -2437,14 +2437,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 09 May 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 11 May 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-08 14:52  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-06-10 15:58  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2567,22 +2567,22 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>35'444.01</t>
+          <t>37'482.23</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.4208</v>
+        <v>0.6452</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.7683</v>
+        <v>0.8581</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
@@ -2634,19 +2634,19 @@
         <v>0.645</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.1338</v>
+        <v>0.194</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4405</v>
+        <v>0.4646</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01757</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2656,57 +2656,57 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Duclot 9 bottles Case Bordeaux Collection (1 x 75cl of each Petrus, Mouton, Lafite, Latour, Margaux, Haut Brion, Mission, Cheval, Yquem)</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Groupe Duclot</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>23</v>
+        <v>184</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>8.70%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>22'358.22</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.435</v>
+        <v>0.027</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2654</v>
+        <v>1</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3672</v>
+        <v>0.4162</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-01757</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -2716,53 +2716,53 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Duclot 9 bottles Case Bordeaux Collection (1 x 75cl of each Petrus, Mouton, Lafite, Latour, Margaux, Haut Brion, Mission, Cheval, Yquem)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Groupe Duclot</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>8.70%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>21'487.96</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.027</v>
+        <v>0.435</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.6896</v>
+        <v>0.3699</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.292</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
@@ -2814,94 +2814,94 @@
         <v>0.2275</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.3706</v>
+        <v>0.5374</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2847</v>
+        <v>0.3515</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01494</t>
+          <t>CM-26-01582</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>41</v>
+        <v>940</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>17'751.48</t>
+          <t>24'405.62</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.122</v>
+        <v>0.0585</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2107</v>
+        <v>0.4201</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.1575</v>
+        <v>0.2031</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01486</t>
+          <t>CM-26-01494</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -2915,29 +2915,29 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>3'550.60</t>
+          <t>17'751.48</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2275</v>
+        <v>0.122</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0421</v>
+        <v>0.3056</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1533</v>
+        <v>0.1954</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2946,63 +2946,63 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01582</t>
+          <t>CM-26-01486</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>940</v>
+        <v>22</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>21'030.62</t>
+          <t>3'550.60</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.053</v>
+        <v>0.2275</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2497</v>
+        <v>0.0611</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1317</v>
+        <v>0.1609</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
@@ -3054,15 +3054,15 @@
         <v>0.187</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0268</v>
+        <v>0.0389</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1229</v>
+        <v>0.1278</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
@@ -3114,135 +3114,135 @@
         <v>0.0825</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1444</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0893</v>
+        <v>0.1073</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01542</t>
+          <t>CM-26-01480</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2'427.03</t>
+          <t>7'358.85</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.115</v>
+        <v>0.0735</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0288</v>
+        <v>0.1267</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0805</v>
+        <v>0.0948</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01480</t>
+          <t>CM-26-01542</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>7'358.85</t>
+          <t>2'427.03</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0735</v>
+        <v>0.115</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0418</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0791</v>
+        <v>0.0857</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
@@ -3294,15 +3294,15 @@
         <v>0.023</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1</v>
+        <v>0.145</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0538</v>
+        <v>0.0718</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
@@ -3354,15 +3354,15 @@
         <v>0.0595</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0276</v>
+        <v>0.0401</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0467</v>
+        <v>0.0517</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
@@ -3414,15 +3414,15 @@
         <v>0.051</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0338</v>
+        <v>0.049</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0441</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
@@ -3474,19 +3474,19 @@
         <v>0.0205</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.023</v>
+        <v>0.0333</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0215</v>
+        <v>0.0256</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01477</t>
+          <t>CM-26-01479</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01479</t>
+          <t>CM-26-01477</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-08 14:52  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-06-10 15:58  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>35'444.01</t>
+          <t>37'482.23</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.4208</v>
+        <v>0.6452</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.7683</v>
+        <v>0.8581</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -4195,10 +4195,10 @@
         <v>0.769</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4418</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6381</v>
+        <v>0.7176</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -4207,58 +4207,58 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01041</t>
+          <t>CM-26-01439</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Viña Tondonia Gran Reserva</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Bodegas López de Heredia Viña Tondonia</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>11.11%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>5'717.80</t>
+          <t>39'065.00</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.8335</v>
+        <v>0.5555</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.0679</v>
+        <v>0.6724</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.5273</v>
+        <v>0.6022999999999999</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01439</t>
+          <t>CM-26-00749</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -4277,48 +4277,48 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>11.11%</t>
+          <t>9.33%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>39'065.00</t>
+          <t>39'344.92</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.5555</v>
+        <v>0.4665</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.4637</v>
+        <v>0.6772</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5188</v>
+        <v>0.5508</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -4327,58 +4327,58 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00749</t>
+          <t>CM-26-01041</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Viña Tondonia Gran Reserva</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Bodegas López de Heredia Viña Tondonia</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>9.33%</t>
+          <t>16.67%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>39'344.92</t>
+          <t>5'717.80</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.4665</v>
+        <v>0.8335</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4671</v>
+        <v>0.0984</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4667</v>
+        <v>0.5395</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -4387,58 +4387,58 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01461</t>
+          <t>CM-25-02970</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Landonne</t>
+          <t>Finca Piedra Infinita Gravascal</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>31</v>
+        <v>512</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>12.90%</t>
+          <t>6.45%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>11'271.04</t>
+          <t>48'377.02</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.645</v>
+        <v>0.3225</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1338</v>
+        <v>0.8327</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4405</v>
+        <v>0.5266</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -4447,58 +4447,58 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02472</t>
+          <t>CM-26-01461</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Clos de Vougeot</t>
+          <t>Côte Rôtie La Landonne</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leroy</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>12.90%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>84'240.00</t>
+          <t>11'271.04</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.043</v>
+        <v>0.645</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1</v>
+        <v>0.194</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.4258</v>
+        <v>0.4646</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -4507,58 +4507,58 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02970</t>
+          <t>CM-26-00724</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita Gravascal</t>
+          <t>Cheval Blanc</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Château Cheval Blanc</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>512</v>
+        <v>106</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>48'512.22</t>
+          <t>53'840.62</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3225</v>
+        <v>0.1415</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.5759</v>
+        <v>0.9268</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4239</v>
+        <v>0.4556</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -4567,58 +4567,58 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01175</t>
+          <t>CM-26-00293</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Latour (Ex-Château)</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>15'223.41</t>
+          <t>51'964.65</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5405</v>
+        <v>0.1615</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1807</v>
+        <v>0.8945</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3966</v>
+        <v>0.4547</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -4627,17 +4627,17 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01757</t>
+          <t>CM-26-01175</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Duclot 9 bottles Case Bordeaux Collection (1 x 75cl of each Petrus, Mouton, Lafite, Latour, Margaux, Haut Brion, Mission, Cheval, Yquem)</t>
+          <t>Côte Rôtie La Mouline</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -4647,38 +4647,38 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Groupe Duclot</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>8.70%</t>
+          <t>10.81%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>22'358.22</t>
+          <t>15'223.41</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.435</v>
+        <v>0.5405</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2654</v>
+        <v>0.262</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3672</v>
+        <v>0.4291</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -4687,58 +4687,58 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01431</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>56</v>
+        <v>184</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>10.71%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>5'680.00</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5355</v>
+        <v>0.027</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0674</v>
+        <v>1</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.4162</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00293</t>
+          <t>CM-26-01757</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -4757,48 +4757,48 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Latour (Ex-Château)</t>
+          <t>Duclot 9 bottles Case Bordeaux Collection (1 x 75cl of each Petrus, Mouton, Lafite, Latour, Margaux, Haut Brion, Mission, Cheval, Yquem)</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Groupe Duclot</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>8.70%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>51'964.65</t>
+          <t>21'487.96</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1615</v>
+        <v>0.435</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.6169</v>
+        <v>0.3699</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.3437</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -4807,58 +4807,58 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00724</t>
+          <t>CM-25-02625</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Cheval Blanc</t>
+          <t>Rumbo al Norte</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Château Cheval Blanc</t>
+          <t>Bodega Comando G</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>53'840.62</t>
+          <t>37'852.12</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1415</v>
+        <v>0.206</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.6391</v>
+        <v>0.6515</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3405</v>
+        <v>0.3842</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00771</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -4877,48 +4877,48 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>10'123.30</t>
+          <t>43'696.73</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.4545</v>
+        <v>0.111</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1202</v>
+        <v>0.7522</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3208</v>
+        <v>0.3675</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -4927,58 +4927,58 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02625</t>
+          <t>CM-26-00871</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Rumbo al Norte</t>
+          <t>Chambertin Très Vieilles Vignes</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Bodega Comando G</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>170</v>
+        <v>38</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>37'852.12</t>
+          <t>29'483.52</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.206</v>
+        <v>0.263</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.4493</v>
+        <v>0.5075</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3033</v>
+        <v>0.3608</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -4987,58 +4987,58 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00871</t>
+          <t>CM-26-01431</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>10.71%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>29'483.52</t>
+          <t>5'680.00</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.263</v>
+        <v>0.5355</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.35</v>
+        <v>0.0978</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2978</v>
+        <v>0.3604</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -5047,58 +5047,58 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-01535</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>31'223.10</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.027</v>
+        <v>0.2275</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.6896</v>
+        <v>0.5374</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.292</v>
+        <v>0.3515</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -5107,58 +5107,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01535</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>31'223.10</t>
+          <t>34'794.10</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.2275</v>
+        <v>0.1785</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.3706</v>
+        <v>0.5989</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2847</v>
+        <v>0.3467</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -5167,58 +5167,58 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-00771</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>10'637.89</t>
+          <t>10'123.30</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3845</v>
+        <v>0.4545</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.1263</v>
+        <v>0.1743</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2812</v>
+        <v>0.3424</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -5227,58 +5227,58 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01429</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>6'458.03</t>
+          <t>38'286.83</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.4165</v>
+        <v>0.1065</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0767</v>
+        <v>0.659</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2806</v>
+        <v>0.3275</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -5297,48 +5297,48 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>43'696.73</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.111</v>
+        <v>0.102</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5187</v>
+        <v>0.6248</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2741</v>
+        <v>0.3111</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -5347,58 +5347,58 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>112</v>
+        <v>26</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>34'794.10</t>
+          <t>10'637.89</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1785</v>
+        <v>0.3845</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.413</v>
+        <v>0.1831</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2723</v>
+        <v>0.3039</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5455,10 +5455,10 @@
         <v>0.319</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1902</v>
+        <v>0.2757</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2675</v>
+        <v>0.3017</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -5477,48 +5477,48 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>3'517.88</t>
+          <t>26'801.63</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.408</v>
+        <v>0.1935</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0418</v>
+        <v>0.4613</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2615</v>
+        <v>0.3006</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5527,58 +5527,58 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01429</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>38'286.83</t>
+          <t>6'458.03</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1065</v>
+        <v>0.4165</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.1112</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2457</v>
+        <v>0.2944</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5587,58 +5587,58 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-00553</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>26'801.63</t>
+          <t>37'269.73</t>
         </is>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.1935</v>
+        <v>0.03</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.3182</v>
+        <v>0.6415</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2434</v>
+        <v>0.2746</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5647,58 +5647,58 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
         <v>49</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>3'517.88</t>
         </is>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.102</v>
+        <v>0.408</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.4309</v>
+        <v>0.0606</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2336</v>
+        <v>0.269</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -5755,10 +5755,10 @@
         <v>0.205</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.2141</v>
+        <v>0.3104</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2086</v>
+        <v>0.2472</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00553</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -5787,38 +5787,38 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>37'269.73</t>
+          <t>21'358.58</t>
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.03</v>
+        <v>0.141</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.4424</v>
+        <v>0.3676</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.195</v>
+        <v>0.2316</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -5827,58 +5827,58 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-26-00774</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>La Grande Rue</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Domaine Francois Lamarche</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>12'881.25</t>
         </is>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.2175</v>
+        <v>0.2085</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1399</v>
+        <v>0.2217</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1865</v>
+        <v>0.2138</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -5887,58 +5887,58 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2085</v>
+        <v>0.2175</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1529</v>
+        <v>0.2029</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1863</v>
+        <v>0.2117</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -5947,58 +5947,58 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-26-01582</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>71</v>
+        <v>940</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>21'358.58</t>
+          <t>24'405.62</t>
         </is>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.141</v>
+        <v>0.0585</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.2535</v>
+        <v>0.4201</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.186</v>
+        <v>0.2031</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6007,58 +6007,58 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>76</v>
+        <v>179</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>5'754.59</t>
+          <t>14'592.69</t>
         </is>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.263</v>
+        <v>0.1675</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.0683</v>
+        <v>0.2512</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.1851</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -6115,10 +6115,10 @@
         <v>0.2175</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1156</v>
+        <v>0.1676</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.1767</v>
+        <v>0.1975</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -6127,58 +6127,58 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03240</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>245</v>
+        <v>76</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>12'609.72</t>
+          <t>5'754.59</t>
         </is>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.1835</v>
+        <v>0.263</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.1497</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.17</v>
+        <v>0.1974</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -6187,58 +6187,58 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-25-03240</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Château Larcis Ducasse</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>14'592.69</t>
+          <t>12'609.72</t>
         </is>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.1675</v>
+        <v>0.1835</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1732</v>
+        <v>0.2171</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1698</v>
+        <v>0.1969</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00844</t>
+          <t>CM-26-01494</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -6257,48 +6257,48 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>10'599.18</t>
+          <t>17'751.48</t>
         </is>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.185</v>
+        <v>0.122</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.1258</v>
+        <v>0.3056</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.1613</v>
+        <v>0.1954</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -6355,10 +6355,10 @@
         <v>0.1355</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1904</v>
+        <v>0.2761</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1575</v>
+        <v>0.1917</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01494</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -6377,48 +6377,48 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="I42" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>17'751.48</t>
+          <t>24'206.56</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.122</v>
+        <v>0.0385</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.2107</v>
+        <v>0.4167</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.1575</v>
+        <v>0.1898</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -6427,58 +6427,58 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01486</t>
+          <t>CM-26-00844</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>3'550.60</t>
+          <t>10'599.18</t>
         </is>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.2275</v>
+        <v>0.185</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.0421</v>
+        <v>0.1824</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1533</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -6487,58 +6487,58 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02431</t>
+          <t>CM-26-00730</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>La Violette</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Château La Violette</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>156</v>
+        <v>95</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>11'961.88</t>
+          <t>17'433.26</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.1605</v>
+        <v>0.1055</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.142</v>
+        <v>0.3001</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.1531</v>
+        <v>0.1833</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -6547,58 +6547,58 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00730</t>
+          <t>CM-25-02431</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>La Violette</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Château La Violette</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>17'433.26</t>
+          <t>11'961.88</t>
         </is>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.1055</v>
+        <v>0.1605</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.2069</v>
+        <v>0.2059</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.1461</v>
+        <v>0.1787</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -6636,29 +6636,29 @@
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>130</v>
+        <v>313</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>24'206.56</t>
+          <t>22'583.46</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.0385</v>
+        <v>0.016</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.2874</v>
+        <v>0.3887</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.1381</v>
+        <v>0.1651</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -6667,58 +6667,58 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01582</t>
+          <t>CM-26-01486</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>940</v>
+        <v>22</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>21'030.62</t>
+          <t>3'550.60</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.053</v>
+        <v>0.2275</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.2497</v>
+        <v>0.0611</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.1317</v>
+        <v>0.1609</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -6727,58 +6727,58 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02972</t>
+          <t>CM-26-00594</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita</t>
+          <t>Côte Rôtie La Mordorée</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Maison M. Chapoutier</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>1'277.97</t>
+          <t>12'780.81</t>
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.2055</v>
+        <v>0.1135</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.0152</v>
+        <v>0.22</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.1294</v>
+        <v>0.1561</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -6787,58 +6787,58 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00594</t>
+          <t>CM-25-02689</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mordorée</t>
+          <t>Nuits Saint Georges la Perrière</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Maison M. Chapoutier</t>
+          <t>Domaine Gouges Henri</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>12'780.81</t>
+          <t>3'300.53</t>
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.1135</v>
+        <v>0.185</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.1517</v>
+        <v>0.0568</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.1288</v>
+        <v>0.1337</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02689</t>
+          <t>CM-25-02972</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges la Perrière</t>
+          <t>Finca Piedra Infinita</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -6867,38 +6867,38 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Domaine Gouges Henri</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>3'300.53</t>
+          <t>1'277.97</t>
         </is>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.185</v>
+        <v>0.2055</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.0392</v>
+        <v>0.022</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.1267</v>
+        <v>0.1321</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -6907,58 +6907,58 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01500</t>
+          <t>CM-26-00963</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2'260.35</t>
+          <t>12'828.11</t>
         </is>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0.187</v>
+        <v>0.0675</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.0268</v>
+        <v>0.2208</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.1229</v>
+        <v>0.1288</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -6967,58 +6967,58 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-01500</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>313</v>
+        <v>107</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>22'583.46</t>
+          <t>2'260.35</t>
         </is>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.016</v>
+        <v>0.187</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.2681</v>
+        <v>0.0389</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.1168</v>
+        <v>0.1278</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -7027,58 +7027,58 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02637</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Hommage à Jacques Perrin</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Château de Beaucastel</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>28</v>
+        <v>348</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>1'587.81</t>
+          <t>14'566.45</t>
         </is>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0.1785</v>
+        <v>0.043</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.0188</v>
+        <v>0.2507</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.1146</v>
+        <v>0.1261</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01284</t>
+          <t>CM-25-02474</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -7097,48 +7097,48 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Mazoyères-Chambertin</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Arnaud Mortet</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>8'112.00</t>
+          <t>9'311.67</t>
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.111</v>
+        <v>0.1</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.0963</v>
+        <v>0.1603</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.1051</v>
+        <v>0.1241</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02474</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -7157,48 +7157,48 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Mazoyères-Chambertin</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Arnaud Mortet</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>9'311.67</t>
+          <t>8'112.00</t>
         </is>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.1</v>
+        <v>0.111</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.1105</v>
+        <v>0.1396</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.1042</v>
+        <v>0.1224</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -7207,27 +7207,27 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -7236,29 +7236,29 @@
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>74</v>
+        <v>317</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>12'828.11</t>
+          <t>12'111.33</t>
         </is>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.0675</v>
+        <v>0.063</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.1523</v>
+        <v>0.2085</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.1014</v>
+        <v>0.1212</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -7315,10 +7315,10 @@
         <v>0.078</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.1271</v>
+        <v>0.1843</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.1205</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -7327,27 +7327,27 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -7356,29 +7356,29 @@
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>317</v>
+        <v>487</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>12'111.33</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.063</v>
+        <v>0.031</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.1438</v>
+        <v>0.2488</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.0953</v>
+        <v>0.1181</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -7387,58 +7387,58 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01376</t>
+          <t>CM-25-02637</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
+          <t>Hommage à Jacques Perrin</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Bollinger</t>
+          <t>Château de Beaucastel</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>348</v>
+        <v>28</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>14'566.45</t>
+          <t>1'587.81</t>
         </is>
       </c>
       <c r="L59" s="6" t="n">
-        <v>0.043</v>
+        <v>0.1785</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0.1729</v>
+        <v>0.0273</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.095</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -7447,58 +7447,58 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02628</t>
+          <t>CM-26-00772</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Grillet Blanc</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Château Grillet</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>6'957.56</t>
+          <t>10'109.38</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.1015</v>
+        <v>0.076</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.174</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.0939</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -7507,58 +7507,58 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00772</t>
+          <t>CM-25-02628</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Grillet Blanc</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Château Grillet</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>10'109.38</t>
+          <t>6'957.56</t>
         </is>
       </c>
       <c r="L61" s="6" t="n">
-        <v>0.076</v>
+        <v>0.1015</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.12</v>
+        <v>0.1198</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.0936</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -7567,58 +7567,58 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-01550</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>8'391.60</t>
         </is>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.104</v>
+        <v>0.0825</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.0684</v>
+        <v>0.1444</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0.0898</v>
+        <v>0.1073</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -7627,58 +7627,58 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01550</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="I63" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>8'391.60</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>0.0825</v>
+        <v>0.104</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.0992</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>0.0893</v>
+        <v>0.1021</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -7735,10 +7735,10 @@
         <v>0.11</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.0558</v>
+        <v>0.0808</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.0883</v>
+        <v>0.0983</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -7747,58 +7747,58 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-25-03004</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>10'547.81</t>
         </is>
       </c>
       <c r="L65" s="6" t="n">
-        <v>0.031</v>
+        <v>0.042</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>0.1716</v>
+        <v>0.1816</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>0.0872</v>
+        <v>0.0978</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -7807,58 +7807,58 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01542</t>
+          <t>CM-25-02535</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Meursault Clos des Bouchers</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Domaine Jean Marc Roulot</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>87</v>
+        <v>268</v>
       </c>
       <c r="I66" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2'427.03</t>
+          <t>10'885.80</t>
         </is>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.115</v>
+        <v>0.0375</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.0288</v>
+        <v>0.1874</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.0805</v>
+        <v>0.0975</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -7915,10 +7915,10 @@
         <v>0.0735</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.1267</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>0.0791</v>
+        <v>0.0948</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -7975,10 +7975,10 @@
         <v>0.0735</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.1208</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.0774</v>
+        <v>0.0924</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -7987,58 +7987,58 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01542</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2'738.04</t>
+          <t>2'427.03</t>
         </is>
       </c>
       <c r="L69" s="6" t="n">
-        <v>0.1065</v>
+        <v>0.115</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>0.0325</v>
+        <v>0.0418</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>0.0769</v>
+        <v>0.0857</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -8047,58 +8047,58 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03004</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>476</v>
+        <v>235</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>10'547.81</t>
+          <t>2'738.04</t>
         </is>
       </c>
       <c r="L70" s="4" t="n">
-        <v>0.042</v>
+        <v>0.1065</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.1252</v>
+        <v>0.0471</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0827</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -8107,58 +8107,58 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02535</t>
+          <t>CM-25-02609</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Meursault Clos des Bouchers</t>
+          <t>Clos de la Roche</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>Domaine Jean Marc Roulot</t>
+          <t>Domaine Georges Lignier</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>268</v>
+        <v>233</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>10'885.80</t>
+          <t>5'003.90</t>
         </is>
       </c>
       <c r="L71" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.0645</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>0.1292</v>
+        <v>0.0861</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>0.0742</v>
+        <v>0.0731</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -8167,17 +8167,17 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02609</t>
+          <t>CM-26-01755</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Clos de la Roche</t>
+          <t>Echézeaux</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -8187,38 +8187,38 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Lignier</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>5'003.90</t>
+          <t>8'422.42</t>
         </is>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.0645</v>
+        <v>0.023</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.0594</v>
+        <v>0.145</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.0625</v>
+        <v>0.0718</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -8275,10 +8275,10 @@
         <v>0.0945</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>0.0083</v>
+        <v>0.012</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>0.06</v>
+        <v>0.0615</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -8287,58 +8287,58 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01755</t>
+          <t>CM-26-01481</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Echézeaux</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>8'422.42</t>
+          <t>2'329.06</t>
         </is>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.023</v>
+        <v>0.0595</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.1</v>
+        <v>0.0401</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.0538</v>
+        <v>0.0517</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -8347,58 +8347,58 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01481</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>252</v>
+        <v>100</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2'329.06</t>
+          <t>3'049.20</t>
         </is>
       </c>
       <c r="L75" s="6" t="n">
-        <v>0.0595</v>
+        <v>0.05</v>
       </c>
       <c r="M75" s="6" t="n">
-        <v>0.0276</v>
+        <v>0.0525</v>
       </c>
       <c r="N75" s="6" t="n">
-        <v>0.0467</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -8407,58 +8407,58 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-26-01495</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>100</v>
+        <v>393</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>3'049.20</t>
+          <t>2'846.36</t>
         </is>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.0362</v>
+        <v>0.049</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.0445</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -8467,22 +8467,22 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01495</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -8492,33 +8492,33 @@
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>393</v>
+        <v>257</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2'846.36</t>
+          <t>3'382.19</t>
         </is>
       </c>
       <c r="L77" s="6" t="n">
-        <v>0.051</v>
+        <v>0.039</v>
       </c>
       <c r="M77" s="6" t="n">
-        <v>0.0338</v>
+        <v>0.0582</v>
       </c>
       <c r="N77" s="6" t="n">
-        <v>0.0441</v>
+        <v>0.0467</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -8527,58 +8527,58 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-26-00851</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>3'382.19</t>
+          <t>4'218.04</t>
         </is>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0.039</v>
+        <v>0.0185</v>
       </c>
       <c r="M78" s="4" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="N78" s="4" t="n">
         <v>0.0401</v>
-      </c>
-      <c r="N78" s="4" t="n">
-        <v>0.0394</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -8635,10 +8635,10 @@
         <v>0.031</v>
       </c>
       <c r="M79" s="6" t="n">
-        <v>0.0346</v>
+        <v>0.0501</v>
       </c>
       <c r="N79" s="6" t="n">
-        <v>0.0324</v>
+        <v>0.0386</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -8647,58 +8647,58 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00851</t>
+          <t>CM-25-02656</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Weingut Markus Molitor</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>271</v>
+        <v>324</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>4'218.04</t>
+          <t>1'865.44</t>
         </is>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0.0185</v>
+        <v>0.031</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>0.0501</v>
+        <v>0.0321</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>0.0311</v>
+        <v>0.0314</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02656</t>
+          <t>CM-26-01497</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -8717,48 +8717,48 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Weingut Markus Molitor</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>324</v>
+        <v>483</v>
       </c>
       <c r="I81" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>1'865.44</t>
+          <t>1'936.52</t>
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>0.031</v>
+        <v>0.0205</v>
       </c>
       <c r="M81" s="6" t="n">
-        <v>0.0221</v>
+        <v>0.0333</v>
       </c>
       <c r="N81" s="6" t="n">
-        <v>0.0274</v>
+        <v>0.0256</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -8767,17 +8767,17 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01497</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -8792,33 +8792,33 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>483</v>
+        <v>280</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>1'936.52</t>
+          <t>568.18</t>
         </is>
       </c>
       <c r="L82" s="4" t="n">
-        <v>0.0205</v>
+        <v>0.018</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>0.023</v>
+        <v>0.0098</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>0.0215</v>
+        <v>0.0147</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -8827,58 +8827,58 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>280</v>
+        <v>129</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>568.18</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L83" s="6" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="M83" s="6" t="n">
-        <v>0.0067</v>
+        <v>0</v>
       </c>
       <c r="N83" s="6" t="n">
-        <v>0.0135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -8897,26 +8897,26 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I84" s="4" t="n">
         <v>0</v>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -8957,26 +8957,26 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>63</v>
+        <v>543</v>
       </c>
       <c r="I85" s="6" t="n">
         <v>0</v>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -9027,16 +9027,16 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="I86" s="4" t="n">
         <v>0</v>
@@ -9067,7 +9067,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -9077,26 +9077,26 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>543</v>
+        <v>11</v>
       </c>
       <c r="I87" s="6" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -9137,26 +9137,26 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I88" s="4" t="n">
         <v>0</v>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -9197,26 +9197,26 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>11</v>
+        <v>362</v>
       </c>
       <c r="I89" s="6" t="n">
         <v>0</v>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -9257,26 +9257,26 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="I90" s="4" t="n">
         <v>0</v>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -9317,12 +9317,12 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -9332,11 +9332,11 @@
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>362</v>
+        <v>126</v>
       </c>
       <c r="I91" s="6" t="n">
         <v>0</v>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -9392,11 +9392,11 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H92" s="4" t="n">
-        <v>28</v>
+        <v>252</v>
       </c>
       <c r="I92" s="4" t="n">
         <v>0</v>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -9447,16 +9447,16 @@
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
-        <v>126</v>
+        <v>643</v>
       </c>
       <c r="I93" s="6" t="n">
         <v>0</v>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -9497,26 +9497,26 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H94" s="4" t="n">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="I94" s="4" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-25-02472</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -9557,26 +9557,26 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Clos de Vougeot</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leroy</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H95" s="6" t="n">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="I95" s="6" t="n">
         <v>0</v>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -9617,26 +9617,26 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H96" s="4" t="n">
-        <v>643</v>
+        <v>103</v>
       </c>
       <c r="I96" s="4" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -9677,26 +9677,26 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H97" s="6" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="I97" s="6" t="n">
         <v>0</v>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-01479</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -9737,26 +9737,26 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H98" s="4" t="n">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="I98" s="4" t="n">
         <v>0</v>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
@@ -9812,11 +9812,11 @@
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H99" s="6" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="I99" s="6" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -9917,17 +9917,17 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
@@ -9936,7 +9936,7 @@
         </is>
       </c>
       <c r="H101" s="6" t="n">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="I101" s="6" t="n">
         <v>0</v>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01288</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -9977,26 +9977,26 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H102" s="4" t="n">
-        <v>240</v>
+        <v>104</v>
       </c>
       <c r="I102" s="4" t="n">
         <v>0</v>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01310</t>
+          <t>CM-26-01288</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -10037,26 +10037,26 @@
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H103" s="6" t="n">
-        <v>716</v>
+        <v>240</v>
       </c>
       <c r="I103" s="6" t="n">
         <v>0</v>
@@ -10087,36 +10087,36 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01341</t>
+          <t>CM-26-01310</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Cathiard Vineyard</t>
+          <t>Domaine Georges Roumier</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H104" s="4" t="n">
-        <v>91</v>
+        <v>716</v>
       </c>
       <c r="I104" s="4" t="n">
         <v>0</v>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01349</t>
+          <t>CM-26-01341</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -10157,26 +10157,26 @@
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Cathiard Vineyard</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H105" s="6" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I105" s="6" t="n">
         <v>0</v>
@@ -10207,36 +10207,36 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01477</t>
+          <t>CM-26-01349</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="H106" s="4" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I106" s="4" t="n">
         <v>0</v>
@@ -10267,7 +10267,7 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01479</t>
+          <t>CM-26-01477</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -10296,7 +10296,7 @@
         </is>
       </c>
       <c r="H107" s="6" t="n">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="I107" s="6" t="n">
         <v>0</v>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,8 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +53,10 @@
     <font>
       <name val="Calibri"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00999999"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -128,6 +131,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -522,7 +526,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:58  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2140,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 03 Jun 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 08 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:58  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2219,188 +2223,14 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01753</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Echézeaux</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Rouget Emmanuel</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>37'482.23</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>0.6452</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0.8581</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01757</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Duclot 9 bottles Case Bordeaux Collection (1 x 75cl of each Petrus, Mouton, Lafite, Latour, Margaux, Haut Brion, Mission, Cheval, Yquem)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Groupe Duclot</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>8.70%</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>21'487.96</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>0.3699</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>0.409</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01755</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Echézeaux</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Rouget Emmanuel</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>216</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>0.46%</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>8'422.42</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0.0718</v>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>No data for this period.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N6"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2415,7 +2245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2437,14 +2267,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 11 May 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 16 May 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:58  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2582,71 +2412,71 @@
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01461</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Landonne</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>12.90%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>11'271.04</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.645</v>
+        <v>0.027</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.194</v>
+        <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4646</v>
+        <v>0.4162</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-01757</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2656,117 +2486,117 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Duclot 9 bottles Case Bordeaux Collection (1 x 75cl of each Petrus, Mouton, Lafite, Latour, Margaux, Haut Brion, Mission, Cheval, Yquem)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Groupe Duclot</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>8.70%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>21'487.96</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.027</v>
+        <v>0.435</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1</v>
+        <v>0.3699</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.4162</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01757</t>
+          <t>CM-26-01535</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Duclot 9 bottles Case Bordeaux Collection (1 x 75cl of each Petrus, Mouton, Lafite, Latour, Margaux, Haut Brion, Mission, Cheval, Yquem)</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Groupe Duclot</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>8.70%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>21'487.96</t>
+          <t>31'223.10</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.435</v>
+        <v>0.2275</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3699</v>
+        <v>0.5374</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.409</v>
+        <v>0.3515</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01535</t>
+          <t>CM-26-01582</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -2776,57 +2606,57 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Philipponnat